--- a/assets_output/09_logistic_regression_blocks.xlsx
+++ b/assets_output/09_logistic_regression_blocks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="156">
   <si>
     <t>MNLogit: 'Route outcomes after 3.08 years', table 0</t>
   </si>
@@ -49,7 +49,7 @@
     <t>rt_outcome</t>
   </si>
   <si>
-    <t>2026-06-14 15:09</t>
+    <t>2026-06-19 14:29</t>
   </si>
   <si>
     <t>2679</t>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>has_longer_term_rt</t>
+  </si>
+  <si>
+    <t>2026-06-19 14:30</t>
   </si>
   <si>
     <t>3032</t>
@@ -4683,7 +4686,7 @@
         <v>18</v>
       </c>
       <c r="E201" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4694,13 +4697,13 @@
         <v>3</v>
       </c>
       <c r="C202" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="D202" t="s">
         <v>19</v>
       </c>
       <c r="E202" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -4711,13 +4714,13 @@
         <v>4</v>
       </c>
       <c r="C203" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D203" t="s">
         <v>20</v>
       </c>
       <c r="E203" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -4734,7 +4737,7 @@
         <v>21</v>
       </c>
       <c r="E204" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -4745,13 +4748,13 @@
         <v>6</v>
       </c>
       <c r="C205" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D205" t="s">
         <v>22</v>
       </c>
       <c r="E205" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -4768,7 +4771,7 @@
         <v>23</v>
       </c>
       <c r="E206" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -4779,7 +4782,7 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D207" t="s">
         <v>24</v>
@@ -4790,7 +4793,7 @@
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -4861,7 +4864,7 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B213">
         <v>-1.1</v>
@@ -4976,7 +4979,7 @@
     </row>
     <row r="219" spans="1:7">
       <c r="A219" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -5058,7 +5061,7 @@
     </row>
     <row r="224" spans="1:7">
       <c r="A224" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B224">
         <v>0.3</v>
@@ -5135,7 +5138,7 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -5177,13 +5180,13 @@
         <v>2</v>
       </c>
       <c r="C232" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D232" t="s">
         <v>18</v>
       </c>
       <c r="E232" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -5194,13 +5197,13 @@
         <v>3</v>
       </c>
       <c r="C233" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="D233" t="s">
         <v>19</v>
       </c>
       <c r="E233" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -5211,13 +5214,13 @@
         <v>4</v>
       </c>
       <c r="C234" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D234" t="s">
         <v>20</v>
       </c>
       <c r="E234" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -5228,13 +5231,13 @@
         <v>5</v>
       </c>
       <c r="C235" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D235" t="s">
         <v>21</v>
       </c>
       <c r="E235" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -5245,13 +5248,13 @@
         <v>6</v>
       </c>
       <c r="C236" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D236" t="s">
         <v>22</v>
       </c>
       <c r="E236" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -5268,7 +5271,7 @@
         <v>23</v>
       </c>
       <c r="E237" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -5290,7 +5293,7 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -5338,7 +5341,7 @@
     </row>
     <row r="243" spans="1:7">
       <c r="A243" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B243">
         <v>2.5</v>
@@ -5384,7 +5387,7 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B245">
         <v>1.2</v>
@@ -5407,7 +5410,7 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -5449,7 +5452,7 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -5469,7 +5472,7 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -5509,7 +5512,7 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -5551,13 +5554,13 @@
         <v>2</v>
       </c>
       <c r="C257" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D257" t="s">
         <v>18</v>
       </c>
       <c r="E257" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="258" spans="1:8">
@@ -5568,13 +5571,13 @@
         <v>3</v>
       </c>
       <c r="C258" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="D258" t="s">
         <v>19</v>
       </c>
       <c r="E258" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -5585,13 +5588,13 @@
         <v>4</v>
       </c>
       <c r="C259" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D259" t="s">
         <v>20</v>
       </c>
       <c r="E259" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -5602,13 +5605,13 @@
         <v>5</v>
       </c>
       <c r="C260" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D260" t="s">
         <v>21</v>
       </c>
       <c r="E260" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -5619,13 +5622,13 @@
         <v>6</v>
       </c>
       <c r="C261" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D261" t="s">
         <v>22</v>
       </c>
       <c r="E261" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -5642,7 +5645,7 @@
         <v>23</v>
       </c>
       <c r="E262" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -5664,12 +5667,12 @@
     </row>
     <row r="265" spans="1:8">
       <c r="A265" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="266" spans="1:8">
       <c r="B266" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>34</v>
@@ -5874,10 +5877,10 @@
     </row>
     <row r="274" spans="1:8">
       <c r="A274" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B274" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C274">
         <v>-0.2</v>
@@ -5978,10 +5981,10 @@
     </row>
     <row r="278" spans="1:8">
       <c r="A278" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B278" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C278">
         <v>-0.1</v>
@@ -6030,12 +6033,12 @@
     </row>
     <row r="281" spans="1:8">
       <c r="A281" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="282" spans="1:8">
       <c r="B282" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>34</v>
@@ -6240,10 +6243,10 @@
     </row>
     <row r="290" spans="1:8">
       <c r="A290" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B290" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C290">
         <v>0.1</v>
@@ -6344,10 +6347,10 @@
     </row>
     <row r="294" spans="1:8">
       <c r="A294" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B294" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C294">
         <v>-0</v>
@@ -6396,12 +6399,12 @@
     </row>
     <row r="297" spans="1:8">
       <c r="A297" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="B298" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>34</v>
@@ -6606,10 +6609,10 @@
     </row>
     <row r="306" spans="1:8">
       <c r="A306" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B306" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C306">
         <v>-0.1</v>
@@ -6710,10 +6713,10 @@
     </row>
     <row r="310" spans="1:8">
       <c r="A310" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B310" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C310">
         <v>0.3</v>
@@ -6762,12 +6765,12 @@
     </row>
     <row r="313" spans="1:8">
       <c r="A313" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="B314" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>34</v>
@@ -6972,10 +6975,10 @@
     </row>
     <row r="322" spans="1:8">
       <c r="A322" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B322" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C322">
         <v>0.1</v>
@@ -7076,10 +7079,10 @@
     </row>
     <row r="326" spans="1:8">
       <c r="A326" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B326" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C326">
         <v>0.1</v>
@@ -7128,12 +7131,12 @@
     </row>
     <row r="329" spans="1:8">
       <c r="A329" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="B330" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>34</v>
@@ -7338,10 +7341,10 @@
     </row>
     <row r="338" spans="1:8">
       <c r="A338" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B338" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C338">
         <v>-0</v>
@@ -7442,10 +7445,10 @@
     </row>
     <row r="342" spans="1:8">
       <c r="A342" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B342" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C342">
         <v>0.1</v>
@@ -7494,12 +7497,12 @@
     </row>
     <row r="345" spans="1:8">
       <c r="A345" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="346" spans="1:8">
       <c r="B346" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>34</v>
@@ -7704,10 +7707,10 @@
     </row>
     <row r="354" spans="1:8">
       <c r="A354" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B354" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C354">
         <v>-0.4</v>
@@ -7808,10 +7811,10 @@
     </row>
     <row r="358" spans="1:8">
       <c r="A358" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B358" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C358">
         <v>-0.5</v>
@@ -7860,7 +7863,7 @@
     </row>
     <row r="361" spans="1:8">
       <c r="A361" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -7945,7 +7948,7 @@
     <row r="366" spans="1:8">
       <c r="A366" s="1"/>
       <c r="B366" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C366">
         <v>0.1</v>
@@ -8020,7 +8023,7 @@
     <row r="370" spans="1:7">
       <c r="A370" s="1"/>
       <c r="B370" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C370">
         <v>0.2</v>
@@ -8130,7 +8133,7 @@
     </row>
     <row r="376" spans="1:7">
       <c r="A376" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B376" s="1" t="s">
         <v>40</v>
@@ -8190,7 +8193,7 @@
     <row r="379" spans="1:7">
       <c r="A379" s="1"/>
       <c r="B379" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C379">
         <v>0</v>
@@ -8271,7 +8274,7 @@
     <row r="383" spans="1:7">
       <c r="A383" s="1"/>
       <c r="B383" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C383">
         <v>0.4</v>
@@ -8384,7 +8387,7 @@
     </row>
     <row r="389" spans="1:7">
       <c r="A389" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B389" s="1" t="s">
         <v>40</v>
@@ -8447,7 +8450,7 @@
     <row r="392" spans="1:7">
       <c r="A392" s="1"/>
       <c r="B392" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C392">
         <v>0.7</v>
@@ -8522,7 +8525,7 @@
     <row r="396" spans="1:7">
       <c r="A396" s="1"/>
       <c r="B396" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C396">
         <v>0.7</v>
@@ -8635,7 +8638,7 @@
     </row>
     <row r="402" spans="1:7">
       <c r="A402" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B402" s="1" t="s">
         <v>40</v>
@@ -8695,7 +8698,7 @@
     <row r="405" spans="1:7">
       <c r="A405" s="1"/>
       <c r="B405" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C405">
         <v>0.5</v>
@@ -8767,7 +8770,7 @@
     <row r="409" spans="1:7">
       <c r="A409" s="1"/>
       <c r="B409" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C409">
         <v>0.3</v>
@@ -8877,7 +8880,7 @@
     </row>
     <row r="415" spans="1:7">
       <c r="A415" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B415" s="1" t="s">
         <v>40</v>
@@ -8943,7 +8946,7 @@
     <row r="418" spans="1:7">
       <c r="A418" s="1"/>
       <c r="B418" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C418">
         <v>0.5</v>
@@ -9021,7 +9024,7 @@
     <row r="422" spans="1:7">
       <c r="A422" s="1"/>
       <c r="B422" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C422">
         <v>0.9</v>
@@ -9197,7 +9200,7 @@
     <row r="431" spans="1:7">
       <c r="A431" s="1"/>
       <c r="B431" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C431">
         <v>0.2</v>
@@ -9275,7 +9278,7 @@
     <row r="435" spans="1:7">
       <c r="A435" s="1"/>
       <c r="B435" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C435">
         <v>0</v>

--- a/assets_output/09_logistic_regression_blocks.xlsx
+++ b/assets_output/09_logistic_regression_blocks.xlsx
@@ -49,7 +49,7 @@
     <t>rt_outcome</t>
   </si>
   <si>
-    <t>2026-06-19 14:29</t>
+    <t>2026-06-19 14:50</t>
   </si>
   <si>
     <t>2679</t>
@@ -313,7 +313,7 @@
     <t>has_longer_term_rt</t>
   </si>
   <si>
-    <t>2026-06-19 14:30</t>
+    <t>2026-06-19 14:51</t>
   </si>
   <si>
     <t>3032</t>

--- a/assets_output/09_logistic_regression_blocks.xlsx
+++ b/assets_output/09_logistic_regression_blocks.xlsx
@@ -49,7 +49,7 @@
     <t>rt_outcome</t>
   </si>
   <si>
-    <t>2026-06-19 14:50</t>
+    <t>2026-06-19 14:59</t>
   </si>
   <si>
     <t>2679</t>
@@ -313,7 +313,7 @@
     <t>has_longer_term_rt</t>
   </si>
   <si>
-    <t>2026-06-19 14:51</t>
+    <t>2026-06-19 15:00</t>
   </si>
   <si>
     <t>3032</t>

--- a/assets_output/09_logistic_regression_blocks.xlsx
+++ b/assets_output/09_logistic_regression_blocks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="159">
   <si>
     <t>MNLogit: 'Route outcomes after 3.08 years', table 0</t>
   </si>
@@ -49,7 +49,7 @@
     <t>rt_outcome</t>
   </si>
   <si>
-    <t>2026-06-19 14:59</t>
+    <t>2026-06-20 11:25</t>
   </si>
   <si>
     <t>2679</t>
@@ -268,6 +268,9 @@
     <t>multiple_returns</t>
   </si>
   <si>
+    <t>2026-06-20 11:26</t>
+  </si>
+  <si>
     <t>3015</t>
   </si>
   <si>
@@ -313,9 +316,6 @@
     <t>has_longer_term_rt</t>
   </si>
   <si>
-    <t>2026-06-19 15:00</t>
-  </si>
-  <si>
     <t>3032</t>
   </si>
   <si>
@@ -403,31 +403,31 @@
     <t>pl_outcome</t>
   </si>
   <si>
-    <t>5191</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>5113</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>17455.0005</t>
-  </si>
-  <si>
-    <t>17966.2657</t>
-  </si>
-  <si>
-    <t>-8649.5</t>
-  </si>
-  <si>
-    <t>-9247.8</t>
-  </si>
-  <si>
-    <t>2.4311e-203</t>
+    <t>5016</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>4920</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>16872.2157</t>
+  </si>
+  <si>
+    <t>17498.1730</t>
+  </si>
+  <si>
+    <t>-8340.1</t>
+  </si>
+  <si>
+    <t>-8932.8</t>
+  </si>
+  <si>
+    <t>1.6272e-190</t>
   </si>
   <si>
     <t>MNLogit: 'Outcomes from individual placements', table 1</t>
@@ -436,6 +436,15 @@
     <t>pl_outcome = 0</t>
   </si>
   <si>
+    <t>ethnicity_grouped_Black</t>
+  </si>
+  <si>
+    <t>ethnicity_grouped_Mixed Heritage</t>
+  </si>
+  <si>
+    <t>ethnicity_grouped_Other</t>
+  </si>
+  <si>
     <t>mental_health</t>
   </si>
   <si>
@@ -472,16 +481,16 @@
     <t>MNLogit: 'Outcomes from individual placements', odds ratios</t>
   </si>
   <si>
-    <t>Independent accommodation</t>
+    <t>Internal move: forwards</t>
+  </si>
+  <si>
+    <t>Internal move: sideways</t>
+  </si>
+  <si>
+    <t>Internal move: backwards</t>
   </si>
   <si>
     <t>Insecure outcome (external)</t>
-  </si>
-  <si>
-    <t>Internal move: backwards</t>
-  </si>
-  <si>
-    <t>Internal move: sideways</t>
   </si>
 </sst>
 </file>
@@ -839,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H476"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -4183,7 +4192,7 @@
         <v>18</v>
       </c>
       <c r="E170" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -4194,13 +4203,13 @@
         <v>3</v>
       </c>
       <c r="C171" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="D171" t="s">
         <v>19</v>
       </c>
       <c r="E171" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -4211,13 +4220,13 @@
         <v>4</v>
       </c>
       <c r="C172" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D172" t="s">
         <v>20</v>
       </c>
       <c r="E172" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -4228,13 +4237,13 @@
         <v>5</v>
       </c>
       <c r="C173" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D173" t="s">
         <v>21</v>
       </c>
       <c r="E173" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -4245,13 +4254,13 @@
         <v>6</v>
       </c>
       <c r="C174" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D174" t="s">
         <v>22</v>
       </c>
       <c r="E174" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -4268,7 +4277,7 @@
         <v>23</v>
       </c>
       <c r="E175" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -4290,7 +4299,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -4301,10 +4310,10 @@
         <v>35</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>38</v>
@@ -4476,7 +4485,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -4638,7 +4647,7 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4680,7 +4689,7 @@
         <v>2</v>
       </c>
       <c r="C201" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D201" t="s">
         <v>18</v>
@@ -4697,7 +4706,7 @@
         <v>3</v>
       </c>
       <c r="C202" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D202" t="s">
         <v>19</v>
@@ -4731,7 +4740,7 @@
         <v>5</v>
       </c>
       <c r="C204" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D204" t="s">
         <v>21</v>
@@ -4804,10 +4813,10 @@
         <v>35</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>38</v>
@@ -5197,7 +5206,7 @@
         <v>3</v>
       </c>
       <c r="C233" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D233" t="s">
         <v>19</v>
@@ -5304,10 +5313,10 @@
         <v>35</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>38</v>
@@ -5571,7 +5580,7 @@
         <v>3</v>
       </c>
       <c r="C258" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D258" t="s">
         <v>19</v>
@@ -5701,22 +5710,22 @@
         <v>40</v>
       </c>
       <c r="C267">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="D267">
         <v>0.1</v>
       </c>
       <c r="E267">
-        <v>2.2</v>
+        <v>-1.5</v>
       </c>
       <c r="F267">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G267">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="H267">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -5727,22 +5736,22 @@
         <v>41</v>
       </c>
       <c r="C268">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="D268">
         <v>0.1</v>
       </c>
       <c r="E268">
-        <v>1.6</v>
+        <v>-1.9</v>
       </c>
       <c r="F268">
         <v>0.1</v>
       </c>
       <c r="G268">
-        <v>-0</v>
+        <v>-0.4</v>
       </c>
       <c r="H268">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -5753,56 +5762,56 @@
         <v>42</v>
       </c>
       <c r="C269">
+        <v>0.1</v>
+      </c>
+      <c r="D269">
+        <v>0.1</v>
+      </c>
+      <c r="E269">
+        <v>1</v>
+      </c>
+      <c r="F269">
+        <v>0.3</v>
+      </c>
+      <c r="G269">
         <v>-0.1</v>
       </c>
-      <c r="D269">
-        <v>0.1</v>
-      </c>
-      <c r="E269">
-        <v>-0.8</v>
-      </c>
-      <c r="F269">
-        <v>0.4</v>
-      </c>
-      <c r="G269">
-        <v>-0.3</v>
-      </c>
       <c r="H269">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="270" spans="1:8">
       <c r="A270" s="1" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="B270" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="C270">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="D270">
         <v>0.1</v>
       </c>
       <c r="E270">
-        <v>1.5</v>
+        <v>-1.7</v>
       </c>
       <c r="F270">
         <v>0.1</v>
       </c>
       <c r="G270">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="H270">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271" spans="1:8">
       <c r="A271" s="1" t="s">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="B271" t="s">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="C271">
         <v>-0.1</v>
@@ -5811,808 +5820,808 @@
         <v>0.2</v>
       </c>
       <c r="E271">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="F271">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G271">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="H271">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="272" spans="1:8">
       <c r="A272" s="1" t="s">
-        <v>45</v>
+        <v>142</v>
       </c>
       <c r="B272" t="s">
-        <v>45</v>
+        <v>142</v>
       </c>
       <c r="C272">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="D272">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E272">
-        <v>-3.6</v>
+        <v>-0.8</v>
       </c>
       <c r="F272">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G272">
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="H272">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="273" spans="1:8">
       <c r="A273" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B273" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C273">
         <v>-0.1</v>
       </c>
       <c r="D273">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E273">
-        <v>-1.1</v>
+        <v>-0.4</v>
       </c>
       <c r="F273">
+        <v>0.7</v>
+      </c>
+      <c r="G273">
+        <v>-0.4</v>
+      </c>
+      <c r="H273">
         <v>0.3</v>
-      </c>
-      <c r="G273">
-        <v>-0.3</v>
-      </c>
-      <c r="H273">
-        <v>0.1</v>
       </c>
     </row>
     <row r="274" spans="1:8">
       <c r="A274" s="1" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="B274" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="C274">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D274">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E274">
-        <v>-2.5</v>
+        <v>0.4</v>
       </c>
       <c r="F274">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G274">
         <v>-0.4</v>
       </c>
       <c r="H274">
-        <v>-0.1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="275" spans="1:8">
       <c r="A275" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B275" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C275">
-        <v>-0.9</v>
+        <v>0.6</v>
       </c>
       <c r="D275">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E275">
-        <v>-9.1</v>
+        <v>3.7</v>
       </c>
       <c r="F275">
         <v>0</v>
       </c>
       <c r="G275">
-        <v>-1.1</v>
+        <v>0.3</v>
       </c>
       <c r="H275">
-        <v>-0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="276" spans="1:8">
       <c r="A276" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B276" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C276">
+        <v>0.1</v>
+      </c>
+      <c r="D276">
+        <v>0.1</v>
+      </c>
+      <c r="E276">
+        <v>1.1</v>
+      </c>
+      <c r="F276">
+        <v>0.3</v>
+      </c>
+      <c r="G276">
         <v>-0.1</v>
       </c>
-      <c r="D276">
-        <v>0.1</v>
-      </c>
-      <c r="E276">
-        <v>-0.6</v>
-      </c>
-      <c r="F276">
-        <v>0.6</v>
-      </c>
-      <c r="G276">
-        <v>-0.4</v>
-      </c>
       <c r="H276">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="277" spans="1:8">
       <c r="A277" s="1" t="s">
-        <v>49</v>
+        <v>143</v>
       </c>
       <c r="B277" t="s">
-        <v>49</v>
+        <v>143</v>
       </c>
       <c r="C277">
-        <v>-1.3</v>
+        <v>0.2</v>
       </c>
       <c r="D277">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E277">
-        <v>-2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F277">
         <v>0</v>
       </c>
       <c r="G277">
-        <v>-2.4</v>
+        <v>0</v>
       </c>
       <c r="H277">
-        <v>-0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="278" spans="1:8">
       <c r="A278" s="1" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="B278" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="C278">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="D278">
         <v>0.1</v>
       </c>
       <c r="E278">
-        <v>-0.8</v>
+        <v>8.6</v>
       </c>
       <c r="F278">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G278">
-        <v>-0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H278">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="279" spans="1:8">
       <c r="A279" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B279" t="s">
+        <v>48</v>
+      </c>
+      <c r="C279">
+        <v>0.1</v>
+      </c>
+      <c r="D279">
+        <v>0.1</v>
+      </c>
+      <c r="E279">
+        <v>0.4</v>
+      </c>
+      <c r="F279">
+        <v>0.7</v>
+      </c>
+      <c r="G279">
+        <v>-0.2</v>
+      </c>
+      <c r="H279">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8">
+      <c r="A280" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B280" t="s">
+        <v>49</v>
+      </c>
+      <c r="C280">
+        <v>1.3</v>
+      </c>
+      <c r="D280">
+        <v>0.5</v>
+      </c>
+      <c r="E280">
+        <v>2.4</v>
+      </c>
+      <c r="F280">
+        <v>0</v>
+      </c>
+      <c r="G280">
+        <v>0.3</v>
+      </c>
+      <c r="H280">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8">
+      <c r="A281" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B281" t="s">
+        <v>125</v>
+      </c>
+      <c r="C281">
+        <v>0.1</v>
+      </c>
+      <c r="D281">
+        <v>0.1</v>
+      </c>
+      <c r="E281">
+        <v>1</v>
+      </c>
+      <c r="F281">
+        <v>0.3</v>
+      </c>
+      <c r="G281">
+        <v>-0.1</v>
+      </c>
+      <c r="H281">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8">
+      <c r="A282" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B279" t="s">
+      <c r="B282" t="s">
         <v>50</v>
       </c>
-      <c r="C279">
-        <v>-0.5</v>
-      </c>
-      <c r="D279">
-        <v>0.2</v>
-      </c>
-      <c r="E279">
-        <v>-2.8</v>
-      </c>
-      <c r="F279">
-        <v>0</v>
-      </c>
-      <c r="G279">
-        <v>-0.9</v>
-      </c>
-      <c r="H279">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="281" spans="1:8">
-      <c r="A281" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="282" spans="1:8">
-      <c r="B282" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C282" s="1" t="s">
+      <c r="C282">
+        <v>0.5</v>
+      </c>
+      <c r="D282">
+        <v>0.2</v>
+      </c>
+      <c r="E282">
+        <v>2.5</v>
+      </c>
+      <c r="F282">
+        <v>0</v>
+      </c>
+      <c r="G282">
+        <v>0.1</v>
+      </c>
+      <c r="H282">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8">
+      <c r="A284" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8">
+      <c r="B285" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C285" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D282" s="1" t="s">
+      <c r="D285" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E282" s="1" t="s">
+      <c r="E285" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F282" s="1" t="s">
+      <c r="F285" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G282" s="1" t="s">
+      <c r="G285" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H282" s="1" t="s">
+      <c r="H285" s="1" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="283" spans="1:8">
-      <c r="A283" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B283" t="s">
-        <v>40</v>
-      </c>
-      <c r="C283">
-        <v>-1.6</v>
-      </c>
-      <c r="D283">
-        <v>0.1</v>
-      </c>
-      <c r="E283">
-        <v>-12.3</v>
-      </c>
-      <c r="F283">
-        <v>0</v>
-      </c>
-      <c r="G283">
-        <v>-1.8</v>
-      </c>
-      <c r="H283">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="284" spans="1:8">
-      <c r="A284" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B284" t="s">
-        <v>41</v>
-      </c>
-      <c r="C284">
-        <v>-0.3</v>
-      </c>
-      <c r="D284">
-        <v>0.1</v>
-      </c>
-      <c r="E284">
-        <v>-2.5</v>
-      </c>
-      <c r="F284">
-        <v>0</v>
-      </c>
-      <c r="G284">
-        <v>-0.5</v>
-      </c>
-      <c r="H284">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="285" spans="1:8">
-      <c r="A285" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B285" t="s">
-        <v>42</v>
-      </c>
-      <c r="C285">
-        <v>0.4</v>
-      </c>
-      <c r="D285">
-        <v>0.1</v>
-      </c>
-      <c r="E285">
-        <v>3.9</v>
-      </c>
-      <c r="F285">
-        <v>0</v>
-      </c>
-      <c r="G285">
-        <v>0.2</v>
-      </c>
-      <c r="H285">
-        <v>0.5</v>
       </c>
     </row>
     <row r="286" spans="1:8">
       <c r="A286" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B286" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C286">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
       <c r="D286">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E286">
-        <v>-3</v>
+        <v>-12.3</v>
       </c>
       <c r="F286">
         <v>0</v>
       </c>
       <c r="G286">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H286">
-        <v>-0.2</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B287" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C287">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="D287">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E287">
-        <v>-1.2</v>
+        <v>-4</v>
       </c>
       <c r="F287">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G287">
         <v>-0.8</v>
       </c>
       <c r="H287">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B288" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C288">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D288">
         <v>0.1</v>
       </c>
       <c r="E288">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="F288">
         <v>0</v>
       </c>
       <c r="G288">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H288">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="289" spans="1:8">
       <c r="A289" s="1" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="B289" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="C289">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="D289">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E289">
-        <v>2</v>
+        <v>-1.3</v>
       </c>
       <c r="F289">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G289">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="H289">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="290" spans="1:8">
       <c r="A290" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B290" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C290">
         <v>0.1</v>
       </c>
       <c r="D290">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E290">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="F290">
+        <v>0.7</v>
+      </c>
+      <c r="G290">
+        <v>-0.4</v>
+      </c>
+      <c r="H290">
         <v>0.5</v>
-      </c>
-      <c r="G290">
-        <v>-0.1</v>
-      </c>
-      <c r="H290">
-        <v>0.3</v>
       </c>
     </row>
     <row r="291" spans="1:8">
       <c r="A291" s="1" t="s">
-        <v>47</v>
+        <v>142</v>
       </c>
       <c r="B291" t="s">
-        <v>47</v>
+        <v>142</v>
       </c>
       <c r="C291">
-        <v>1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D291">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E291">
-        <v>12.1</v>
+        <v>-0.3</v>
       </c>
       <c r="F291">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G291">
-        <v>1.1</v>
+        <v>-0.6</v>
       </c>
       <c r="H291">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="292" spans="1:8">
       <c r="A292" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B292" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C292">
-        <v>0.7</v>
+        <v>-0.7</v>
       </c>
       <c r="D292">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E292">
-        <v>6.9</v>
+        <v>-2.9</v>
       </c>
       <c r="F292">
         <v>0</v>
       </c>
       <c r="G292">
-        <v>0.5</v>
+        <v>-1.2</v>
       </c>
       <c r="H292">
-        <v>0.9</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="293" spans="1:8">
       <c r="A293" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B293" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C293">
+        <v>-0.3</v>
+      </c>
+      <c r="D293">
         <v>0.3</v>
       </c>
-      <c r="D293">
-        <v>0.2</v>
-      </c>
       <c r="E293">
-        <v>1.5</v>
+        <v>-1</v>
       </c>
       <c r="F293">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G293">
-        <v>-0.1</v>
+        <v>-0.9</v>
       </c>
       <c r="H293">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="294" spans="1:8">
       <c r="A294" s="1" t="s">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="B294" t="s">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="C294">
-        <v>-0</v>
+        <v>1.1</v>
       </c>
       <c r="D294">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E294">
-        <v>-0.1</v>
+        <v>7.6</v>
       </c>
       <c r="F294">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G294">
-        <v>-0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H294">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="295" spans="1:8">
       <c r="A295" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B295" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C295">
-        <v>-0</v>
+        <v>0.3</v>
       </c>
       <c r="D295">
         <v>0.1</v>
       </c>
       <c r="E295">
-        <v>-0.2</v>
+        <v>2.8</v>
       </c>
       <c r="F295">
+        <v>0</v>
+      </c>
+      <c r="G295">
+        <v>0.1</v>
+      </c>
+      <c r="H295">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8">
+      <c r="A296" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B296" t="s">
+        <v>143</v>
+      </c>
+      <c r="C296">
+        <v>0.3</v>
+      </c>
+      <c r="D296">
+        <v>0.1</v>
+      </c>
+      <c r="E296">
+        <v>2.5</v>
+      </c>
+      <c r="F296">
+        <v>0</v>
+      </c>
+      <c r="G296">
+        <v>0.1</v>
+      </c>
+      <c r="H296">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8">
+      <c r="A297" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B297" t="s">
+        <v>47</v>
+      </c>
+      <c r="C297">
+        <v>2.1</v>
+      </c>
+      <c r="D297">
+        <v>0.1</v>
+      </c>
+      <c r="E297">
+        <v>17.7</v>
+      </c>
+      <c r="F297">
+        <v>0</v>
+      </c>
+      <c r="G297">
+        <v>1.9</v>
+      </c>
+      <c r="H297">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8">
+      <c r="A298" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B298" t="s">
+        <v>48</v>
+      </c>
+      <c r="C298">
         <v>0.8</v>
       </c>
-      <c r="G295">
-        <v>-0.3</v>
-      </c>
-      <c r="H295">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="297" spans="1:8">
-      <c r="A297" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="298" spans="1:8">
-      <c r="B298" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E298" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F298" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G298" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H298" s="1" t="s">
-        <v>39</v>
+      <c r="D298">
+        <v>0.1</v>
+      </c>
+      <c r="E298">
+        <v>5.8</v>
+      </c>
+      <c r="F298">
+        <v>0</v>
+      </c>
+      <c r="G298">
+        <v>0.5</v>
+      </c>
+      <c r="H298">
+        <v>1.1</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B299" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C299">
-        <v>-1.3</v>
+        <v>1.7</v>
       </c>
       <c r="D299">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="E299">
-        <v>-9.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="F299">
         <v>0</v>
       </c>
       <c r="G299">
-        <v>-1.5</v>
+        <v>0.6</v>
       </c>
       <c r="H299">
-        <v>-1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" s="1" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="B300" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="C300">
+        <v>0.1</v>
+      </c>
+      <c r="D300">
+        <v>0.2</v>
+      </c>
+      <c r="E300">
+        <v>0.8</v>
+      </c>
+      <c r="F300">
+        <v>0.4</v>
+      </c>
+      <c r="G300">
         <v>-0.2</v>
       </c>
-      <c r="D300">
-        <v>0.1</v>
-      </c>
-      <c r="E300">
-        <v>-1.7</v>
-      </c>
-      <c r="F300">
-        <v>0.1</v>
-      </c>
-      <c r="G300">
-        <v>-0.5</v>
-      </c>
       <c r="H300">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B301" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C301">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D301">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E301">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="F301">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G301">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="H301">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8">
-      <c r="A302" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B302" t="s">
-        <v>43</v>
-      </c>
-      <c r="C302">
-        <v>-0.7</v>
-      </c>
-      <c r="D302">
-        <v>0.2</v>
-      </c>
-      <c r="E302">
-        <v>-3.1</v>
-      </c>
-      <c r="F302">
-        <v>0</v>
-      </c>
-      <c r="G302">
-        <v>-1.2</v>
-      </c>
-      <c r="H302">
-        <v>-0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="303" spans="1:8">
-      <c r="A303" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B303" t="s">
-        <v>44</v>
-      </c>
-      <c r="C303">
-        <v>0.2</v>
-      </c>
-      <c r="D303">
-        <v>0.3</v>
-      </c>
-      <c r="E303">
-        <v>0.7</v>
-      </c>
-      <c r="F303">
-        <v>0.5</v>
-      </c>
-      <c r="G303">
-        <v>-0.3</v>
-      </c>
-      <c r="H303">
-        <v>0.7</v>
+      <c r="A303" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="304" spans="1:8">
-      <c r="A304" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B304" t="s">
-        <v>45</v>
-      </c>
-      <c r="C304">
-        <v>0.6</v>
-      </c>
-      <c r="D304">
-        <v>0.1</v>
-      </c>
-      <c r="E304">
-        <v>5</v>
-      </c>
-      <c r="F304">
-        <v>0</v>
-      </c>
-      <c r="G304">
-        <v>0.4</v>
-      </c>
-      <c r="H304">
-        <v>0.8</v>
+      <c r="B304" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F304" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G304" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H304" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B305" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C305">
-        <v>-0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="D305">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E305">
+        <v>-11.3</v>
+      </c>
+      <c r="F305">
+        <v>0</v>
+      </c>
+      <c r="G305">
+        <v>-2.1</v>
+      </c>
+      <c r="H305">
         <v>-1.5</v>
-      </c>
-      <c r="F305">
-        <v>0.1</v>
-      </c>
-      <c r="G305">
-        <v>-0.4</v>
-      </c>
-      <c r="H305">
-        <v>0</v>
       </c>
     </row>
     <row r="306" spans="1:8">
       <c r="A306" s="1" t="s">
-        <v>140</v>
+        <v>41</v>
       </c>
       <c r="B306" t="s">
-        <v>140</v>
+        <v>41</v>
       </c>
       <c r="C306">
         <v>-0.1</v>
@@ -6621,1624 +6630,1745 @@
         <v>0.1</v>
       </c>
       <c r="E306">
-        <v>-1.3</v>
+        <v>-0.6</v>
       </c>
       <c r="F306">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="G306">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="H306">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="A307" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B307" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C307">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D307">
         <v>0.1</v>
       </c>
       <c r="E307">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="F307">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G307">
-        <v>0.3</v>
+        <v>-0</v>
       </c>
       <c r="H307">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="308" spans="1:8">
       <c r="A308" s="1" t="s">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="B308" t="s">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="C308">
-        <v>1</v>
+        <v>-0.2</v>
       </c>
       <c r="D308">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E308">
-        <v>8.800000000000001</v>
+        <v>-0.8</v>
       </c>
       <c r="F308">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G308">
-        <v>0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="H308">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="A309" s="1" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="B309" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="C309">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="D309">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E309">
-        <v>-0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F309">
         <v>0.6</v>
       </c>
       <c r="G309">
-        <v>-0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="H309">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="310" spans="1:8">
       <c r="A310" s="1" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="B310" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="C310">
+        <v>-0.5</v>
+      </c>
+      <c r="D310">
         <v>0.3</v>
       </c>
-      <c r="D310">
-        <v>0.1</v>
-      </c>
       <c r="E310">
-        <v>2.1</v>
+        <v>-1.4</v>
       </c>
       <c r="F310">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G310">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="H310">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="A311" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B311" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C311">
-        <v>-0.3</v>
+        <v>0.1</v>
       </c>
       <c r="D311">
         <v>0.2</v>
       </c>
       <c r="E311">
-        <v>-2</v>
+        <v>0.3</v>
       </c>
       <c r="F311">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G311">
-        <v>-0.7</v>
+        <v>-0.4</v>
       </c>
       <c r="H311">
-        <v>-0</v>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8">
+      <c r="A312" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B312" t="s">
+        <v>44</v>
+      </c>
+      <c r="C312">
+        <v>0.4</v>
+      </c>
+      <c r="D312">
+        <v>0.3</v>
+      </c>
+      <c r="E312">
+        <v>1.2</v>
+      </c>
+      <c r="F312">
+        <v>0.2</v>
+      </c>
+      <c r="G312">
+        <v>-0.2</v>
+      </c>
+      <c r="H312">
+        <v>0.9</v>
       </c>
     </row>
     <row r="313" spans="1:8">
-      <c r="A313" t="s">
-        <v>145</v>
+      <c r="A313" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B313" t="s">
+        <v>45</v>
+      </c>
+      <c r="C313">
+        <v>0.7</v>
+      </c>
+      <c r="D313">
+        <v>0.2</v>
+      </c>
+      <c r="E313">
+        <v>4.2</v>
+      </c>
+      <c r="F313">
+        <v>0</v>
+      </c>
+      <c r="G313">
+        <v>0.4</v>
+      </c>
+      <c r="H313">
+        <v>1.1</v>
       </c>
     </row>
     <row r="314" spans="1:8">
-      <c r="B314" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C314" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D314" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E314" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F314" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G314" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H314" s="1" t="s">
-        <v>39</v>
+      <c r="A314" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B314" t="s">
+        <v>46</v>
+      </c>
+      <c r="C314">
+        <v>0.1</v>
+      </c>
+      <c r="D314">
+        <v>0.1</v>
+      </c>
+      <c r="E314">
+        <v>1.1</v>
+      </c>
+      <c r="F314">
+        <v>0.3</v>
+      </c>
+      <c r="G314">
+        <v>-0.1</v>
+      </c>
+      <c r="H314">
+        <v>0.4</v>
       </c>
     </row>
     <row r="315" spans="1:8">
       <c r="A315" s="1" t="s">
-        <v>40</v>
+        <v>143</v>
       </c>
       <c r="B315" t="s">
-        <v>40</v>
+        <v>143</v>
       </c>
       <c r="C315">
-        <v>-1.6</v>
+        <v>0.3</v>
       </c>
       <c r="D315">
         <v>0.1</v>
       </c>
       <c r="E315">
-        <v>-11.4</v>
+        <v>2.1</v>
       </c>
       <c r="F315">
         <v>0</v>
       </c>
       <c r="G315">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="H315">
-        <v>-1.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="A316" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B316" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C316">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="D316">
         <v>0.1</v>
       </c>
       <c r="E316">
-        <v>1.3</v>
+        <v>12.7</v>
       </c>
       <c r="F316">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G316">
-        <v>-0.1</v>
+        <v>1.4</v>
       </c>
       <c r="H316">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="A317" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B317" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C317">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D317">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E317">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="F317">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G317">
         <v>-0.1</v>
       </c>
       <c r="H317">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="318" spans="1:8">
       <c r="A318" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B318" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C318">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="D318">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E318">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="F318">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G318">
-        <v>-0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H318">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="319" spans="1:8">
       <c r="A319" s="1" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="B319" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="C319">
         <v>0.3</v>
       </c>
       <c r="D319">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E319">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="F319">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="G319">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="H319">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="320" spans="1:8">
       <c r="A320" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B320" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C320">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D320">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E320">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="F320">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G320">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H320">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="321" spans="1:8">
-      <c r="A321" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B321" t="s">
-        <v>46</v>
-      </c>
-      <c r="C321">
-        <v>0</v>
-      </c>
-      <c r="D321">
-        <v>0.1</v>
-      </c>
-      <c r="E321">
-        <v>0.1</v>
-      </c>
-      <c r="F321">
-        <v>0.9</v>
-      </c>
-      <c r="G321">
-        <v>-0.2</v>
-      </c>
-      <c r="H321">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="322" spans="1:8">
-      <c r="A322" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B322" t="s">
-        <v>140</v>
-      </c>
-      <c r="C322">
-        <v>0.1</v>
-      </c>
-      <c r="D322">
-        <v>0.1</v>
-      </c>
-      <c r="E322">
-        <v>0.7</v>
-      </c>
-      <c r="F322">
-        <v>0.5</v>
-      </c>
-      <c r="G322">
-        <v>-0.1</v>
-      </c>
-      <c r="H322">
-        <v>0.3</v>
+      <c r="A322" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="323" spans="1:8">
-      <c r="A323" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B323" t="s">
-        <v>47</v>
-      </c>
-      <c r="C323">
-        <v>0.8</v>
-      </c>
-      <c r="D323">
-        <v>0.1</v>
-      </c>
-      <c r="E323">
-        <v>6.8</v>
-      </c>
-      <c r="F323">
-        <v>0</v>
-      </c>
-      <c r="G323">
-        <v>0.6</v>
-      </c>
-      <c r="H323">
-        <v>1</v>
+      <c r="B323" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E323" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F323" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G323" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H323" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="324" spans="1:8">
       <c r="A324" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B324" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C324">
-        <v>0.1</v>
+        <v>-1.5</v>
       </c>
       <c r="D324">
         <v>0.1</v>
       </c>
       <c r="E324">
-        <v>1.1</v>
+        <v>-10.2</v>
       </c>
       <c r="F324">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G324">
-        <v>-0.1</v>
+        <v>-1.8</v>
       </c>
       <c r="H324">
-        <v>0.4</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B325" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C325">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="D325">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E325">
-        <v>0.5</v>
+        <v>-3.1</v>
       </c>
       <c r="F325">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G325">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="H325">
-        <v>0.6</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" s="1" t="s">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="B326" t="s">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="C326">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D326">
         <v>0.1</v>
       </c>
       <c r="E326">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="F326">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G326">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="H326">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="1" t="s">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="B327" t="s">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="C327">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="D327">
         <v>0.2</v>
       </c>
       <c r="E327">
+        <v>-0.7</v>
+      </c>
+      <c r="F327">
+        <v>0.5</v>
+      </c>
+      <c r="G327">
+        <v>-0.5</v>
+      </c>
+      <c r="H327">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8">
+      <c r="A328" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B328" t="s">
+        <v>141</v>
+      </c>
+      <c r="C328">
+        <v>0.2</v>
+      </c>
+      <c r="D328">
+        <v>0.2</v>
+      </c>
+      <c r="E328">
         <v>0.9</v>
       </c>
-      <c r="F327">
+      <c r="F328">
         <v>0.4</v>
       </c>
-      <c r="G327">
+      <c r="G328">
+        <v>-0.3</v>
+      </c>
+      <c r="H328">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8">
+      <c r="A329" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B329" t="s">
+        <v>142</v>
+      </c>
+      <c r="C329">
         <v>-0.2</v>
       </c>
-      <c r="H327">
+      <c r="D329">
+        <v>0.3</v>
+      </c>
+      <c r="E329">
+        <v>-0.5</v>
+      </c>
+      <c r="F329">
+        <v>0.6</v>
+      </c>
+      <c r="G329">
+        <v>-0.8</v>
+      </c>
+      <c r="H329">
         <v>0.4</v>
       </c>
     </row>
-    <row r="329" spans="1:8">
-      <c r="A329" t="s">
-        <v>147</v>
-      </c>
-    </row>
     <row r="330" spans="1:8">
-      <c r="B330" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C330" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E330" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F330" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G330" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H330" s="1" t="s">
-        <v>39</v>
+      <c r="A330" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B330" t="s">
+        <v>43</v>
+      </c>
+      <c r="C330">
+        <v>-0.8</v>
+      </c>
+      <c r="D330">
+        <v>0.3</v>
+      </c>
+      <c r="E330">
+        <v>-3.1</v>
+      </c>
+      <c r="F330">
+        <v>0</v>
+      </c>
+      <c r="G330">
+        <v>-1.4</v>
+      </c>
+      <c r="H330">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="331" spans="1:8">
       <c r="A331" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B331" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C331">
-        <v>-1.3</v>
+        <v>0.2</v>
       </c>
       <c r="D331">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E331">
-        <v>-9.699999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="F331">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G331">
-        <v>-1.6</v>
+        <v>-0.3</v>
       </c>
       <c r="H331">
-        <v>-1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="332" spans="1:8">
       <c r="A332" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B332" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C332">
-        <v>-0</v>
+        <v>1.1</v>
       </c>
       <c r="D332">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E332">
-        <v>-0.3</v>
+        <v>7</v>
       </c>
       <c r="F332">
+        <v>0</v>
+      </c>
+      <c r="G332">
         <v>0.8</v>
       </c>
-      <c r="G332">
-        <v>-0.3</v>
-      </c>
       <c r="H332">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="333" spans="1:8">
       <c r="A333" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B333" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C333">
-        <v>0.3</v>
+        <v>-0</v>
       </c>
       <c r="D333">
         <v>0.1</v>
       </c>
       <c r="E333">
-        <v>2.7</v>
+        <v>-0.2</v>
       </c>
       <c r="F333">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G333">
-        <v>0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="H333">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="334" spans="1:8">
       <c r="A334" s="1" t="s">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="B334" t="s">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="C334">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="D334">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E334">
-        <v>-2.2</v>
+        <v>0.4</v>
       </c>
       <c r="F334">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G334">
-        <v>-0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="H334">
-        <v>-0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="335" spans="1:8">
       <c r="A335" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B335" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C335">
-        <v>-0.2</v>
+        <v>1.4</v>
       </c>
       <c r="D335">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E335">
-        <v>-0.6</v>
+        <v>11.1</v>
       </c>
       <c r="F335">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G335">
-        <v>-0.8</v>
+        <v>1.2</v>
       </c>
       <c r="H335">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="336" spans="1:8">
       <c r="A336" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B336" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C336">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="D336">
         <v>0.1</v>
       </c>
       <c r="E336">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="F336">
         <v>0</v>
       </c>
       <c r="G336">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H336">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="337" spans="1:8">
       <c r="A337" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B337" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C337">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="D337">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="E337">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="F337">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G337">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H337">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="338" spans="1:8">
       <c r="A338" s="1" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B338" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C338">
-        <v>-0</v>
+        <v>0.4</v>
       </c>
       <c r="D338">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E338">
-        <v>-0.3</v>
+        <v>2.6</v>
       </c>
       <c r="F338">
+        <v>0</v>
+      </c>
+      <c r="G338">
+        <v>0.1</v>
+      </c>
+      <c r="H338">
         <v>0.7</v>
-      </c>
-      <c r="G338">
-        <v>-0.3</v>
-      </c>
-      <c r="H338">
-        <v>0.2</v>
       </c>
     </row>
     <row r="339" spans="1:8">
       <c r="A339" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B339" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C339">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D339">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E339">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F339">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G339">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="H339">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="340" spans="1:8">
-      <c r="A340" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B340" t="s">
-        <v>48</v>
-      </c>
-      <c r="C340">
-        <v>0.4</v>
-      </c>
-      <c r="D340">
-        <v>0.1</v>
-      </c>
-      <c r="E340">
-        <v>3.1</v>
-      </c>
-      <c r="F340">
-        <v>0</v>
-      </c>
-      <c r="G340">
-        <v>0.2</v>
-      </c>
-      <c r="H340">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="341" spans="1:8">
-      <c r="A341" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B341" t="s">
-        <v>49</v>
-      </c>
-      <c r="C341">
-        <v>-0.6</v>
-      </c>
-      <c r="D341">
-        <v>0.4</v>
-      </c>
-      <c r="E341">
-        <v>-1.5</v>
-      </c>
-      <c r="F341">
-        <v>0.1</v>
-      </c>
-      <c r="G341">
-        <v>-1.3</v>
-      </c>
-      <c r="H341">
-        <v>0.2</v>
+      <c r="A341" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="342" spans="1:8">
-      <c r="A342" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B342" t="s">
-        <v>125</v>
-      </c>
-      <c r="C342">
-        <v>0.1</v>
-      </c>
-      <c r="D342">
-        <v>0.2</v>
-      </c>
-      <c r="E342">
-        <v>0.4</v>
-      </c>
-      <c r="F342">
-        <v>0.7</v>
-      </c>
-      <c r="G342">
-        <v>-0.2</v>
-      </c>
-      <c r="H342">
-        <v>0.4</v>
+      <c r="B342" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E342" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F342" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G342" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H342" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="343" spans="1:8">
       <c r="A343" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B343" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C343">
+        <v>-1.5</v>
+      </c>
+      <c r="D343">
+        <v>0.2</v>
+      </c>
+      <c r="E343">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="F343">
+        <v>0</v>
+      </c>
+      <c r="G343">
+        <v>-1.8</v>
+      </c>
+      <c r="H343">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8">
+      <c r="A344" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B344" t="s">
+        <v>41</v>
+      </c>
+      <c r="C344">
+        <v>-0.3</v>
+      </c>
+      <c r="D344">
+        <v>0.1</v>
+      </c>
+      <c r="E344">
+        <v>-1.7</v>
+      </c>
+      <c r="F344">
+        <v>0.1</v>
+      </c>
+      <c r="G344">
+        <v>-0.5</v>
+      </c>
+      <c r="H344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8">
+      <c r="A345" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B345" t="s">
+        <v>42</v>
+      </c>
+      <c r="C345">
+        <v>0.4</v>
+      </c>
+      <c r="D345">
+        <v>0.1</v>
+      </c>
+      <c r="E345">
+        <v>3</v>
+      </c>
+      <c r="F345">
+        <v>0</v>
+      </c>
+      <c r="G345">
+        <v>0.1</v>
+      </c>
+      <c r="H345">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8">
+      <c r="A346" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B346" t="s">
+        <v>140</v>
+      </c>
+      <c r="C346">
+        <v>-0.4</v>
+      </c>
+      <c r="D346">
+        <v>0.2</v>
+      </c>
+      <c r="E346">
+        <v>-2</v>
+      </c>
+      <c r="F346">
+        <v>0</v>
+      </c>
+      <c r="G346">
+        <v>-0.8</v>
+      </c>
+      <c r="H346">
         <v>-0</v>
-      </c>
-      <c r="D343">
-        <v>0.2</v>
-      </c>
-      <c r="E343">
-        <v>-0.3</v>
-      </c>
-      <c r="F343">
-        <v>0.8</v>
-      </c>
-      <c r="G343">
-        <v>-0.4</v>
-      </c>
-      <c r="H343">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="345" spans="1:8">
-      <c r="A345" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="346" spans="1:8">
-      <c r="B346" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D346" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E346" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F346" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G346" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H346" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="347" spans="1:8">
       <c r="A347" s="1" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="B347" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="C347">
-        <v>-3.2</v>
+        <v>0.1</v>
       </c>
       <c r="D347">
         <v>0.3</v>
       </c>
       <c r="E347">
-        <v>-9.6</v>
+        <v>0.3</v>
       </c>
       <c r="F347">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G347">
-        <v>-3.9</v>
+        <v>-0.4</v>
       </c>
       <c r="H347">
-        <v>-2.6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="348" spans="1:8">
       <c r="A348" s="1" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="B348" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="C348">
-        <v>-0.6</v>
+        <v>0.1</v>
       </c>
       <c r="D348">
         <v>0.3</v>
       </c>
       <c r="E348">
-        <v>-1.8</v>
+        <v>0.4</v>
       </c>
       <c r="F348">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="G348">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="H348">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="349" spans="1:8">
       <c r="A349" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B349" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C349">
-        <v>-0.9</v>
+        <v>-0.5</v>
       </c>
       <c r="D349">
         <v>0.3</v>
       </c>
       <c r="E349">
-        <v>-2.5</v>
+        <v>-2</v>
       </c>
       <c r="F349">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G349">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="H349">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350" spans="1:8">
       <c r="A350" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B350" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C350">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D350">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E350">
-        <v>-0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="F350">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G350">
-        <v>-1.4</v>
+        <v>-0.7</v>
       </c>
       <c r="H350">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="351" spans="1:8">
       <c r="A351" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B351" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C351">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="D351">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="E351">
-        <v>0.1</v>
+        <v>7.3</v>
       </c>
       <c r="F351">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G351">
-        <v>-1.2</v>
+        <v>0.9</v>
       </c>
       <c r="H351">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="352" spans="1:8">
       <c r="A352" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B352" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C352">
+        <v>0.2</v>
+      </c>
+      <c r="D352">
+        <v>0.1</v>
+      </c>
+      <c r="E352">
+        <v>1.2</v>
+      </c>
+      <c r="F352">
+        <v>0.2</v>
+      </c>
+      <c r="G352">
         <v>-0.1</v>
       </c>
-      <c r="D352">
-        <v>0.3</v>
-      </c>
-      <c r="E352">
-        <v>-0.3</v>
-      </c>
-      <c r="F352">
-        <v>0.7</v>
-      </c>
-      <c r="G352">
-        <v>-0.7</v>
-      </c>
       <c r="H352">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="353" spans="1:8">
       <c r="A353" s="1" t="s">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="B353" t="s">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="C353">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="D353">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E353">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="F353">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G353">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="H353">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="354" spans="1:8">
       <c r="A354" s="1" t="s">
-        <v>140</v>
+        <v>47</v>
       </c>
       <c r="B354" t="s">
-        <v>140</v>
+        <v>47</v>
       </c>
       <c r="C354">
-        <v>-0.4</v>
+        <v>1</v>
       </c>
       <c r="D354">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E354">
-        <v>-1.6</v>
+        <v>7.5</v>
       </c>
       <c r="F354">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G354">
-        <v>-0.9</v>
+        <v>0.7</v>
       </c>
       <c r="H354">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="355" spans="1:8">
       <c r="A355" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B355" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C355">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="D355">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E355">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="F355">
         <v>0</v>
       </c>
       <c r="G355">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="H355">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="356" spans="1:8">
       <c r="A356" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B356" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C356">
-        <v>-0.3</v>
+        <v>0.8</v>
       </c>
       <c r="D356">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E356">
-        <v>-0.9</v>
+        <v>1.3</v>
       </c>
       <c r="F356">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G356">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="H356">
-        <v>0.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357" spans="1:8">
       <c r="A357" s="1" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="B357" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="C357">
+        <v>0.2</v>
+      </c>
+      <c r="D357">
+        <v>0.2</v>
+      </c>
+      <c r="E357">
+        <v>1</v>
+      </c>
+      <c r="F357">
+        <v>0.3</v>
+      </c>
+      <c r="G357">
+        <v>-0.2</v>
+      </c>
+      <c r="H357">
         <v>0.5</v>
-      </c>
-      <c r="D357">
-        <v>0.8</v>
-      </c>
-      <c r="E357">
-        <v>0.6</v>
-      </c>
-      <c r="F357">
-        <v>0.6</v>
-      </c>
-      <c r="G357">
-        <v>-1.1</v>
-      </c>
-      <c r="H357">
-        <v>2.1</v>
       </c>
     </row>
     <row r="358" spans="1:8">
       <c r="A358" s="1" t="s">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="B358" t="s">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="C358">
-        <v>-0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D358">
+        <v>0.2</v>
+      </c>
+      <c r="E358">
+        <v>1.9</v>
+      </c>
+      <c r="F358">
+        <v>0.1</v>
+      </c>
+      <c r="G358">
+        <v>-0</v>
+      </c>
+      <c r="H358">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8">
+      <c r="A360" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8">
+      <c r="B361" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C361" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E361" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F361" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G361" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H361" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8">
+      <c r="A362" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B362" t="s">
+        <v>40</v>
+      </c>
+      <c r="C362">
+        <v>-3.3</v>
+      </c>
+      <c r="D362">
         <v>0.4</v>
       </c>
-      <c r="E358">
-        <v>-1.2</v>
-      </c>
-      <c r="F358">
-        <v>0.2</v>
-      </c>
-      <c r="G358">
-        <v>-1.3</v>
-      </c>
-      <c r="H358">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="359" spans="1:8">
-      <c r="A359" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B359" t="s">
-        <v>50</v>
-      </c>
-      <c r="C359">
-        <v>-0.4</v>
-      </c>
-      <c r="D359">
-        <v>0.4</v>
-      </c>
-      <c r="E359">
-        <v>-1.1</v>
-      </c>
-      <c r="F359">
-        <v>0.3</v>
-      </c>
-      <c r="G359">
-        <v>-1.3</v>
-      </c>
-      <c r="H359">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="361" spans="1:8">
-      <c r="A361" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="362" spans="1:8">
-      <c r="C362" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D362" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E362" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F362" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G362" s="1" t="s">
-        <v>39</v>
+      <c r="E362">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="F362">
+        <v>0</v>
+      </c>
+      <c r="G362">
+        <v>-4</v>
+      </c>
+      <c r="H362">
+        <v>-2.6</v>
       </c>
     </row>
     <row r="363" spans="1:8">
       <c r="A363" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B363" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="B363" t="s">
+        <v>41</v>
       </c>
       <c r="C363">
-        <v>0</v>
-      </c>
-      <c r="D363" t="s">
-        <v>57</v>
+        <v>-1.1</v>
+      </c>
+      <c r="D363">
+        <v>0.4</v>
       </c>
       <c r="E363">
-        <v>0</v>
+        <v>-2.8</v>
       </c>
       <c r="F363">
         <v>0</v>
       </c>
       <c r="G363">
-        <v>0.1</v>
+        <v>-1.9</v>
+      </c>
+      <c r="H363">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="364" spans="1:8">
-      <c r="A364" s="1"/>
-      <c r="B364" s="1" t="s">
+      <c r="A364" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="B364" t="s">
+        <v>42</v>
+      </c>
       <c r="C364">
-        <v>0</v>
-      </c>
-      <c r="D364" t="s">
-        <v>57</v>
+        <v>-0.8</v>
+      </c>
+      <c r="D364">
+        <v>0.4</v>
       </c>
       <c r="E364">
-        <v>0.4</v>
+        <v>-2.4</v>
       </c>
       <c r="F364">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G364">
-        <v>0.8</v>
+        <v>-1.5</v>
+      </c>
+      <c r="H364">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="365" spans="1:8">
-      <c r="A365" s="1"/>
-      <c r="B365" s="1" t="s">
-        <v>41</v>
+      <c r="A365" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B365" t="s">
+        <v>140</v>
       </c>
       <c r="C365">
-        <v>0.1</v>
+        <v>-0.5</v>
+      </c>
+      <c r="D365">
+        <v>0.5</v>
       </c>
       <c r="E365">
-        <v>0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="F365">
         <v>0.3</v>
       </c>
       <c r="G365">
-        <v>1.1</v>
+        <v>-1.5</v>
+      </c>
+      <c r="H365">
+        <v>0.4</v>
       </c>
     </row>
     <row r="366" spans="1:8">
-      <c r="A366" s="1"/>
-      <c r="B366" s="1" t="s">
-        <v>140</v>
+      <c r="A366" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B366" t="s">
+        <v>141</v>
       </c>
       <c r="C366">
-        <v>0.1</v>
+        <v>-0.6</v>
+      </c>
+      <c r="D366">
+        <v>0.7</v>
       </c>
       <c r="E366">
-        <v>0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="F366">
         <v>0.4</v>
       </c>
       <c r="G366">
+        <v>-2.1</v>
+      </c>
+      <c r="H366">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8">
+      <c r="A367" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B367" t="s">
+        <v>142</v>
+      </c>
+      <c r="C367">
+        <v>0.3</v>
+      </c>
+      <c r="D367">
+        <v>0.6</v>
+      </c>
+      <c r="E367">
+        <v>0.5</v>
+      </c>
+      <c r="F367">
+        <v>0.6</v>
+      </c>
+      <c r="G367">
+        <v>-0.9</v>
+      </c>
+      <c r="H367">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8">
+      <c r="A368" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B368" t="s">
+        <v>43</v>
+      </c>
+      <c r="C368">
+        <v>-0.4</v>
+      </c>
+      <c r="D368">
+        <v>0.6</v>
+      </c>
+      <c r="E368">
+        <v>-0.7</v>
+      </c>
+      <c r="F368">
+        <v>0.5</v>
+      </c>
+      <c r="G368">
+        <v>-1.6</v>
+      </c>
+      <c r="H368">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8">
+      <c r="A369" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B369" t="s">
+        <v>44</v>
+      </c>
+      <c r="C369">
+        <v>0.1</v>
+      </c>
+      <c r="D369">
+        <v>0.6</v>
+      </c>
+      <c r="E369">
+        <v>0.2</v>
+      </c>
+      <c r="F369">
+        <v>0.9</v>
+      </c>
+      <c r="G369">
+        <v>-1.1</v>
+      </c>
+      <c r="H369">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8">
+      <c r="A370" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B370" t="s">
+        <v>45</v>
+      </c>
+      <c r="C370">
+        <v>0.5</v>
+      </c>
+      <c r="D370">
+        <v>0.3</v>
+      </c>
+      <c r="E370">
+        <v>1.5</v>
+      </c>
+      <c r="F370">
+        <v>0.1</v>
+      </c>
+      <c r="G370">
+        <v>-0.2</v>
+      </c>
+      <c r="H370">
         <v>1.1</v>
       </c>
     </row>
-    <row r="367" spans="1:8">
-      <c r="A367" s="1"/>
-      <c r="B367" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C367">
-        <v>0.7</v>
-      </c>
-      <c r="E367">
+    <row r="371" spans="1:8">
+      <c r="A371" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B371" t="s">
+        <v>46</v>
+      </c>
+      <c r="C371">
+        <v>0.8</v>
+      </c>
+      <c r="D371">
+        <v>0.2</v>
+      </c>
+      <c r="E371">
+        <v>3.2</v>
+      </c>
+      <c r="F371">
+        <v>0</v>
+      </c>
+      <c r="G371">
+        <v>0.3</v>
+      </c>
+      <c r="H371">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8">
+      <c r="A372" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B372" t="s">
+        <v>143</v>
+      </c>
+      <c r="C372">
+        <v>-0.2</v>
+      </c>
+      <c r="D372">
+        <v>0.3</v>
+      </c>
+      <c r="E372">
+        <v>-0.9</v>
+      </c>
+      <c r="F372">
+        <v>0.4</v>
+      </c>
+      <c r="G372">
+        <v>-0.7</v>
+      </c>
+      <c r="H372">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8">
+      <c r="A373" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B373" t="s">
+        <v>47</v>
+      </c>
+      <c r="C373">
+        <v>2.1</v>
+      </c>
+      <c r="D373">
+        <v>0.3</v>
+      </c>
+      <c r="E373">
+        <v>6.8</v>
+      </c>
+      <c r="F373">
+        <v>0</v>
+      </c>
+      <c r="G373">
+        <v>1.5</v>
+      </c>
+      <c r="H373">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8">
+      <c r="A374" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B374" t="s">
+        <v>48</v>
+      </c>
+      <c r="C374">
+        <v>-0.2</v>
+      </c>
+      <c r="D374">
+        <v>0.3</v>
+      </c>
+      <c r="E374">
+        <v>-0.6</v>
+      </c>
+      <c r="F374">
+        <v>0.6</v>
+      </c>
+      <c r="G374">
+        <v>-0.9</v>
+      </c>
+      <c r="H374">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8">
+      <c r="A375" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B375" t="s">
+        <v>49</v>
+      </c>
+      <c r="C375">
+        <v>2</v>
+      </c>
+      <c r="D375">
+        <v>1</v>
+      </c>
+      <c r="E375">
+        <v>2.1</v>
+      </c>
+      <c r="F375">
+        <v>0</v>
+      </c>
+      <c r="G375">
+        <v>0.1</v>
+      </c>
+      <c r="H375">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8">
+      <c r="A376" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B376" t="s">
+        <v>125</v>
+      </c>
+      <c r="C376">
+        <v>-0.3</v>
+      </c>
+      <c r="D376">
+        <v>0.4</v>
+      </c>
+      <c r="E376">
+        <v>-0.6</v>
+      </c>
+      <c r="F376">
+        <v>0.6</v>
+      </c>
+      <c r="G376">
+        <v>-1.1</v>
+      </c>
+      <c r="H376">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8">
+      <c r="A377" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B377" t="s">
+        <v>50</v>
+      </c>
+      <c r="C377">
+        <v>0.1</v>
+      </c>
+      <c r="D377">
+        <v>0.4</v>
+      </c>
+      <c r="E377">
+        <v>0.2</v>
+      </c>
+      <c r="F377">
         <v>0.9</v>
       </c>
-      <c r="F367">
-        <v>0.5</v>
-      </c>
-      <c r="G367">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="368" spans="1:8">
-      <c r="A368" s="1"/>
-      <c r="B368" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C368">
-        <v>0</v>
-      </c>
-      <c r="D368" t="s">
-        <v>57</v>
-      </c>
-      <c r="E368">
-        <v>2</v>
-      </c>
-      <c r="F368">
-        <v>1.3</v>
-      </c>
-      <c r="G368">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="369" spans="1:7">
-      <c r="A369" s="1"/>
-      <c r="B369" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C369">
-        <v>0.3</v>
-      </c>
-      <c r="E369">
-        <v>0.6</v>
-      </c>
-      <c r="F369">
-        <v>0.3</v>
-      </c>
-      <c r="G369">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="370" spans="1:7">
-      <c r="A370" s="1"/>
-      <c r="B370" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C370">
-        <v>0.2</v>
-      </c>
-      <c r="E370">
-        <v>0.6</v>
-      </c>
-      <c r="F370">
-        <v>0.3</v>
-      </c>
-      <c r="G370">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="371" spans="1:7">
-      <c r="A371" s="1"/>
-      <c r="B371" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C371">
-        <v>0.4</v>
-      </c>
-      <c r="E371">
-        <v>0.7</v>
-      </c>
-      <c r="F371">
-        <v>0.4</v>
-      </c>
-      <c r="G371">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="372" spans="1:7">
-      <c r="A372" s="1"/>
-      <c r="B372" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C372">
-        <v>0.6</v>
-      </c>
-      <c r="E372">
-        <v>1.6</v>
-      </c>
-      <c r="F372">
-        <v>0.3</v>
-      </c>
-      <c r="G372">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="373" spans="1:7">
-      <c r="A373" s="1"/>
-      <c r="B373" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C373">
-        <v>0</v>
-      </c>
-      <c r="D373" t="s">
-        <v>57</v>
-      </c>
-      <c r="E373">
-        <v>3.5</v>
-      </c>
-      <c r="F373">
-        <v>2</v>
-      </c>
-      <c r="G373">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="374" spans="1:7">
-      <c r="A374" s="1"/>
-      <c r="B374" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C374">
+      <c r="G377">
+        <v>-0.8</v>
+      </c>
+      <c r="H377">
         <v>1</v>
       </c>
-      <c r="E374">
-        <v>1</v>
-      </c>
-      <c r="F374">
-        <v>0.3</v>
-      </c>
-      <c r="G374">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="375" spans="1:7">
-      <c r="A375" s="1"/>
-      <c r="B375" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C375">
-        <v>0.5</v>
-      </c>
-      <c r="E375">
-        <v>0.7</v>
-      </c>
-      <c r="F375">
-        <v>0.3</v>
-      </c>
-      <c r="G375">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="376" spans="1:7">
-      <c r="A376" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B376" s="1" t="s">
+    </row>
+    <row r="379" spans="1:8">
+      <c r="A379" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8">
+      <c r="C380" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D380" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E380" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F380" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G380" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8">
+      <c r="A381" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B381" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C376">
-        <v>0</v>
-      </c>
-      <c r="D376" t="s">
-        <v>57</v>
-      </c>
-      <c r="E376">
-        <v>1.3</v>
-      </c>
-      <c r="F376">
-        <v>1</v>
-      </c>
-      <c r="G376">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="377" spans="1:7">
-      <c r="A377" s="1"/>
-      <c r="B377" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C377">
-        <v>0.4</v>
-      </c>
-      <c r="E377">
-        <v>0.9</v>
-      </c>
-      <c r="F377">
-        <v>0.8</v>
-      </c>
-      <c r="G377">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="378" spans="1:7">
-      <c r="A378" s="1"/>
-      <c r="B378" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C378">
-        <v>0.1</v>
-      </c>
-      <c r="E378">
-        <v>1.2</v>
-      </c>
-      <c r="F378">
-        <v>1</v>
-      </c>
-      <c r="G378">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="379" spans="1:7">
-      <c r="A379" s="1"/>
-      <c r="B379" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C379">
-        <v>0</v>
-      </c>
-      <c r="D379" t="s">
-        <v>57</v>
-      </c>
-      <c r="E379">
-        <v>0.8</v>
-      </c>
-      <c r="F379">
-        <v>0.6</v>
-      </c>
-      <c r="G379">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="380" spans="1:7">
-      <c r="A380" s="1"/>
-      <c r="B380" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C380">
-        <v>0</v>
-      </c>
-      <c r="D380" t="s">
-        <v>57</v>
-      </c>
-      <c r="E380">
-        <v>0.6</v>
-      </c>
-      <c r="F380">
-        <v>0.4</v>
-      </c>
-      <c r="G380">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="381" spans="1:7">
-      <c r="A381" s="1"/>
-      <c r="B381" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="C381">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E381">
         <v>0.9</v>
@@ -8250,49 +8380,46 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" spans="1:8">
       <c r="A382" s="1"/>
       <c r="B382" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C382">
-        <v>0</v>
-      </c>
-      <c r="D382" t="s">
-        <v>57</v>
+        <v>0.3</v>
       </c>
       <c r="E382">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="F382">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="G382">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="383" spans="1:7">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8">
       <c r="A383" s="1"/>
       <c r="B383" s="1" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C383">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E383">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F383">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G383">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="384" spans="1:7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8">
       <c r="A384" s="1"/>
       <c r="B384" s="1" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="C384">
         <v>0.6</v>
@@ -8301,117 +8428,112 @@
         <v>0.9</v>
       </c>
       <c r="F384">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G384">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="385" spans="1:7">
       <c r="A385" s="1"/>
       <c r="B385" s="1" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="C385">
-        <v>0</v>
-      </c>
-      <c r="D385" t="s">
-        <v>57</v>
+        <v>0.4</v>
       </c>
       <c r="E385">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="F385">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="G385">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="386" spans="1:7">
       <c r="A386" s="1"/>
       <c r="B386" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C386">
-        <v>0</v>
-      </c>
-      <c r="D386" t="s">
-        <v>57</v>
+        <v>0.1</v>
       </c>
       <c r="E386">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="F386">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="G386">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="387" spans="1:7">
       <c r="A387" s="1"/>
       <c r="B387" s="1" t="s">
-        <v>44</v>
+        <v>143</v>
       </c>
       <c r="C387">
-        <v>0.7</v>
+        <v>0</v>
+      </c>
+      <c r="D387" t="s">
+        <v>57</v>
       </c>
       <c r="E387">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="F387">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G387">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="388" spans="1:7">
       <c r="A388" s="1"/>
       <c r="B388" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C388">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="D388" t="s">
+        <v>57</v>
       </c>
       <c r="E388">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="F388">
+        <v>1.3</v>
+      </c>
+      <c r="G388">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7">
+      <c r="A389" s="1"/>
+      <c r="B389" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C389">
+        <v>0.3</v>
+      </c>
+      <c r="E389">
+        <v>1.1</v>
+      </c>
+      <c r="F389">
         <v>0.9</v>
       </c>
-      <c r="G388">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="389" spans="1:7">
-      <c r="A389" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B389" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C389">
-        <v>0</v>
-      </c>
-      <c r="D389" t="s">
-        <v>57</v>
-      </c>
-      <c r="E389">
-        <v>0.3</v>
-      </c>
-      <c r="F389">
-        <v>0.2</v>
-      </c>
       <c r="G389">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="390" spans="1:7">
       <c r="A390" s="1"/>
       <c r="B390" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C390">
         <v>0</v>
@@ -8420,55 +8542,55 @@
         <v>57</v>
       </c>
       <c r="E390">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F390">
         <v>1.1</v>
       </c>
       <c r="G390">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="391" spans="1:7">
       <c r="A391" s="1"/>
       <c r="B391" s="1" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="C391">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E391">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F391">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G391">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="392" spans="1:7">
       <c r="A392" s="1"/>
       <c r="B392" s="1" t="s">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="C392">
         <v>0.7</v>
       </c>
       <c r="E392">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F392">
         <v>0.8</v>
       </c>
       <c r="G392">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="393" spans="1:7">
       <c r="A393" s="1"/>
       <c r="B393" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C393">
         <v>0</v>
@@ -8477,73 +8599,78 @@
         <v>57</v>
       </c>
       <c r="E393">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="F393">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G393">
-        <v>2.5</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="394" spans="1:7">
       <c r="A394" s="1"/>
       <c r="B394" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C394">
-        <v>0.6</v>
+        <v>0</v>
+      </c>
+      <c r="D394" t="s">
+        <v>57</v>
       </c>
       <c r="E394">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="F394">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="G394">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="395" spans="1:7">
       <c r="A395" s="1"/>
       <c r="B395" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C395">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E395">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F395">
         <v>0.7</v>
       </c>
       <c r="G395">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="396" spans="1:7">
       <c r="A396" s="1"/>
       <c r="B396" s="1" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="C396">
         <v>0.7</v>
       </c>
       <c r="E396">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="F396">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G396">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="397" spans="1:7">
-      <c r="A397" s="1"/>
+      <c r="A397" s="1" t="s">
+        <v>156</v>
+      </c>
       <c r="B397" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C397">
         <v>0</v>
@@ -8552,279 +8679,298 @@
         <v>57</v>
       </c>
       <c r="E397">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="F397">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="G397">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="398" spans="1:7">
       <c r="A398" s="1"/>
       <c r="B398" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C398">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="D398" t="s">
+        <v>57</v>
       </c>
       <c r="E398">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="F398">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="G398">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="399" spans="1:7">
       <c r="A399" s="1"/>
       <c r="B399" s="1" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
       <c r="C399">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E399">
+        <v>0.8</v>
+      </c>
+      <c r="F399">
+        <v>0.6</v>
+      </c>
+      <c r="G399">
         <v>1.1</v>
-      </c>
-      <c r="F399">
-        <v>0.9</v>
-      </c>
-      <c r="G399">
-        <v>1.4</v>
       </c>
     </row>
     <row r="400" spans="1:7">
       <c r="A400" s="1"/>
       <c r="B400" s="1" t="s">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="C400">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E400">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="F400">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G400">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="401" spans="1:7">
       <c r="A401" s="1"/>
       <c r="B401" s="1" t="s">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="C401">
-        <v>0</v>
-      </c>
-      <c r="D401" t="s">
-        <v>57</v>
+        <v>0.8</v>
       </c>
       <c r="E401">
+        <v>0.9</v>
+      </c>
+      <c r="F401">
+        <v>0.5</v>
+      </c>
+      <c r="G401">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7">
+      <c r="A402" s="1"/>
+      <c r="B402" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C402">
+        <v>0</v>
+      </c>
+      <c r="D402" t="s">
+        <v>57</v>
+      </c>
+      <c r="E402">
         <v>0.6</v>
       </c>
-      <c r="F401">
-        <v>0.4</v>
-      </c>
-      <c r="G401">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="402" spans="1:7">
-      <c r="A402" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B402" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C402">
-        <v>0</v>
-      </c>
-      <c r="D402" t="s">
-        <v>57</v>
-      </c>
-      <c r="E402">
-        <v>0.2</v>
-      </c>
       <c r="F402">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G402">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="403" spans="1:7">
       <c r="A403" s="1"/>
       <c r="B403" s="1" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="C403">
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="D403" t="s">
+        <v>57</v>
       </c>
       <c r="E403">
+        <v>1.3</v>
+      </c>
+      <c r="F403">
         <v>1.1</v>
       </c>
-      <c r="F403">
-        <v>0.9</v>
-      </c>
       <c r="G403">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="404" spans="1:7">
       <c r="A404" s="1"/>
       <c r="B404" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C404">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="D404" t="s">
+        <v>57</v>
       </c>
       <c r="E404">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="F404">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="G404">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="405" spans="1:7">
       <c r="A405" s="1"/>
       <c r="B405" s="1" t="s">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="C405">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="D405" t="s">
+        <v>57</v>
       </c>
       <c r="E405">
+        <v>1.4</v>
+      </c>
+      <c r="F405">
         <v>1.1</v>
       </c>
-      <c r="F405">
-        <v>0.9</v>
-      </c>
       <c r="G405">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="406" spans="1:7">
       <c r="A406" s="1"/>
       <c r="B406" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C406">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="D406" t="s">
+        <v>57</v>
       </c>
       <c r="E406">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="F406">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="G406">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="407" spans="1:7">
       <c r="A407" s="1"/>
       <c r="B407" s="1" t="s">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="C407">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="E407">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F407">
         <v>0.8</v>
       </c>
       <c r="G407">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="408" spans="1:7">
       <c r="A408" s="1"/>
       <c r="B408" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C408">
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="D408" t="s">
+        <v>57</v>
       </c>
       <c r="E408">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="F408">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="G408">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="409" spans="1:7">
       <c r="A409" s="1"/>
       <c r="B409" s="1" t="s">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="C409">
-        <v>0.3</v>
+        <v>0</v>
+      </c>
+      <c r="D409" t="s">
+        <v>57</v>
       </c>
       <c r="E409">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="F409">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="G409">
-        <v>1.5</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="410" spans="1:7">
       <c r="A410" s="1"/>
       <c r="B410" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C410">
-        <v>0.3</v>
+        <v>0</v>
+      </c>
+      <c r="D410" t="s">
+        <v>57</v>
       </c>
       <c r="E410">
-        <v>1.2</v>
+        <v>8.4</v>
       </c>
       <c r="F410">
-        <v>0.9</v>
+        <v>6.7</v>
       </c>
       <c r="G410">
-        <v>1.5</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="411" spans="1:7">
       <c r="A411" s="1"/>
       <c r="B411" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C411">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E411">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="F411">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G411">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="412" spans="1:7">
       <c r="A412" s="1"/>
       <c r="B412" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C412">
         <v>0</v>
@@ -8833,138 +8979,132 @@
         <v>57</v>
       </c>
       <c r="E412">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="F412">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="G412">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="413" spans="1:7">
-      <c r="A413" s="1"/>
+      <c r="A413" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="B413" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C413">
-        <v>0.3</v>
+        <v>0</v>
+      </c>
+      <c r="D413" t="s">
+        <v>57</v>
       </c>
       <c r="E413">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="F413">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="G413">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="414" spans="1:7">
       <c r="A414" s="1"/>
       <c r="B414" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C414">
+        <v>0.1</v>
+      </c>
+      <c r="E414">
+        <v>1.2</v>
+      </c>
+      <c r="F414">
+        <v>1</v>
+      </c>
+      <c r="G414">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7">
+      <c r="A415" s="1"/>
+      <c r="B415" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C415">
+        <v>0.4</v>
+      </c>
+      <c r="E415">
+        <v>0.9</v>
+      </c>
+      <c r="F415">
         <v>0.6</v>
       </c>
-      <c r="E414">
-        <v>1.1</v>
-      </c>
-      <c r="F414">
-        <v>0.8</v>
-      </c>
-      <c r="G414">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="415" spans="1:7">
-      <c r="A415" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B415" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C415">
-        <v>0</v>
-      </c>
-      <c r="D415" t="s">
-        <v>57</v>
-      </c>
-      <c r="E415">
-        <v>0.2</v>
-      </c>
-      <c r="F415">
-        <v>0.2</v>
-      </c>
       <c r="G415">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="416" spans="1:7">
       <c r="A416" s="1"/>
       <c r="B416" s="1" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="C416">
-        <v>0</v>
-      </c>
-      <c r="D416" t="s">
-        <v>57</v>
+        <v>0.6</v>
       </c>
       <c r="E416">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F416">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="G416">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="417" spans="1:7">
       <c r="A417" s="1"/>
       <c r="B417" s="1" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="C417">
-        <v>0</v>
-      </c>
-      <c r="D417" t="s">
-        <v>57</v>
+        <v>0.1</v>
       </c>
       <c r="E417">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F417">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G417">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="418" spans="1:7">
       <c r="A418" s="1"/>
       <c r="B418" s="1" t="s">
-        <v>140</v>
+        <v>41</v>
       </c>
       <c r="C418">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E418">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="F418">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G418">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="419" spans="1:7">
       <c r="A419" s="1"/>
       <c r="B419" s="1" t="s">
-        <v>45</v>
+        <v>143</v>
       </c>
       <c r="C419">
         <v>0</v>
@@ -8973,19 +9113,19 @@
         <v>57</v>
       </c>
       <c r="E419">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="F419">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G419">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="420" spans="1:7">
       <c r="A420" s="1"/>
       <c r="B420" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C420">
         <v>0</v>
@@ -8994,94 +9134,94 @@
         <v>57</v>
       </c>
       <c r="E420">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="F420">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G420">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="421" spans="1:7">
       <c r="A421" s="1"/>
       <c r="B421" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C421">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E421">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F421">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G421">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="422" spans="1:7">
       <c r="A422" s="1"/>
       <c r="B422" s="1" t="s">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="C422">
-        <v>0.9</v>
+        <v>0</v>
+      </c>
+      <c r="D422" t="s">
+        <v>57</v>
       </c>
       <c r="E422">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="F422">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="G422">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="423" spans="1:7">
       <c r="A423" s="1"/>
       <c r="B423" s="1" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="C423">
-        <v>0</v>
-      </c>
-      <c r="D423" t="s">
-        <v>57</v>
+        <v>0.1</v>
       </c>
       <c r="E423">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="F423">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="G423">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="424" spans="1:7">
       <c r="A424" s="1"/>
       <c r="B424" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C424">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E424">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F424">
         <v>0.9</v>
       </c>
       <c r="G424">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="425" spans="1:7">
       <c r="A425" s="1"/>
       <c r="B425" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C425">
         <v>0</v>
@@ -9090,111 +9230,114 @@
         <v>57</v>
       </c>
       <c r="E425">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="F425">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="G425">
-        <v>4.3</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="426" spans="1:7">
       <c r="A426" s="1"/>
       <c r="B426" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C426">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="D426" t="s">
+        <v>57</v>
       </c>
       <c r="E426">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="F426">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="G426">
-        <v>1.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="427" spans="1:7">
       <c r="A427" s="1"/>
       <c r="B427" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C427">
+        <v>0.2</v>
+      </c>
+      <c r="E427">
+        <v>1.4</v>
+      </c>
+      <c r="F427">
+        <v>0.8</v>
+      </c>
+      <c r="G427">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7">
+      <c r="A428" s="1"/>
+      <c r="B428" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C427">
-        <v>0</v>
-      </c>
-      <c r="D427" t="s">
-        <v>57</v>
-      </c>
-      <c r="E427">
-        <v>0.5</v>
-      </c>
-      <c r="F427">
-        <v>0.4</v>
-      </c>
-      <c r="G427">
+      <c r="C428">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="428" spans="1:7">
-      <c r="A428" s="1" t="s">
+      <c r="E428">
+        <v>1.1</v>
+      </c>
+      <c r="F428">
+        <v>0.7</v>
+      </c>
+      <c r="G428">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7">
+      <c r="A429" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B428" s="1" t="s">
+      <c r="B429" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C428">
-        <v>0</v>
-      </c>
-      <c r="D428" t="s">
-        <v>57</v>
-      </c>
-      <c r="E428">
+      <c r="C429">
+        <v>0</v>
+      </c>
+      <c r="D429" t="s">
+        <v>57</v>
+      </c>
+      <c r="E429">
+        <v>0.2</v>
+      </c>
+      <c r="F429">
+        <v>0.2</v>
+      </c>
+      <c r="G429">
         <v>0.3</v>
-      </c>
-      <c r="F428">
-        <v>0.2</v>
-      </c>
-      <c r="G428">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="429" spans="1:7">
-      <c r="A429" s="1"/>
-      <c r="B429" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C429">
-        <v>0.1</v>
-      </c>
-      <c r="E429">
-        <v>1.2</v>
-      </c>
-      <c r="F429">
-        <v>1</v>
-      </c>
-      <c r="G429">
-        <v>1.5</v>
       </c>
     </row>
     <row r="430" spans="1:7">
       <c r="A430" s="1"/>
       <c r="B430" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C430">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="D430" t="s">
+        <v>57</v>
       </c>
       <c r="E430">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="F430">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G430">
-        <v>1</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="431" spans="1:7">
@@ -9203,61 +9346,58 @@
         <v>140</v>
       </c>
       <c r="C431">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E431">
         <v>0.9</v>
       </c>
       <c r="F431">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G431">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="432" spans="1:7">
       <c r="A432" s="1"/>
       <c r="B432" s="1" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="C432">
-        <v>0</v>
-      </c>
-      <c r="D432" t="s">
-        <v>57</v>
+        <v>0.4</v>
       </c>
       <c r="E432">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="F432">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="G432">
-        <v>2.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433" spans="1:7">
       <c r="A433" s="1"/>
       <c r="B433" s="1" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="C433">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="E433">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F433">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G433">
-        <v>1</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="434" spans="1:7">
       <c r="A434" s="1"/>
       <c r="B434" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C434">
         <v>0</v>
@@ -9266,40 +9406,37 @@
         <v>57</v>
       </c>
       <c r="E434">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F434">
         <v>0.5</v>
       </c>
       <c r="G434">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="435" spans="1:7">
       <c r="A435" s="1"/>
       <c r="B435" s="1" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="C435">
-        <v>0</v>
-      </c>
-      <c r="D435" t="s">
-        <v>57</v>
+        <v>0.7</v>
       </c>
       <c r="E435">
+        <v>1</v>
+      </c>
+      <c r="F435">
+        <v>0.8</v>
+      </c>
+      <c r="G435">
         <v>1.3</v>
-      </c>
-      <c r="F435">
-        <v>1</v>
-      </c>
-      <c r="G435">
-        <v>1.8</v>
       </c>
     </row>
     <row r="436" spans="1:7">
       <c r="A436" s="1"/>
       <c r="B436" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C436">
         <v>0</v>
@@ -9308,91 +9445,788 @@
         <v>57</v>
       </c>
       <c r="E436">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="F436">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G436">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="437" spans="1:7">
       <c r="A437" s="1"/>
       <c r="B437" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C437">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E437">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F437">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G437">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="438" spans="1:7">
       <c r="A438" s="1"/>
       <c r="B438" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C438">
-        <v>0</v>
-      </c>
-      <c r="D438" t="s">
-        <v>57</v>
+        <v>0.4</v>
       </c>
       <c r="E438">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="F438">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="G438">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="439" spans="1:7">
       <c r="A439" s="1"/>
       <c r="B439" s="1" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="C439">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="D439" t="s">
+        <v>57</v>
       </c>
       <c r="E439">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="F439">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="G439">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="440" spans="1:7">
       <c r="A440" s="1"/>
       <c r="B440" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C440">
+        <v>0</v>
+      </c>
+      <c r="D440" t="s">
+        <v>57</v>
+      </c>
+      <c r="E440">
+        <v>3.1</v>
+      </c>
+      <c r="F440">
+        <v>2.3</v>
+      </c>
+      <c r="G440">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7">
+      <c r="A441" s="1"/>
+      <c r="B441" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C441">
+        <v>0</v>
+      </c>
+      <c r="D441" t="s">
+        <v>57</v>
+      </c>
+      <c r="E441">
+        <v>3.3</v>
+      </c>
+      <c r="F441">
+        <v>1.1</v>
+      </c>
+      <c r="G441">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7">
+      <c r="A442" s="1"/>
+      <c r="B442" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C442">
+        <v>0</v>
+      </c>
+      <c r="D442" t="s">
+        <v>57</v>
+      </c>
+      <c r="E442">
+        <v>4.1</v>
+      </c>
+      <c r="F442">
+        <v>3.2</v>
+      </c>
+      <c r="G442">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7">
+      <c r="A443" s="1"/>
+      <c r="B443" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C443">
+        <v>0.4</v>
+      </c>
+      <c r="E443">
+        <v>1.3</v>
+      </c>
+      <c r="F443">
+        <v>0.7</v>
+      </c>
+      <c r="G443">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7">
+      <c r="A444" s="1"/>
+      <c r="B444" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C440">
-        <v>0</v>
-      </c>
-      <c r="D440" t="s">
-        <v>57</v>
-      </c>
-      <c r="E440">
+      <c r="C444">
+        <v>0</v>
+      </c>
+      <c r="D444" t="s">
+        <v>57</v>
+      </c>
+      <c r="E444">
+        <v>0.4</v>
+      </c>
+      <c r="F444">
+        <v>0.3</v>
+      </c>
+      <c r="G444">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7">
+      <c r="A445" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C445">
+        <v>0</v>
+      </c>
+      <c r="D445" t="s">
+        <v>57</v>
+      </c>
+      <c r="E445">
+        <v>0.2</v>
+      </c>
+      <c r="F445">
+        <v>0.2</v>
+      </c>
+      <c r="G445">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7">
+      <c r="A446" s="1"/>
+      <c r="B446" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C446">
+        <v>0</v>
+      </c>
+      <c r="D446" t="s">
+        <v>57</v>
+      </c>
+      <c r="E446">
+        <v>1.5</v>
+      </c>
+      <c r="F446">
+        <v>1.1</v>
+      </c>
+      <c r="G446">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7">
+      <c r="A447" s="1"/>
+      <c r="B447" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C447">
+        <v>0</v>
+      </c>
+      <c r="D447" t="s">
+        <v>57</v>
+      </c>
+      <c r="E447">
+        <v>0.7</v>
+      </c>
+      <c r="F447">
+        <v>0.4</v>
+      </c>
+      <c r="G447">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7">
+      <c r="A448" s="1"/>
+      <c r="B448" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C448">
+        <v>0.8</v>
+      </c>
+      <c r="E448">
+        <v>1.1</v>
+      </c>
+      <c r="F448">
+        <v>0.7</v>
+      </c>
+      <c r="G448">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7">
+      <c r="A449" s="1"/>
+      <c r="B449" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C449">
+        <v>0.7</v>
+      </c>
+      <c r="E449">
+        <v>1.1</v>
+      </c>
+      <c r="F449">
+        <v>0.6</v>
+      </c>
+      <c r="G449">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7">
+      <c r="A450" s="1"/>
+      <c r="B450" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C450">
+        <v>0.1</v>
+      </c>
+      <c r="E450">
+        <v>0.8</v>
+      </c>
+      <c r="F450">
+        <v>0.6</v>
+      </c>
+      <c r="G450">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7">
+      <c r="A451" s="1"/>
+      <c r="B451" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C451">
+        <v>0.3</v>
+      </c>
+      <c r="E451">
+        <v>1.2</v>
+      </c>
+      <c r="F451">
+        <v>0.9</v>
+      </c>
+      <c r="G451">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7">
+      <c r="A452" s="1"/>
+      <c r="B452" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C452">
+        <v>0</v>
+      </c>
+      <c r="D452" t="s">
+        <v>57</v>
+      </c>
+      <c r="E452">
+        <v>3.4</v>
+      </c>
+      <c r="F452">
+        <v>2.5</v>
+      </c>
+      <c r="G452">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7">
+      <c r="A453" s="1"/>
+      <c r="B453" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C453">
+        <v>0.2</v>
+      </c>
+      <c r="E453">
+        <v>1.2</v>
+      </c>
+      <c r="F453">
+        <v>0.9</v>
+      </c>
+      <c r="G453">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7">
+      <c r="A454" s="1"/>
+      <c r="B454" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C454">
+        <v>0.1</v>
+      </c>
+      <c r="E454">
+        <v>1.6</v>
+      </c>
+      <c r="F454">
+        <v>1</v>
+      </c>
+      <c r="G454">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7">
+      <c r="A455" s="1"/>
+      <c r="B455" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C455">
+        <v>0.3</v>
+      </c>
+      <c r="E455">
+        <v>1.2</v>
+      </c>
+      <c r="F455">
+        <v>0.8</v>
+      </c>
+      <c r="G455">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7">
+      <c r="A456" s="1"/>
+      <c r="B456" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C456">
+        <v>0</v>
+      </c>
+      <c r="D456" t="s">
+        <v>57</v>
+      </c>
+      <c r="E456">
+        <v>1.7</v>
+      </c>
+      <c r="F456">
+        <v>1.2</v>
+      </c>
+      <c r="G456">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7">
+      <c r="A457" s="1"/>
+      <c r="B457" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C457">
+        <v>0.2</v>
+      </c>
+      <c r="E457">
+        <v>2.2</v>
+      </c>
+      <c r="F457">
+        <v>0.6</v>
+      </c>
+      <c r="G457">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7">
+      <c r="A458" s="1"/>
+      <c r="B458" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C458">
+        <v>0</v>
+      </c>
+      <c r="D458" t="s">
+        <v>57</v>
+      </c>
+      <c r="E458">
+        <v>2.6</v>
+      </c>
+      <c r="F458">
+        <v>2.1</v>
+      </c>
+      <c r="G458">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7">
+      <c r="A459" s="1"/>
+      <c r="B459" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C459">
+        <v>0.8</v>
+      </c>
+      <c r="E459">
+        <v>0.9</v>
+      </c>
+      <c r="F459">
         <v>0.5</v>
       </c>
-      <c r="F440">
+      <c r="G459">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7">
+      <c r="A460" s="1"/>
+      <c r="B460" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C460">
+        <v>0.1</v>
+      </c>
+      <c r="E460">
+        <v>0.6</v>
+      </c>
+      <c r="F460">
+        <v>0.4</v>
+      </c>
+      <c r="G460">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7">
+      <c r="A461" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B461" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C461">
+        <v>0</v>
+      </c>
+      <c r="D461" t="s">
+        <v>57</v>
+      </c>
+      <c r="E461">
+        <v>0</v>
+      </c>
+      <c r="F461">
+        <v>0</v>
+      </c>
+      <c r="G461">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7">
+      <c r="A462" s="1"/>
+      <c r="B462" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C462">
+        <v>0</v>
+      </c>
+      <c r="D462" t="s">
+        <v>57</v>
+      </c>
+      <c r="E462">
+        <v>0.4</v>
+      </c>
+      <c r="F462">
+        <v>0.2</v>
+      </c>
+      <c r="G462">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7">
+      <c r="A463" s="1"/>
+      <c r="B463" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C463">
         <v>0.3</v>
       </c>
-      <c r="G440">
+      <c r="E463">
+        <v>0.6</v>
+      </c>
+      <c r="F463">
+        <v>0.2</v>
+      </c>
+      <c r="G463">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7">
+      <c r="A464" s="1"/>
+      <c r="B464" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C464">
+        <v>0.4</v>
+      </c>
+      <c r="E464">
+        <v>0.5</v>
+      </c>
+      <c r="F464">
+        <v>0.1</v>
+      </c>
+      <c r="G464">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7">
+      <c r="A465" s="1"/>
+      <c r="B465" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C465">
+        <v>0.6</v>
+      </c>
+      <c r="E465">
+        <v>1.3</v>
+      </c>
+      <c r="F465">
+        <v>0.4</v>
+      </c>
+      <c r="G465">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7">
+      <c r="A466" s="1"/>
+      <c r="B466" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C466">
+        <v>0</v>
+      </c>
+      <c r="D466" t="s">
+        <v>57</v>
+      </c>
+      <c r="E466">
+        <v>0.3</v>
+      </c>
+      <c r="F466">
+        <v>0.1</v>
+      </c>
+      <c r="G466">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7">
+      <c r="A467" s="1"/>
+      <c r="B467" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C467">
+        <v>0.4</v>
+      </c>
+      <c r="E467">
         <v>0.8</v>
+      </c>
+      <c r="F467">
+        <v>0.5</v>
+      </c>
+      <c r="G467">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7">
+      <c r="A468" s="1"/>
+      <c r="B468" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C468">
+        <v>0.1</v>
+      </c>
+      <c r="E468">
+        <v>1.6</v>
+      </c>
+      <c r="F468">
+        <v>0.8</v>
+      </c>
+      <c r="G468">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7">
+      <c r="A469" s="1"/>
+      <c r="B469" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C469">
+        <v>0</v>
+      </c>
+      <c r="D469" t="s">
+        <v>57</v>
+      </c>
+      <c r="E469">
+        <v>2.2</v>
+      </c>
+      <c r="F469">
+        <v>1.4</v>
+      </c>
+      <c r="G469">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7">
+      <c r="A470" s="1"/>
+      <c r="B470" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C470">
+        <v>0.9</v>
+      </c>
+      <c r="E470">
+        <v>1.1</v>
+      </c>
+      <c r="F470">
+        <v>0.5</v>
+      </c>
+      <c r="G470">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7">
+      <c r="A471" s="1"/>
+      <c r="B471" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C471">
+        <v>0.6</v>
+      </c>
+      <c r="E471">
+        <v>0.8</v>
+      </c>
+      <c r="F471">
+        <v>0.3</v>
+      </c>
+      <c r="G471">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7">
+      <c r="A472" s="1"/>
+      <c r="B472" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C472">
+        <v>0.6</v>
+      </c>
+      <c r="E472">
+        <v>0.8</v>
+      </c>
+      <c r="F472">
+        <v>0.4</v>
+      </c>
+      <c r="G472">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7">
+      <c r="A473" s="1"/>
+      <c r="B473" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C473">
+        <v>0</v>
+      </c>
+      <c r="D473" t="s">
+        <v>57</v>
+      </c>
+      <c r="E473">
+        <v>7.3</v>
+      </c>
+      <c r="F473">
+        <v>1.1</v>
+      </c>
+      <c r="G473">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7">
+      <c r="A474" s="1"/>
+      <c r="B474" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C474">
+        <v>0</v>
+      </c>
+      <c r="D474" t="s">
+        <v>57</v>
+      </c>
+      <c r="E474">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F474">
+        <v>4.5</v>
+      </c>
+      <c r="G474">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7">
+      <c r="A475" s="1"/>
+      <c r="B475" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C475">
+        <v>0.9</v>
+      </c>
+      <c r="E475">
+        <v>1.1</v>
+      </c>
+      <c r="F475">
+        <v>0.3</v>
+      </c>
+      <c r="G475">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7">
+      <c r="A476" s="1"/>
+      <c r="B476" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C476">
+        <v>0.5</v>
+      </c>
+      <c r="E476">
+        <v>0.7</v>
+      </c>
+      <c r="F476">
+        <v>0.2</v>
+      </c>
+      <c r="G476">
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>
@@ -9403,12 +10237,12 @@
     <mergeCell ref="A139:A147"/>
     <mergeCell ref="A148:A156"/>
     <mergeCell ref="A157:A165"/>
-    <mergeCell ref="A363:A375"/>
-    <mergeCell ref="A376:A388"/>
-    <mergeCell ref="A389:A401"/>
-    <mergeCell ref="A402:A414"/>
-    <mergeCell ref="A415:A427"/>
-    <mergeCell ref="A428:A440"/>
+    <mergeCell ref="A381:A396"/>
+    <mergeCell ref="A397:A412"/>
+    <mergeCell ref="A413:A428"/>
+    <mergeCell ref="A429:A444"/>
+    <mergeCell ref="A445:A460"/>
+    <mergeCell ref="A461:A476"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets_output/09_logistic_regression_blocks.xlsx
+++ b/assets_output/09_logistic_regression_blocks.xlsx
@@ -49,7 +49,7 @@
     <t>rt_outcome</t>
   </si>
   <si>
-    <t>2026-06-20 11:53</t>
+    <t>2026-06-20 12:03</t>
   </si>
   <si>
     <t>2679</t>
@@ -208,9 +208,6 @@
     <t>cli_outcome</t>
   </si>
   <si>
-    <t>2026-06-20 11:54</t>
-  </si>
-  <si>
     <t>2014</t>
   </si>
   <si>
@@ -269,6 +266,9 @@
   </si>
   <si>
     <t>multiple_returns</t>
+  </si>
+  <si>
+    <t>2026-06-20 12:04</t>
   </si>
   <si>
     <t>3015</t>
@@ -855,7 +855,7 @@
   <dimension ref="A1:H476"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="7" width="9.140625" style="1"/>
+    <col min="3" max="8" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1063,7 +1063,7 @@
       <c r="G14" s="1">
         <v>-1.11392903337809</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>-0.6771811836907633</v>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       <c r="G15" s="1">
         <v>-0.4664249767471592</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>0.01388151312686606</v>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       <c r="G16" s="1">
         <v>0.08279480070465725</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>0.5198881519044269</v>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       <c r="G17" s="1">
         <v>-0.9239845564630997</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>-0.1923814052085897</v>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       <c r="G18" s="1">
         <v>-0.7284895018228333</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>0.4767695563220496</v>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       <c r="G19" s="1">
         <v>0.7365420173661663</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>1.34989440607928</v>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       <c r="G20" s="1">
         <v>0.04728124236257084</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>0.4849791568365172</v>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       <c r="G21" s="1">
         <v>1.050661769717664</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>1.483762529884471</v>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       <c r="G22" s="1">
         <v>0.201091380258715</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>0.7789886830308901</v>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       <c r="G23" s="1">
         <v>0.5236482076952025</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>3.495677134365566</v>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       <c r="G24" s="1">
         <v>0.02136272894230934</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>0.8032696084855746</v>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       <c r="G28" s="1">
         <v>-1.598398172647587</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>-1.115806990223457</v>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       <c r="G29" s="1">
         <v>-0.6076771548383374</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>-0.0846235192558179</v>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       <c r="G30" s="1">
         <v>-0.009359675379155691</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>0.4525063299653923</v>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       <c r="G31" s="1">
         <v>-1.311202228878892</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>-0.4091390632618893</v>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       <c r="G32" s="1">
         <v>-0.3906379681625919</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>0.8205279544400883</v>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       <c r="G33" s="1">
         <v>0.9834857793138327</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>1.601909089934065</v>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       <c r="G34" s="1">
         <v>-0.1081427162185326</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
         <v>0.3533904765169871</v>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       <c r="G35" s="1">
         <v>1.483541591110296</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="1">
         <v>1.952539403950829</v>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       <c r="G36" s="1">
         <v>0.8201709235385017</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="1">
         <v>1.387319471441722</v>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       <c r="G37" s="1">
         <v>0.7101315293755073</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="1">
         <v>3.701468415464758</v>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       <c r="G38" s="1">
         <v>-0.1622614325075197</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="1">
         <v>0.6640108904397559</v>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       <c r="G42" s="1">
         <v>-4.590412142661291</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="1">
         <v>-3.083112121701626</v>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       <c r="G43" s="1">
         <v>-1.27002330243478</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="1">
         <v>0.3175047081542241</v>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       <c r="G44" s="1">
         <v>-1.742754103359455</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="1">
         <v>-0.07616710704500573</v>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       <c r="G45" s="1">
         <v>-1.57490143462012</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="1">
         <v>0.8730840651048752</v>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       <c r="G46" s="1">
         <v>-0.2391325064177163</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="1">
         <v>2.311771029488853</v>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       <c r="G47" s="1">
         <v>-0.8400555367908615</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="1">
         <v>0.9939348365493195</v>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       <c r="G48" s="1">
         <v>0.1439029390041684</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="1">
         <v>1.351763038172491</v>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       <c r="G49" s="1">
         <v>1.164531804614537</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="1">
         <v>2.587692101413705</v>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       <c r="G50" s="1">
         <v>-1.019312160346784</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="1">
         <v>0.6804843090684729</v>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       <c r="G51" s="1">
         <v>0.6708046202848363</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="1">
         <v>4.960468528318827</v>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       <c r="G52" s="1">
         <v>-2.379952731895911</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="1">
         <v>0.5639181848985116</v>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
         <v>18</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2701,13 +2701,13 @@
         <v>3</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2718,13 +2718,13 @@
         <v>4</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2735,13 +2735,13 @@
         <v>5</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -2752,13 +2752,13 @@
         <v>6</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -2775,7 +2775,7 @@
         <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -2786,7 +2786,7 @@
         <v>8</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>24</v>
@@ -2797,12 +2797,12 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="B102" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>34</v>
@@ -2845,7 +2845,7 @@
       <c r="G103" s="1">
         <v>-1.581671125626535</v>
       </c>
-      <c r="H103">
+      <c r="H103" s="1">
         <v>-1.121933421239041</v>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       <c r="G104" s="1">
         <v>0.09821225139456244</v>
       </c>
-      <c r="H104">
+      <c r="H104" s="1">
         <v>0.5630220212008613</v>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       <c r="G105" s="1">
         <v>-1.105158534854958</v>
       </c>
-      <c r="H105">
+      <c r="H105" s="1">
         <v>-0.2719567335956136</v>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
       <c r="G106" s="1">
         <v>-0.7431440666727596</v>
       </c>
-      <c r="H106">
+      <c r="H106" s="1">
         <v>0.4894810949225405</v>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       <c r="G107" s="1">
         <v>0.7804091716324164</v>
       </c>
-      <c r="H107">
+      <c r="H107" s="1">
         <v>1.421845837535434</v>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       <c r="G108" s="1">
         <v>0.06152846867379258</v>
       </c>
-      <c r="H108">
+      <c r="H108" s="1">
         <v>0.5254846845735226</v>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       <c r="G109" s="1">
         <v>1.09511987964771</v>
       </c>
-      <c r="H109">
+      <c r="H109" s="1">
         <v>1.553474525821898</v>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       <c r="G110" s="1">
         <v>0.2572075455024447</v>
       </c>
-      <c r="H110">
+      <c r="H110" s="1">
         <v>0.8689035141718615</v>
       </c>
     </row>
@@ -3053,18 +3053,18 @@
       <c r="G111" s="1">
         <v>0.5514154012494417</v>
       </c>
-      <c r="H111">
+      <c r="H111" s="1">
         <v>3.577640313321367</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="B114" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>34</v>
@@ -3107,7 +3107,7 @@
       <c r="G115" s="1">
         <v>-2.26094286510595</v>
       </c>
-      <c r="H115">
+      <c r="H115" s="1">
         <v>-1.703790596333637</v>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       <c r="G116" s="1">
         <v>0.09977619639470781</v>
       </c>
-      <c r="H116">
+      <c r="H116" s="1">
         <v>0.6340541049345748</v>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       <c r="G117" s="1">
         <v>-1.445298367343927</v>
       </c>
-      <c r="H117">
+      <c r="H117" s="1">
         <v>-0.320375812927729</v>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
       <c r="G118" s="1">
         <v>-0.5552189959505973</v>
       </c>
-      <c r="H118">
+      <c r="H118" s="1">
         <v>0.7971064393036733</v>
       </c>
     </row>
@@ -3211,7 +3211,7 @@
       <c r="G119" s="1">
         <v>1.057537946935777</v>
       </c>
-      <c r="H119">
+      <c r="H119" s="1">
         <v>1.742491397233148</v>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       <c r="G120" s="1">
         <v>-0.4405542135482299</v>
       </c>
-      <c r="H120">
+      <c r="H120" s="1">
         <v>0.113856668556694</v>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       <c r="G121" s="1">
         <v>1.161560996922351</v>
       </c>
-      <c r="H121">
+      <c r="H121" s="1">
         <v>1.709458263052691</v>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       <c r="G122" s="1">
         <v>0.9176530279087538</v>
       </c>
-      <c r="H122">
+      <c r="H122" s="1">
         <v>1.552383594767749</v>
       </c>
     </row>
@@ -3315,18 +3315,18 @@
       <c r="G123" s="1">
         <v>0.4147109040290966</v>
       </c>
-      <c r="H123">
+      <c r="H123" s="1">
         <v>3.56721682068298</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="B126" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>34</v>
@@ -3369,7 +3369,7 @@
       <c r="G127" s="1">
         <v>-4.651449608929791</v>
       </c>
-      <c r="H127">
+      <c r="H127" s="1">
         <v>-3.125417455077427</v>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       <c r="G128" s="1">
         <v>-2.010675540612974</v>
       </c>
-      <c r="H128">
+      <c r="H128" s="1">
         <v>-0.05662752269617033</v>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       <c r="G129" s="1">
         <v>-1.983359913220259</v>
       </c>
-      <c r="H129">
+      <c r="H129" s="1">
         <v>0.9658182630324635</v>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
       <c r="G130" s="1">
         <v>-0.8141782442142619</v>
       </c>
-      <c r="H130">
+      <c r="H130" s="1">
         <v>2.188265962122714</v>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       <c r="G131" s="1">
         <v>-0.4763501192047371</v>
       </c>
-      <c r="H131">
+      <c r="H131" s="1">
         <v>1.506320001443703</v>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       <c r="G132" s="1">
         <v>-0.2109480295578882</v>
       </c>
-      <c r="H132">
+      <c r="H132" s="1">
         <v>1.182250792286782</v>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       <c r="G133" s="1">
         <v>0.5626440109166015</v>
       </c>
-      <c r="H133">
+      <c r="H133" s="1">
         <v>2.06934081441574</v>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       <c r="G134" s="1">
         <v>-0.9479014751812982</v>
       </c>
-      <c r="H134">
+      <c r="H134" s="1">
         <v>1.035544504843304</v>
       </c>
     </row>
@@ -3577,13 +3577,13 @@
       <c r="G135" s="1">
         <v>-0.1724693582507544</v>
       </c>
-      <c r="H135">
+      <c r="H135" s="1">
         <v>4.777935751991526</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -4151,7 +4151,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -4176,7 +4176,7 @@
         <v>1</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>17</v>
@@ -4193,7 +4193,7 @@
         <v>2</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>18</v>
@@ -4210,7 +4210,7 @@
         <v>3</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>19</v>
@@ -4295,7 +4295,7 @@
         <v>8</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>24</v>
@@ -4679,7 +4679,7 @@
         <v>1</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>17</v>
@@ -4713,7 +4713,7 @@
         <v>3</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>19</v>
@@ -5179,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>17</v>
@@ -5213,7 +5213,7 @@
         <v>3</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>19</v>
@@ -5587,7 +5587,7 @@
         <v>3</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>19</v>
@@ -5672,7 +5672,7 @@
         <v>8</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>24</v>
@@ -5731,7 +5731,7 @@
       <c r="G267" s="1">
         <v>-0.3794521339112729</v>
       </c>
-      <c r="H267">
+      <c r="H267" s="1">
         <v>0.05596069615941091</v>
       </c>
     </row>
@@ -5757,7 +5757,7 @@
       <c r="G268" s="1">
         <v>-0.4156794261977594</v>
       </c>
-      <c r="H268">
+      <c r="H268" s="1">
         <v>0.008212463020749405</v>
       </c>
     </row>
@@ -5783,7 +5783,7 @@
       <c r="G269" s="1">
         <v>-0.09855550044876138</v>
       </c>
-      <c r="H269">
+      <c r="H269" s="1">
         <v>0.2852048773364834</v>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       <c r="G270" s="1">
         <v>-0.5206101709821805</v>
       </c>
-      <c r="H270">
+      <c r="H270" s="1">
         <v>0.04045529280377202</v>
       </c>
     </row>
@@ -5835,7 +5835,7 @@
       <c r="G271" s="1">
         <v>-0.5178652812497002</v>
       </c>
-      <c r="H271">
+      <c r="H271" s="1">
         <v>0.282641141164032</v>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       <c r="G272" s="1">
         <v>-0.592490250309573</v>
       </c>
-      <c r="H272">
+      <c r="H272" s="1">
         <v>0.2422490531489189</v>
       </c>
     </row>
@@ -5887,7 +5887,7 @@
       <c r="G273" s="1">
         <v>-0.4076298473186334</v>
       </c>
-      <c r="H273">
+      <c r="H273" s="1">
         <v>0.258787783388101</v>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       <c r="G274" s="1">
         <v>-0.3628869222050291</v>
       </c>
-      <c r="H274">
+      <c r="H274" s="1">
         <v>0.5725779932168049</v>
       </c>
     </row>
@@ -5939,7 +5939,7 @@
       <c r="G275" s="1">
         <v>0.2569037196486199</v>
       </c>
-      <c r="H275">
+      <c r="H275" s="1">
         <v>0.8457558249120503</v>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       <c r="G276" s="1">
         <v>-0.08241003193804454</v>
       </c>
-      <c r="H276">
+      <c r="H276" s="1">
         <v>0.2994432408921167</v>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       <c r="G277" s="1">
         <v>0.02913405936958183</v>
       </c>
-      <c r="H277">
+      <c r="H277" s="1">
         <v>0.4164607320931782</v>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
       <c r="G278" s="1">
         <v>0.6636036815215647</v>
       </c>
-      <c r="H278">
+      <c r="H278" s="1">
         <v>1.053377552986486</v>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       <c r="G279" s="1">
         <v>-0.2264007150358374</v>
       </c>
-      <c r="H279">
+      <c r="H279" s="1">
         <v>0.3287318803315753</v>
       </c>
     </row>
@@ -6069,7 +6069,7 @@
       <c r="G280" s="1">
         <v>0.2509095883644255</v>
       </c>
-      <c r="H280">
+      <c r="H280" s="1">
         <v>2.365493653693948</v>
       </c>
     </row>
@@ -6095,7 +6095,7 @@
       <c r="G281" s="1">
         <v>-0.1313914841385387</v>
       </c>
-      <c r="H281">
+      <c r="H281" s="1">
         <v>0.3971902230541606</v>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       <c r="G282" s="1">
         <v>0.0928326932544668</v>
       </c>
-      <c r="H282">
+      <c r="H282" s="1">
         <v>0.8218305198931841</v>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       <c r="G286" s="1">
         <v>-2.029965583019055</v>
       </c>
-      <c r="H286">
+      <c r="H286" s="1">
         <v>-1.470084922694495</v>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       <c r="G287" s="1">
         <v>-0.7523918254036385</v>
       </c>
-      <c r="H287">
+      <c r="H287" s="1">
         <v>-0.2543621368008436</v>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       <c r="G288" s="1">
         <v>0.2305917466235909</v>
       </c>
-      <c r="H288">
+      <c r="H288" s="1">
         <v>0.6562999672258583</v>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       <c r="G289" s="1">
         <v>-0.5730547224899674</v>
       </c>
-      <c r="H289">
+      <c r="H289" s="1">
         <v>0.1239337246814425</v>
       </c>
     </row>
@@ -6279,7 +6279,7 @@
       <c r="G290" s="1">
         <v>-0.3647661217938782</v>
       </c>
-      <c r="H290">
+      <c r="H290" s="1">
         <v>0.5161779499616461</v>
       </c>
     </row>
@@ -6305,7 +6305,7 @@
       <c r="G291" s="1">
         <v>-0.6101141260653213</v>
       </c>
-      <c r="H291">
+      <c r="H291" s="1">
         <v>0.4599743893740868</v>
       </c>
     </row>
@@ -6331,7 +6331,7 @@
       <c r="G292" s="1">
         <v>-1.173265044696065</v>
       </c>
-      <c r="H292">
+      <c r="H292" s="1">
         <v>-0.2352943097830613</v>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       <c r="G293" s="1">
         <v>-0.9061301887400135</v>
       </c>
-      <c r="H293">
+      <c r="H293" s="1">
         <v>0.2917793033203441</v>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       <c r="G294" s="1">
         <v>0.8482745320418015</v>
       </c>
-      <c r="H294">
+      <c r="H294" s="1">
         <v>1.442096917649641</v>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       <c r="G295" s="1">
         <v>0.09510166709235848</v>
       </c>
-      <c r="H295">
+      <c r="H295" s="1">
         <v>0.5157075113464218</v>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       <c r="G296" s="1">
         <v>0.06667682371058628</v>
       </c>
-      <c r="H296">
+      <c r="H296" s="1">
         <v>0.5225732684393821</v>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       <c r="G297" s="1">
         <v>1.895775871206949</v>
       </c>
-      <c r="H297">
+      <c r="H297" s="1">
         <v>2.369129669327319</v>
       </c>
     </row>
@@ -6487,7 +6487,7 @@
       <c r="G298" s="1">
         <v>0.5344773274419343</v>
       </c>
-      <c r="H298">
+      <c r="H298" s="1">
         <v>1.082229491680292</v>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
       <c r="G299" s="1">
         <v>0.6153211839312183</v>
       </c>
-      <c r="H299">
+      <c r="H299" s="1">
         <v>2.736269407437578</v>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       <c r="G300" s="1">
         <v>-0.1736908324032717</v>
       </c>
-      <c r="H300">
+      <c r="H300" s="1">
         <v>0.4179751144470288</v>
       </c>
     </row>
@@ -6565,7 +6565,7 @@
       <c r="G301" s="1">
         <v>0.06460931570213491</v>
       </c>
-      <c r="H301">
+      <c r="H301" s="1">
         <v>0.8304754246572181</v>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       <c r="G305" s="1">
         <v>-2.072725186876687</v>
       </c>
-      <c r="H305">
+      <c r="H305" s="1">
         <v>-1.460896647553666</v>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       <c r="G306" s="1">
         <v>-0.3405916219352946</v>
       </c>
-      <c r="H306">
+      <c r="H306" s="1">
         <v>0.1897202485915027</v>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
       <c r="G307" s="1">
         <v>-0.04716994659839932</v>
       </c>
-      <c r="H307">
+      <c r="H307" s="1">
         <v>0.4316558923622377</v>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       <c r="G308" s="1">
         <v>-0.5414807457307159</v>
       </c>
-      <c r="H308">
+      <c r="H308" s="1">
         <v>0.2181943098687102</v>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
       <c r="G309" s="1">
         <v>-0.3346749806920611</v>
       </c>
-      <c r="H309">
+      <c r="H309" s="1">
         <v>0.6225128769362706</v>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       <c r="G310" s="1">
         <v>-1.070329688994984</v>
       </c>
-      <c r="H310">
+      <c r="H310" s="1">
         <v>0.1611247705406285</v>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       <c r="G311" s="1">
         <v>-0.382400541654449</v>
       </c>
-      <c r="H311">
+      <c r="H311" s="1">
         <v>0.5109474205583086</v>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       <c r="G312" s="1">
         <v>-0.2232518259586685</v>
       </c>
-      <c r="H312">
+      <c r="H312" s="1">
         <v>0.9327930429342112</v>
       </c>
     </row>
@@ -6827,7 +6827,7 @@
       <c r="G313" s="1">
         <v>0.3796587802912924</v>
       </c>
-      <c r="H313">
+      <c r="H313" s="1">
         <v>1.055820429376243</v>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       <c r="G314" s="1">
         <v>-0.1095286321140161</v>
       </c>
-      <c r="H314">
+      <c r="H314" s="1">
         <v>0.3627804638057345</v>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       <c r="G315" s="1">
         <v>0.01714843807045363</v>
       </c>
-      <c r="H315">
+      <c r="H315" s="1">
         <v>0.5286652165240471</v>
       </c>
     </row>
@@ -6905,7 +6905,7 @@
       <c r="G316" s="1">
         <v>1.390289901573426</v>
       </c>
-      <c r="H316">
+      <c r="H316" s="1">
         <v>1.897608378770266</v>
       </c>
     </row>
@@ -6931,7 +6931,7 @@
       <c r="G317" s="1">
         <v>-0.1287881369037527</v>
       </c>
-      <c r="H317">
+      <c r="H317" s="1">
         <v>0.5104473116702856</v>
       </c>
     </row>
@@ -6957,7 +6957,7 @@
       <c r="G318" s="1">
         <v>0.3917152749969173</v>
       </c>
-      <c r="H318">
+      <c r="H318" s="1">
         <v>2.560632861239616</v>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       <c r="G319" s="1">
         <v>-0.06196136672496927</v>
       </c>
-      <c r="H319">
+      <c r="H319" s="1">
         <v>0.5723969009635295</v>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       <c r="G320" s="1">
         <v>0.2460957029449067</v>
       </c>
-      <c r="H320">
+      <c r="H320" s="1">
         <v>1.051289388167086</v>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       <c r="G324" s="1">
         <v>-1.779681354985243</v>
       </c>
-      <c r="H324">
+      <c r="H324" s="1">
         <v>-1.203673209740966</v>
       </c>
     </row>
@@ -7089,7 +7089,7 @@
       <c r="G325" s="1">
         <v>-0.7127365325249728</v>
       </c>
-      <c r="H325">
+      <c r="H325" s="1">
         <v>-0.1554162212376664</v>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       <c r="G326" s="1">
         <v>0.02492089707416853</v>
       </c>
-      <c r="H326">
+      <c r="H326" s="1">
         <v>0.4969478061980688</v>
       </c>
     </row>
@@ -7141,7 +7141,7 @@
       <c r="G327" s="1">
         <v>-0.5137537833940388</v>
       </c>
-      <c r="H327">
+      <c r="H327" s="1">
         <v>0.2349713644088363</v>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       <c r="G328" s="1">
         <v>-0.2593570436178049</v>
       </c>
-      <c r="H328">
+      <c r="H328" s="1">
         <v>0.6827400439911467</v>
       </c>
     </row>
@@ -7193,7 +7193,7 @@
       <c r="G329" s="1">
         <v>-0.771983646886419</v>
       </c>
-      <c r="H329">
+      <c r="H329" s="1">
         <v>0.4394190304625612</v>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
       <c r="G330" s="1">
         <v>-1.381128981040567</v>
       </c>
-      <c r="H330">
+      <c r="H330" s="1">
         <v>-0.3017835157078526</v>
       </c>
     </row>
@@ -7245,7 +7245,7 @@
       <c r="G331" s="1">
         <v>-0.3377962619885364</v>
       </c>
-      <c r="H331">
+      <c r="H331" s="1">
         <v>0.8166958990011259</v>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
       <c r="G332" s="1">
         <v>0.8143774989642329</v>
       </c>
-      <c r="H332">
+      <c r="H332" s="1">
         <v>1.447641279784983</v>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       <c r="G333" s="1">
         <v>-0.260938305050137</v>
       </c>
-      <c r="H333">
+      <c r="H333" s="1">
         <v>0.2120565023667073</v>
       </c>
     </row>
@@ -7323,7 +7323,7 @@
       <c r="G334" s="1">
         <v>-0.1999110807604748</v>
       </c>
-      <c r="H334">
+      <c r="H334" s="1">
         <v>0.2907875932124501</v>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       <c r="G335" s="1">
         <v>1.16081756745314</v>
       </c>
-      <c r="H335">
+      <c r="H335" s="1">
         <v>1.65861368521251</v>
       </c>
     </row>
@@ -7375,7 +7375,7 @@
       <c r="G336" s="1">
         <v>0.8361674612182191</v>
       </c>
-      <c r="H336">
+      <c r="H336" s="1">
         <v>1.415019414558038</v>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       <c r="G337" s="1">
         <v>0.07503980290788737</v>
       </c>
-      <c r="H337">
+      <c r="H337" s="1">
         <v>2.326292122397795</v>
       </c>
     </row>
@@ -7427,7 +7427,7 @@
       <c r="G338" s="1">
         <v>0.1016957884901405</v>
       </c>
-      <c r="H338">
+      <c r="H338" s="1">
         <v>0.7424539501964886</v>
       </c>
     </row>
@@ -7453,7 +7453,7 @@
       <c r="G339" s="1">
         <v>-0.236752523531176</v>
       </c>
-      <c r="H339">
+      <c r="H339" s="1">
         <v>0.6337690560963747</v>
       </c>
     </row>
@@ -7507,7 +7507,7 @@
       <c r="G343" s="1">
         <v>-1.7832611939023</v>
       </c>
-      <c r="H343">
+      <c r="H343" s="1">
         <v>-1.186612231126567</v>
       </c>
     </row>
@@ -7533,7 +7533,7 @@
       <c r="G344" s="1">
         <v>-0.5406015896630854</v>
       </c>
-      <c r="H344">
+      <c r="H344" s="1">
         <v>0.03097531535405146</v>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       <c r="G345" s="1">
         <v>0.1270387599356181</v>
       </c>
-      <c r="H345">
+      <c r="H345" s="1">
         <v>0.6212667389029632</v>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       <c r="G346" s="1">
         <v>-0.8381303894055891</v>
       </c>
-      <c r="H346">
+      <c r="H346" s="1">
         <v>-0.01840949957910193</v>
       </c>
     </row>
@@ -7611,7 +7611,7 @@
       <c r="G347" s="1">
         <v>-0.4237964386129014</v>
       </c>
-      <c r="H347">
+      <c r="H347" s="1">
         <v>0.5767915293081115</v>
       </c>
     </row>
@@ -7637,7 +7637,7 @@
       <c r="G348" s="1">
         <v>-0.4531655650997795</v>
       </c>
-      <c r="H348">
+      <c r="H348" s="1">
         <v>0.6760699267891392</v>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
       <c r="G349" s="1">
         <v>-1.032061481682584</v>
       </c>
-      <c r="H349">
+      <c r="H349" s="1">
         <v>0.002354701984092156</v>
       </c>
     </row>
@@ -7689,7 +7689,7 @@
       <c r="G350" s="1">
         <v>-0.7211615688475324</v>
       </c>
-      <c r="H350">
+      <c r="H350" s="1">
         <v>0.5910706460996578</v>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
       <c r="G351" s="1">
         <v>0.9001411363603826</v>
       </c>
-      <c r="H351">
+      <c r="H351" s="1">
         <v>1.555911414664031</v>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       <c r="G352" s="1">
         <v>-0.09535135922127466</v>
       </c>
-      <c r="H352">
+      <c r="H352" s="1">
         <v>0.4010403355315284</v>
       </c>
     </row>
@@ -7767,7 +7767,7 @@
       <c r="G353" s="1">
         <v>-0.1138148149619644</v>
       </c>
-      <c r="H353">
+      <c r="H353" s="1">
         <v>0.4057781958152997</v>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       <c r="G354" s="1">
         <v>0.7179174510773059</v>
       </c>
-      <c r="H354">
+      <c r="H354" s="1">
         <v>1.22715333600319</v>
       </c>
     </row>
@@ -7819,7 +7819,7 @@
       <c r="G355" s="1">
         <v>0.1780476598988924</v>
       </c>
-      <c r="H355">
+      <c r="H355" s="1">
         <v>0.8241542965455424</v>
       </c>
     </row>
@@ -7845,7 +7845,7 @@
       <c r="G356" s="1">
         <v>-0.4319139815820435</v>
       </c>
-      <c r="H356">
+      <c r="H356" s="1">
         <v>1.983054500026549</v>
       </c>
     </row>
@@ -7871,7 +7871,7 @@
       <c r="G357" s="1">
         <v>-0.1643150917220104</v>
       </c>
-      <c r="H357">
+      <c r="H357" s="1">
         <v>0.5189407390004216</v>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       <c r="G358" s="1">
         <v>-0.003782097928405614</v>
       </c>
-      <c r="H358">
+      <c r="H358" s="1">
         <v>0.8867400416544984</v>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       <c r="G362" s="1">
         <v>-4.000417301084121</v>
       </c>
-      <c r="H362">
+      <c r="H362" s="1">
         <v>-2.606818454421251</v>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
       <c r="G363" s="1">
         <v>-1.912294662764338</v>
       </c>
-      <c r="H363">
+      <c r="H363" s="1">
         <v>-0.3512020892614878</v>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       <c r="G364" s="1">
         <v>-1.530350648272595</v>
       </c>
-      <c r="H364">
+      <c r="H364" s="1">
         <v>-0.139230706053731</v>
       </c>
     </row>
@@ -8029,7 +8029,7 @@
       <c r="G365" s="1">
         <v>-1.522058699987674</v>
       </c>
-      <c r="H365">
+      <c r="H365" s="1">
         <v>0.4381666504900092</v>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       <c r="G366" s="1">
         <v>-2.062432488382198</v>
       </c>
-      <c r="H366">
+      <c r="H366" s="1">
         <v>0.8421422264156312</v>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       <c r="G367" s="1">
         <v>-0.8745902031262747</v>
       </c>
-      <c r="H367">
+      <c r="H367" s="1">
         <v>1.46934270526139</v>
       </c>
     </row>
@@ -8107,7 +8107,7 @@
       <c r="G368" s="1">
         <v>-1.575954811601535</v>
       </c>
-      <c r="H368">
+      <c r="H368" s="1">
         <v>0.7591144298301369</v>
       </c>
     </row>
@@ -8133,7 +8133,7 @@
       <c r="G369" s="1">
         <v>-1.144966090798028</v>
       </c>
-      <c r="H369">
+      <c r="H369" s="1">
         <v>1.344563850095496</v>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       <c r="G370" s="1">
         <v>-0.1687945306777891</v>
       </c>
-      <c r="H370">
+      <c r="H370" s="1">
         <v>1.148256588619847</v>
       </c>
     </row>
@@ -8185,7 +8185,7 @@
       <c r="G371" s="1">
         <v>0.3108404765601874</v>
       </c>
-      <c r="H371">
+      <c r="H371" s="1">
         <v>1.27748703258986</v>
       </c>
     </row>
@@ -8211,7 +8211,7 @@
       <c r="G372" s="1">
         <v>-0.7374030849275288</v>
       </c>
-      <c r="H372">
+      <c r="H372" s="1">
         <v>0.2644607121807914</v>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       <c r="G373" s="1">
         <v>1.498579790028376</v>
       </c>
-      <c r="H373">
+      <c r="H373" s="1">
         <v>2.715975734229473</v>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       <c r="G374" s="1">
         <v>-0.8610833067820753</v>
       </c>
-      <c r="H374">
+      <c r="H374" s="1">
         <v>0.4749084948005612</v>
       </c>
     </row>
@@ -8289,7 +8289,7 @@
       <c r="G375" s="1">
         <v>0.09105692280961741</v>
       </c>
-      <c r="H375">
+      <c r="H375" s="1">
         <v>3.882701724248067</v>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
       <c r="G376" s="1">
         <v>-1.094813380716308</v>
       </c>
-      <c r="H376">
+      <c r="H376" s="1">
         <v>0.5851765342471886</v>
       </c>
     </row>
@@ -8341,7 +8341,7 @@
       <c r="G377" s="1">
         <v>-0.793898663225588</v>
       </c>
-      <c r="H377">
+      <c r="H377" s="1">
         <v>0.9518238887025006</v>
       </c>
     </row>

--- a/assets_output/09_logistic_regression_blocks.xlsx
+++ b/assets_output/09_logistic_regression_blocks.xlsx
@@ -49,7 +49,7 @@
     <t>rt_outcome</t>
   </si>
   <si>
-    <t>2026-06-20 12:03</t>
+    <t>2026-06-20 12:08</t>
   </si>
   <si>
     <t>2679</t>
@@ -268,9 +268,6 @@
     <t>multiple_returns</t>
   </si>
   <si>
-    <t>2026-06-20 12:04</t>
-  </si>
-  <si>
     <t>3015</t>
   </si>
   <si>
@@ -314,6 +311,9 @@
   </si>
   <si>
     <t>has_longer_term_rt</t>
+  </si>
+  <si>
+    <t>2026-06-20 12:09</t>
   </si>
   <si>
     <t>3032</t>
@@ -855,7 +855,7 @@
   <dimension ref="A1:H476"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="8" width="9.140625" style="1"/>
+    <col min="2" max="8" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -881,7 +881,7 @@
       <c r="A3" s="2">
         <v>0</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -898,7 +898,7 @@
       <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -915,7 +915,7 @@
       <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -932,7 +932,7 @@
       <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -949,7 +949,7 @@
       <c r="A7" s="2">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -966,7 +966,7 @@
       <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -983,7 +983,7 @@
       <c r="A9" s="2">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1000,7 +1000,7 @@
       <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1045,7 +1045,7 @@
       <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="1">
@@ -1071,7 +1071,7 @@
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C15" s="1">
@@ -1097,7 +1097,7 @@
       <c r="A16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C16" s="1">
@@ -1123,7 +1123,7 @@
       <c r="A17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="1">
@@ -1149,7 +1149,7 @@
       <c r="A18" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="1">
@@ -1175,7 +1175,7 @@
       <c r="A19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C19" s="1">
@@ -1201,7 +1201,7 @@
       <c r="A20" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C20" s="1">
@@ -1227,7 +1227,7 @@
       <c r="A21" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C21" s="1">
@@ -1253,7 +1253,7 @@
       <c r="A22" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C22" s="1">
@@ -1279,7 +1279,7 @@
       <c r="A23" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C23" s="1">
@@ -1305,7 +1305,7 @@
       <c r="A24" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C24" s="1">
@@ -1359,7 +1359,7 @@
       <c r="A28" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C28" s="1">
@@ -1385,7 +1385,7 @@
       <c r="A29" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C29" s="1">
@@ -1411,7 +1411,7 @@
       <c r="A30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C30" s="1">
@@ -1437,7 +1437,7 @@
       <c r="A31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="1">
@@ -1463,7 +1463,7 @@
       <c r="A32" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C32" s="1">
@@ -1489,7 +1489,7 @@
       <c r="A33" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C33" s="1">
@@ -1515,7 +1515,7 @@
       <c r="A34" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C34" s="1">
@@ -1541,7 +1541,7 @@
       <c r="A35" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C35" s="1">
@@ -1567,7 +1567,7 @@
       <c r="A36" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C36" s="1">
@@ -1593,7 +1593,7 @@
       <c r="A37" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C37" s="1">
@@ -1619,7 +1619,7 @@
       <c r="A38" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C38" s="1">
@@ -1673,7 +1673,7 @@
       <c r="A42" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C42" s="1">
@@ -1699,7 +1699,7 @@
       <c r="A43" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C43" s="1">
@@ -1725,7 +1725,7 @@
       <c r="A44" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C44" s="1">
@@ -1751,7 +1751,7 @@
       <c r="A45" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C45" s="1">
@@ -1777,7 +1777,7 @@
       <c r="A46" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C46" s="1">
@@ -1803,7 +1803,7 @@
       <c r="A47" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C47" s="1">
@@ -1829,7 +1829,7 @@
       <c r="A48" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C48" s="1">
@@ -1855,7 +1855,7 @@
       <c r="A49" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C49" s="1">
@@ -1881,7 +1881,7 @@
       <c r="A50" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C50" s="1">
@@ -1907,7 +1907,7 @@
       <c r="A51" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C51" s="1">
@@ -1933,7 +1933,7 @@
       <c r="A52" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C52" s="1">
@@ -2663,7 +2663,7 @@
       <c r="A92" s="2">
         <v>0</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C92" s="1" t="s">
@@ -2680,7 +2680,7 @@
       <c r="A93" s="2">
         <v>1</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="1" t="s">
@@ -2697,7 +2697,7 @@
       <c r="A94" s="2">
         <v>2</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C94" s="1" t="s">
@@ -2714,7 +2714,7 @@
       <c r="A95" s="2">
         <v>3</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C95" s="1" t="s">
@@ -2731,7 +2731,7 @@
       <c r="A96" s="2">
         <v>4</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C96" s="1" t="s">
@@ -2748,7 +2748,7 @@
       <c r="A97" s="2">
         <v>5</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="1" t="s">
@@ -2765,7 +2765,7 @@
       <c r="A98" s="2">
         <v>6</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="1" t="s">
@@ -2782,7 +2782,7 @@
       <c r="A99" s="2">
         <v>7</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C99" s="1" t="s">
@@ -2827,7 +2827,7 @@
       <c r="A103" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C103" s="1">
@@ -2853,7 +2853,7 @@
       <c r="A104" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C104" s="1">
@@ -2879,7 +2879,7 @@
       <c r="A105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C105" s="1">
@@ -2905,7 +2905,7 @@
       <c r="A106" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C106" s="1">
@@ -2931,7 +2931,7 @@
       <c r="A107" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C107" s="1">
@@ -2957,7 +2957,7 @@
       <c r="A108" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C108" s="1">
@@ -2983,7 +2983,7 @@
       <c r="A109" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C109" s="1">
@@ -3009,7 +3009,7 @@
       <c r="A110" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C110" s="1">
@@ -3035,7 +3035,7 @@
       <c r="A111" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C111" s="1">
@@ -3089,7 +3089,7 @@
       <c r="A115" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C115" s="1">
@@ -3115,7 +3115,7 @@
       <c r="A116" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C116" s="1">
@@ -3141,7 +3141,7 @@
       <c r="A117" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C117" s="1">
@@ -3167,7 +3167,7 @@
       <c r="A118" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C118" s="1">
@@ -3193,7 +3193,7 @@
       <c r="A119" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C119" s="1">
@@ -3219,7 +3219,7 @@
       <c r="A120" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C120" s="1">
@@ -3245,7 +3245,7 @@
       <c r="A121" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C121" s="1">
@@ -3271,7 +3271,7 @@
       <c r="A122" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C122" s="1">
@@ -3297,7 +3297,7 @@
       <c r="A123" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C123" s="1">
@@ -3351,7 +3351,7 @@
       <c r="A127" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C127" s="1">
@@ -3377,7 +3377,7 @@
       <c r="A128" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C128" s="1">
@@ -3403,7 +3403,7 @@
       <c r="A129" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C129" s="1">
@@ -3429,7 +3429,7 @@
       <c r="A130" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C130" s="1">
@@ -3455,7 +3455,7 @@
       <c r="A131" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C131" s="1">
@@ -3481,7 +3481,7 @@
       <c r="A132" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C132" s="1">
@@ -3507,7 +3507,7 @@
       <c r="A133" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C133" s="1">
@@ -3533,7 +3533,7 @@
       <c r="A134" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C134" s="1">
@@ -3559,7 +3559,7 @@
       <c r="A135" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C135" s="1">
@@ -4172,7 +4172,7 @@
       <c r="A169" s="2">
         <v>0</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C169" s="1" t="s">
@@ -4189,7 +4189,7 @@
       <c r="A170" s="2">
         <v>1</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C170" s="1" t="s">
@@ -4199,82 +4199,82 @@
         <v>18</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2">
         <v>2</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2">
         <v>3</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B172" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2">
         <v>4</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B173" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2">
         <v>5</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2">
         <v>6</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B175" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C175" s="1" t="s">
@@ -4284,14 +4284,14 @@
         <v>23</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2">
         <v>7</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C176" s="1" t="s">
@@ -4306,7 +4306,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -4317,10 +4317,10 @@
         <v>35</v>
       </c>
       <c r="D179" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E179" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="E179" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>38</v>
@@ -4333,7 +4333,7 @@
       <c r="A180" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B180">
+      <c r="B180" s="1">
         <v>-4.333940926732454</v>
       </c>
       <c r="C180" s="1">
@@ -4356,7 +4356,7 @@
       <c r="A181" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B181">
+      <c r="B181" s="1">
         <v>0.5024721662958982</v>
       </c>
       <c r="C181" s="1">
@@ -4379,7 +4379,7 @@
       <c r="A182" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B182">
+      <c r="B182" s="1">
         <v>0.7840184968228269</v>
       </c>
       <c r="C182" s="1">
@@ -4402,7 +4402,7 @@
       <c r="A183" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B183">
+      <c r="B183" s="1">
         <v>0.3872625266993386</v>
       </c>
       <c r="C183" s="1">
@@ -4425,7 +4425,7 @@
       <c r="A184" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B184">
+      <c r="B184" s="1">
         <v>1.895252685444775</v>
       </c>
       <c r="C184" s="1">
@@ -4448,7 +4448,7 @@
       <c r="A185" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B185">
+      <c r="B185" s="1">
         <v>0.5274721624755884</v>
       </c>
       <c r="C185" s="1">
@@ -4471,7 +4471,7 @@
       <c r="A186" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B186">
+      <c r="B186" s="1">
         <v>0.7722157720370918</v>
       </c>
       <c r="C186" s="1">
@@ -4492,7 +4492,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -4516,7 +4516,7 @@
       <c r="A190" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B190">
+      <c r="B190" s="1">
         <v>3.403877632060557E-100</v>
       </c>
       <c r="C190" s="1" t="s">
@@ -4536,7 +4536,7 @@
       <c r="A191" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B191">
+      <c r="B191" s="1">
         <v>0.0002162299178150398</v>
       </c>
       <c r="C191" s="1" t="s">
@@ -4556,7 +4556,7 @@
       <c r="A192" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B192">
+      <c r="B192" s="1">
         <v>3.877645465391263E-08</v>
       </c>
       <c r="C192" s="1" t="s">
@@ -4576,7 +4576,7 @@
       <c r="A193" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B193">
+      <c r="B193" s="1">
         <v>0.004006522046895985</v>
       </c>
       <c r="C193" s="1" t="s">
@@ -4596,7 +4596,7 @@
       <c r="A194" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B194">
+      <c r="B194" s="1">
         <v>0.0001671667483768753</v>
       </c>
       <c r="C194" s="1" t="s">
@@ -4616,7 +4616,7 @@
       <c r="A195" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B195">
+      <c r="B195" s="1">
         <v>0.01872462001917282</v>
       </c>
       <c r="C195" s="1" t="s">
@@ -4636,7 +4636,7 @@
       <c r="A196" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B196">
+      <c r="B196" s="1">
         <v>5.644264481205005E-23</v>
       </c>
       <c r="C196" s="1" t="s">
@@ -4654,7 +4654,7 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4675,7 +4675,7 @@
       <c r="A200" s="2">
         <v>0</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B200" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C200" s="1" t="s">
@@ -4692,11 +4692,11 @@
       <c r="A201" s="2">
         <v>1</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B201" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>18</v>
@@ -4709,11 +4709,11 @@
       <c r="A202" s="2">
         <v>2</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>19</v>
@@ -4726,7 +4726,7 @@
       <c r="A203" s="2">
         <v>3</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B203" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C203" s="1" t="s">
@@ -4743,11 +4743,11 @@
       <c r="A204" s="2">
         <v>4</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B204" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>21</v>
@@ -4760,7 +4760,7 @@
       <c r="A205" s="2">
         <v>5</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B205" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C205" s="1" t="s">
@@ -4777,7 +4777,7 @@
       <c r="A206" s="2">
         <v>6</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B206" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C206" s="1" t="s">
@@ -4794,7 +4794,7 @@
       <c r="A207" s="2">
         <v>7</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B207" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C207" s="1" t="s">
@@ -4820,10 +4820,10 @@
         <v>35</v>
       </c>
       <c r="D210" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E210" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>38</v>
@@ -4836,7 +4836,7 @@
       <c r="A211" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B211">
+      <c r="B211" s="1">
         <v>-1.147198797506423</v>
       </c>
       <c r="C211" s="1">
@@ -4859,7 +4859,7 @@
       <c r="A212" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B212">
+      <c r="B212" s="1">
         <v>-0.5288436847696434</v>
       </c>
       <c r="C212" s="1">
@@ -4882,7 +4882,7 @@
       <c r="A213" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B213">
+      <c r="B213" s="1">
         <v>-1.11558867186674</v>
       </c>
       <c r="C213" s="1">
@@ -4905,7 +4905,7 @@
       <c r="A214" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B214">
+      <c r="B214" s="1">
         <v>-0.5562121563176856</v>
       </c>
       <c r="C214" s="1">
@@ -4928,7 +4928,7 @@
       <c r="A215" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B215">
+      <c r="B215" s="1">
         <v>-0.7739634004747185</v>
       </c>
       <c r="C215" s="1">
@@ -4951,7 +4951,7 @@
       <c r="A216" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B216">
+      <c r="B216" s="1">
         <v>-1.207732428258562</v>
       </c>
       <c r="C216" s="1">
@@ -4974,7 +4974,7 @@
       <c r="A217" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B217">
+      <c r="B217" s="1">
         <v>0.4898034909014749</v>
       </c>
       <c r="C217" s="1">
@@ -5019,7 +5019,7 @@
       <c r="A221" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B221">
+      <c r="B221" s="1">
         <v>7.285949456051732E-54</v>
       </c>
       <c r="C221" s="1" t="s">
@@ -5039,7 +5039,7 @@
       <c r="A222" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B222">
+      <c r="B222" s="1">
         <v>7.537727985363454E-07</v>
       </c>
       <c r="C222" s="1" t="s">
@@ -5059,7 +5059,7 @@
       <c r="A223" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B223">
+      <c r="B223" s="1">
         <v>3.024980425802322E-05</v>
       </c>
       <c r="C223" s="1" t="s">
@@ -5079,7 +5079,7 @@
       <c r="A224" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B224">
+      <c r="B224" s="1">
         <v>0.2824771975296116</v>
       </c>
       <c r="D224" s="1">
@@ -5096,7 +5096,7 @@
       <c r="A225" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B225">
+      <c r="B225" s="1">
         <v>4.231429130550076E-06</v>
       </c>
       <c r="C225" s="1" t="s">
@@ -5116,7 +5116,7 @@
       <c r="A226" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B226">
+      <c r="B226" s="1">
         <v>0.005169534398375955</v>
       </c>
       <c r="C226" s="1" t="s">
@@ -5136,7 +5136,7 @@
       <c r="A227" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B227">
+      <c r="B227" s="1">
         <v>6.031114858474766E-12</v>
       </c>
       <c r="C227" s="1" t="s">
@@ -5175,7 +5175,7 @@
       <c r="A231" s="2">
         <v>0</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B231" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C231" s="1" t="s">
@@ -5192,7 +5192,7 @@
       <c r="A232" s="2">
         <v>1</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B232" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C232" s="1" t="s">
@@ -5209,11 +5209,11 @@
       <c r="A233" s="2">
         <v>2</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>19</v>
@@ -5226,7 +5226,7 @@
       <c r="A234" s="2">
         <v>3</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B234" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C234" s="1" t="s">
@@ -5243,7 +5243,7 @@
       <c r="A235" s="2">
         <v>4</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B235" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C235" s="1" t="s">
@@ -5260,7 +5260,7 @@
       <c r="A236" s="2">
         <v>5</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B236" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C236" s="1" t="s">
@@ -5277,7 +5277,7 @@
       <c r="A237" s="2">
         <v>6</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B237" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C237" s="1" t="s">
@@ -5294,7 +5294,7 @@
       <c r="A238" s="2">
         <v>7</v>
       </c>
-      <c r="B238" t="s">
+      <c r="B238" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C238" s="1" t="s">
@@ -5320,10 +5320,10 @@
         <v>35</v>
       </c>
       <c r="D241" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E241" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>38</v>
@@ -5336,7 +5336,7 @@
       <c r="A242" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B242">
+      <c r="B242" s="1">
         <v>-5.389729049222971</v>
       </c>
       <c r="C242" s="1">
@@ -5359,7 +5359,7 @@
       <c r="A243" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B243">
+      <c r="B243" s="1">
         <v>2.475108324951747</v>
       </c>
       <c r="C243" s="1">
@@ -5382,7 +5382,7 @@
       <c r="A244" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B244">
+      <c r="B244" s="1">
         <v>2.648706171830171</v>
       </c>
       <c r="C244" s="1">
@@ -5405,7 +5405,7 @@
       <c r="A245" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B245">
+      <c r="B245" s="1">
         <v>1.172146522488462</v>
       </c>
       <c r="C245" s="1">
@@ -5450,7 +5450,7 @@
       <c r="A249" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B249">
+      <c r="B249" s="1">
         <v>3.222904910656649E-17</v>
       </c>
       <c r="C249" s="1" t="s">
@@ -5470,7 +5470,7 @@
       <c r="A250" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B250">
+      <c r="B250" s="1">
         <v>0.0004389868297785795</v>
       </c>
       <c r="C250" s="1" t="s">
@@ -5490,7 +5490,7 @@
       <c r="A251" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B251">
+      <c r="B251" s="1">
         <v>0.03919733536927187</v>
       </c>
       <c r="C251" s="1" t="s">
@@ -5510,7 +5510,7 @@
       <c r="A252" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B252">
+      <c r="B252" s="1">
         <v>3.086842961632247E-05</v>
       </c>
       <c r="C252" s="1" t="s">
@@ -5549,7 +5549,7 @@
       <c r="A256" s="2">
         <v>0</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B256" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C256" s="1" t="s">
@@ -5566,7 +5566,7 @@
       <c r="A257" s="2">
         <v>1</v>
       </c>
-      <c r="B257" t="s">
+      <c r="B257" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C257" s="1" t="s">
@@ -5583,11 +5583,11 @@
       <c r="A258" s="2">
         <v>2</v>
       </c>
-      <c r="B258" t="s">
+      <c r="B258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>19</v>
@@ -5600,7 +5600,7 @@
       <c r="A259" s="2">
         <v>3</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B259" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C259" s="1" t="s">
@@ -5617,7 +5617,7 @@
       <c r="A260" s="2">
         <v>4</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B260" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C260" s="1" t="s">
@@ -5634,7 +5634,7 @@
       <c r="A261" s="2">
         <v>5</v>
       </c>
-      <c r="B261" t="s">
+      <c r="B261" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C261" s="1" t="s">
@@ -5651,7 +5651,7 @@
       <c r="A262" s="2">
         <v>6</v>
       </c>
-      <c r="B262" t="s">
+      <c r="B262" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C262" s="1" t="s">
@@ -5668,7 +5668,7 @@
       <c r="A263" s="2">
         <v>7</v>
       </c>
-      <c r="B263" t="s">
+      <c r="B263" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C263" s="1" t="s">
@@ -5713,7 +5713,7 @@
       <c r="A267" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B267" t="s">
+      <c r="B267" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C267" s="1">
@@ -5739,7 +5739,7 @@
       <c r="A268" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B268" t="s">
+      <c r="B268" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C268" s="1">
@@ -5765,7 +5765,7 @@
       <c r="A269" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B269" t="s">
+      <c r="B269" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C269" s="1">
@@ -5791,7 +5791,7 @@
       <c r="A270" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B270" t="s">
+      <c r="B270" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C270" s="1">
@@ -5817,7 +5817,7 @@
       <c r="A271" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B271" t="s">
+      <c r="B271" s="1" t="s">
         <v>141</v>
       </c>
       <c r="C271" s="1">
@@ -5843,7 +5843,7 @@
       <c r="A272" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B272" t="s">
+      <c r="B272" s="1" t="s">
         <v>142</v>
       </c>
       <c r="C272" s="1">
@@ -5869,7 +5869,7 @@
       <c r="A273" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B273" t="s">
+      <c r="B273" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C273" s="1">
@@ -5895,7 +5895,7 @@
       <c r="A274" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B274" t="s">
+      <c r="B274" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C274" s="1">
@@ -5921,7 +5921,7 @@
       <c r="A275" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B275" t="s">
+      <c r="B275" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C275" s="1">
@@ -5947,7 +5947,7 @@
       <c r="A276" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B276" t="s">
+      <c r="B276" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C276" s="1">
@@ -5973,7 +5973,7 @@
       <c r="A277" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B277" t="s">
+      <c r="B277" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C277" s="1">
@@ -5999,7 +5999,7 @@
       <c r="A278" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B278" t="s">
+      <c r="B278" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C278" s="1">
@@ -6025,7 +6025,7 @@
       <c r="A279" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B279" t="s">
+      <c r="B279" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C279" s="1">
@@ -6051,7 +6051,7 @@
       <c r="A280" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B280" t="s">
+      <c r="B280" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C280" s="1">
@@ -6077,7 +6077,7 @@
       <c r="A281" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B281" t="s">
+      <c r="B281" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C281" s="1">
@@ -6103,7 +6103,7 @@
       <c r="A282" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B282" t="s">
+      <c r="B282" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C282" s="1">
@@ -6157,7 +6157,7 @@
       <c r="A286" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B286" t="s">
+      <c r="B286" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C286" s="1">
@@ -6183,7 +6183,7 @@
       <c r="A287" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B287" t="s">
+      <c r="B287" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C287" s="1">
@@ -6209,7 +6209,7 @@
       <c r="A288" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B288" t="s">
+      <c r="B288" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C288" s="1">
@@ -6235,7 +6235,7 @@
       <c r="A289" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B289" t="s">
+      <c r="B289" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C289" s="1">
@@ -6261,7 +6261,7 @@
       <c r="A290" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B290" t="s">
+      <c r="B290" s="1" t="s">
         <v>141</v>
       </c>
       <c r="C290" s="1">
@@ -6287,7 +6287,7 @@
       <c r="A291" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B291" t="s">
+      <c r="B291" s="1" t="s">
         <v>142</v>
       </c>
       <c r="C291" s="1">
@@ -6313,7 +6313,7 @@
       <c r="A292" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B292" t="s">
+      <c r="B292" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C292" s="1">
@@ -6339,7 +6339,7 @@
       <c r="A293" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B293" t="s">
+      <c r="B293" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C293" s="1">
@@ -6365,7 +6365,7 @@
       <c r="A294" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B294" t="s">
+      <c r="B294" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C294" s="1">
@@ -6391,7 +6391,7 @@
       <c r="A295" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B295" t="s">
+      <c r="B295" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C295" s="1">
@@ -6417,7 +6417,7 @@
       <c r="A296" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B296" t="s">
+      <c r="B296" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C296" s="1">
@@ -6443,7 +6443,7 @@
       <c r="A297" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B297" t="s">
+      <c r="B297" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C297" s="1">
@@ -6469,7 +6469,7 @@
       <c r="A298" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B298" t="s">
+      <c r="B298" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C298" s="1">
@@ -6495,7 +6495,7 @@
       <c r="A299" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B299" t="s">
+      <c r="B299" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C299" s="1">
@@ -6521,7 +6521,7 @@
       <c r="A300" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B300" t="s">
+      <c r="B300" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C300" s="1">
@@ -6547,7 +6547,7 @@
       <c r="A301" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B301" t="s">
+      <c r="B301" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C301" s="1">
@@ -6601,7 +6601,7 @@
       <c r="A305" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B305" t="s">
+      <c r="B305" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C305" s="1">
@@ -6627,7 +6627,7 @@
       <c r="A306" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B306" t="s">
+      <c r="B306" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C306" s="1">
@@ -6653,7 +6653,7 @@
       <c r="A307" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B307" t="s">
+      <c r="B307" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C307" s="1">
@@ -6679,7 +6679,7 @@
       <c r="A308" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B308" t="s">
+      <c r="B308" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C308" s="1">
@@ -6705,7 +6705,7 @@
       <c r="A309" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B309" t="s">
+      <c r="B309" s="1" t="s">
         <v>141</v>
       </c>
       <c r="C309" s="1">
@@ -6731,7 +6731,7 @@
       <c r="A310" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B310" t="s">
+      <c r="B310" s="1" t="s">
         <v>142</v>
       </c>
       <c r="C310" s="1">
@@ -6757,7 +6757,7 @@
       <c r="A311" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B311" t="s">
+      <c r="B311" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C311" s="1">
@@ -6783,7 +6783,7 @@
       <c r="A312" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B312" t="s">
+      <c r="B312" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C312" s="1">
@@ -6809,7 +6809,7 @@
       <c r="A313" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B313" t="s">
+      <c r="B313" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C313" s="1">
@@ -6835,7 +6835,7 @@
       <c r="A314" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B314" t="s">
+      <c r="B314" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C314" s="1">
@@ -6861,7 +6861,7 @@
       <c r="A315" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B315" t="s">
+      <c r="B315" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C315" s="1">
@@ -6887,7 +6887,7 @@
       <c r="A316" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B316" t="s">
+      <c r="B316" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C316" s="1">
@@ -6913,7 +6913,7 @@
       <c r="A317" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B317" t="s">
+      <c r="B317" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C317" s="1">
@@ -6939,7 +6939,7 @@
       <c r="A318" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B318" t="s">
+      <c r="B318" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C318" s="1">
@@ -6965,7 +6965,7 @@
       <c r="A319" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B319" t="s">
+      <c r="B319" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C319" s="1">
@@ -6991,7 +6991,7 @@
       <c r="A320" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B320" t="s">
+      <c r="B320" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C320" s="1">
@@ -7045,7 +7045,7 @@
       <c r="A324" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B324" t="s">
+      <c r="B324" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C324" s="1">
@@ -7071,7 +7071,7 @@
       <c r="A325" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B325" t="s">
+      <c r="B325" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C325" s="1">
@@ -7097,7 +7097,7 @@
       <c r="A326" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B326" t="s">
+      <c r="B326" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C326" s="1">
@@ -7123,7 +7123,7 @@
       <c r="A327" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B327" t="s">
+      <c r="B327" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C327" s="1">
@@ -7149,7 +7149,7 @@
       <c r="A328" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B328" t="s">
+      <c r="B328" s="1" t="s">
         <v>141</v>
       </c>
       <c r="C328" s="1">
@@ -7175,7 +7175,7 @@
       <c r="A329" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B329" t="s">
+      <c r="B329" s="1" t="s">
         <v>142</v>
       </c>
       <c r="C329" s="1">
@@ -7201,7 +7201,7 @@
       <c r="A330" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B330" t="s">
+      <c r="B330" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C330" s="1">
@@ -7227,7 +7227,7 @@
       <c r="A331" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B331" t="s">
+      <c r="B331" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C331" s="1">
@@ -7253,7 +7253,7 @@
       <c r="A332" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B332" t="s">
+      <c r="B332" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C332" s="1">
@@ -7279,7 +7279,7 @@
       <c r="A333" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B333" t="s">
+      <c r="B333" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C333" s="1">
@@ -7305,7 +7305,7 @@
       <c r="A334" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B334" t="s">
+      <c r="B334" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C334" s="1">
@@ -7331,7 +7331,7 @@
       <c r="A335" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B335" t="s">
+      <c r="B335" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C335" s="1">
@@ -7357,7 +7357,7 @@
       <c r="A336" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B336" t="s">
+      <c r="B336" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C336" s="1">
@@ -7383,7 +7383,7 @@
       <c r="A337" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B337" t="s">
+      <c r="B337" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C337" s="1">
@@ -7409,7 +7409,7 @@
       <c r="A338" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B338" t="s">
+      <c r="B338" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C338" s="1">
@@ -7435,7 +7435,7 @@
       <c r="A339" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B339" t="s">
+      <c r="B339" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C339" s="1">
@@ -7489,7 +7489,7 @@
       <c r="A343" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B343" t="s">
+      <c r="B343" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C343" s="1">
@@ -7515,7 +7515,7 @@
       <c r="A344" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B344" t="s">
+      <c r="B344" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C344" s="1">
@@ -7541,7 +7541,7 @@
       <c r="A345" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B345" t="s">
+      <c r="B345" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C345" s="1">
@@ -7567,7 +7567,7 @@
       <c r="A346" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B346" t="s">
+      <c r="B346" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C346" s="1">
@@ -7593,7 +7593,7 @@
       <c r="A347" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B347" t="s">
+      <c r="B347" s="1" t="s">
         <v>141</v>
       </c>
       <c r="C347" s="1">
@@ -7619,7 +7619,7 @@
       <c r="A348" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B348" t="s">
+      <c r="B348" s="1" t="s">
         <v>142</v>
       </c>
       <c r="C348" s="1">
@@ -7645,7 +7645,7 @@
       <c r="A349" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B349" t="s">
+      <c r="B349" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C349" s="1">
@@ -7671,7 +7671,7 @@
       <c r="A350" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B350" t="s">
+      <c r="B350" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C350" s="1">
@@ -7697,7 +7697,7 @@
       <c r="A351" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B351" t="s">
+      <c r="B351" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C351" s="1">
@@ -7723,7 +7723,7 @@
       <c r="A352" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B352" t="s">
+      <c r="B352" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C352" s="1">
@@ -7749,7 +7749,7 @@
       <c r="A353" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B353" t="s">
+      <c r="B353" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C353" s="1">
@@ -7775,7 +7775,7 @@
       <c r="A354" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B354" t="s">
+      <c r="B354" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C354" s="1">
@@ -7801,7 +7801,7 @@
       <c r="A355" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B355" t="s">
+      <c r="B355" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C355" s="1">
@@ -7827,7 +7827,7 @@
       <c r="A356" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B356" t="s">
+      <c r="B356" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C356" s="1">
@@ -7853,7 +7853,7 @@
       <c r="A357" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B357" t="s">
+      <c r="B357" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C357" s="1">
@@ -7879,7 +7879,7 @@
       <c r="A358" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B358" t="s">
+      <c r="B358" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C358" s="1">
@@ -7933,7 +7933,7 @@
       <c r="A362" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B362" t="s">
+      <c r="B362" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C362" s="1">
@@ -7959,7 +7959,7 @@
       <c r="A363" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B363" t="s">
+      <c r="B363" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C363" s="1">
@@ -7985,7 +7985,7 @@
       <c r="A364" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B364" t="s">
+      <c r="B364" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C364" s="1">
@@ -8011,7 +8011,7 @@
       <c r="A365" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B365" t="s">
+      <c r="B365" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C365" s="1">
@@ -8037,7 +8037,7 @@
       <c r="A366" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B366" t="s">
+      <c r="B366" s="1" t="s">
         <v>141</v>
       </c>
       <c r="C366" s="1">
@@ -8063,7 +8063,7 @@
       <c r="A367" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B367" t="s">
+      <c r="B367" s="1" t="s">
         <v>142</v>
       </c>
       <c r="C367" s="1">
@@ -8089,7 +8089,7 @@
       <c r="A368" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B368" t="s">
+      <c r="B368" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C368" s="1">
@@ -8115,7 +8115,7 @@
       <c r="A369" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B369" t="s">
+      <c r="B369" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C369" s="1">
@@ -8141,7 +8141,7 @@
       <c r="A370" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B370" t="s">
+      <c r="B370" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C370" s="1">
@@ -8167,7 +8167,7 @@
       <c r="A371" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B371" t="s">
+      <c r="B371" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C371" s="1">
@@ -8193,7 +8193,7 @@
       <c r="A372" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B372" t="s">
+      <c r="B372" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C372" s="1">
@@ -8219,7 +8219,7 @@
       <c r="A373" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B373" t="s">
+      <c r="B373" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C373" s="1">
@@ -8245,7 +8245,7 @@
       <c r="A374" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B374" t="s">
+      <c r="B374" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C374" s="1">
@@ -8271,7 +8271,7 @@
       <c r="A375" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B375" t="s">
+      <c r="B375" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C375" s="1">
@@ -8297,7 +8297,7 @@
       <c r="A376" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B376" t="s">
+      <c r="B376" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C376" s="1">
@@ -8323,7 +8323,7 @@
       <c r="A377" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B377" t="s">
+      <c r="B377" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C377" s="1">

--- a/assets_output/09_logistic_regression_blocks.xlsx
+++ b/assets_output/09_logistic_regression_blocks.xlsx
@@ -49,7 +49,7 @@
     <t>rt_outcome</t>
   </si>
   <si>
-    <t>2026-06-20 12:08</t>
+    <t>2026-06-20 12:49</t>
   </si>
   <si>
     <t>2679</t>
@@ -115,7 +115,7 @@
     <t>MNLogit: 'Route outcomes after 3.08 years', table 1</t>
   </si>
   <si>
-    <t>rt_outcome = 0</t>
+    <t>rt_outcome=Insecure outcome</t>
   </si>
   <si>
     <t>Coef.</t>
@@ -172,13 +172,13 @@
     <t>MNLogit: 'Route outcomes after 3.08 years', table 2</t>
   </si>
   <si>
-    <t>rt_outcome = 1</t>
+    <t>rt_outcome=Returned to homelessness</t>
   </si>
   <si>
     <t>MNLogit: 'Route outcomes after 3.08 years', table 3</t>
   </si>
   <si>
-    <t>rt_outcome = 2</t>
+    <t>rt_outcome=Died</t>
   </si>
   <si>
     <t>MNLogit: 'Route outcomes after 3.08 years', odds ratios</t>
@@ -241,19 +241,19 @@
     <t>MNLogit: 'Outcomes 3.08 years after a person's first route started', table 1</t>
   </si>
   <si>
-    <t>cli_outcome = 0</t>
+    <t>cli_outcome=Insecure outcome</t>
   </si>
   <si>
     <t>MNLogit: 'Outcomes 3.08 years after a person's first route started', table 2</t>
   </si>
   <si>
-    <t>cli_outcome = 1</t>
+    <t>cli_outcome=Returned to homelessness</t>
   </si>
   <si>
     <t>MNLogit: 'Outcomes 3.08 years after a person's first route started', table 3</t>
   </si>
   <si>
-    <t>cli_outcome = 2</t>
+    <t>cli_outcome=Died</t>
   </si>
   <si>
     <t>MNLogit: 'Outcomes 3.08 years after a person's first route started', odds ratios</t>
@@ -313,9 +313,6 @@
     <t>has_longer_term_rt</t>
   </si>
   <si>
-    <t>2026-06-20 12:09</t>
-  </si>
-  <si>
     <t>3032</t>
   </si>
   <si>
@@ -403,6 +400,9 @@
     <t>pl_outcome</t>
   </si>
   <si>
+    <t>2026-06-20 12:50</t>
+  </si>
+  <si>
     <t>5016</t>
   </si>
   <si>
@@ -433,7 +433,7 @@
     <t>MNLogit: 'Outcomes from individual placements', table 1</t>
   </si>
   <si>
-    <t>pl_outcome = 0</t>
+    <t>pl_outcome=Internal move: forwards</t>
   </si>
   <si>
     <t>ethnicity_grouped_Black</t>
@@ -451,31 +451,31 @@
     <t>MNLogit: 'Outcomes from individual placements', table 2</t>
   </si>
   <si>
-    <t>pl_outcome = 1</t>
+    <t>pl_outcome=Internal move: sideways</t>
   </si>
   <si>
     <t>MNLogit: 'Outcomes from individual placements', table 3</t>
   </si>
   <si>
-    <t>pl_outcome = 2</t>
+    <t>pl_outcome=Internal move: backwards</t>
   </si>
   <si>
     <t>MNLogit: 'Outcomes from individual placements', table 4</t>
   </si>
   <si>
-    <t>pl_outcome = 3</t>
+    <t>pl_outcome=Returned to homelessness</t>
   </si>
   <si>
     <t>MNLogit: 'Outcomes from individual placements', table 5</t>
   </si>
   <si>
-    <t>pl_outcome = 4</t>
+    <t>pl_outcome=Insecure outcome (external)</t>
   </si>
   <si>
     <t>MNLogit: 'Outcomes from individual placements', table 6</t>
   </si>
   <si>
-    <t>pl_outcome = 5</t>
+    <t>pl_outcome=Died</t>
   </si>
   <si>
     <t>MNLogit: 'Outcomes from individual placements', odds ratios</t>
@@ -4702,7 +4702,7 @@
         <v>18</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4713,13 +4713,13 @@
         <v>3</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -4730,13 +4730,13 @@
         <v>4</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -4753,7 +4753,7 @@
         <v>21</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -4764,13 +4764,13 @@
         <v>6</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -4787,7 +4787,7 @@
         <v>23</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -4798,7 +4798,7 @@
         <v>8</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>24</v>
@@ -4809,7 +4809,7 @@
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -4880,7 +4880,7 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B213" s="1">
         <v>-1.11558867186674</v>
@@ -4995,7 +4995,7 @@
     </row>
     <row r="219" spans="1:7">
       <c r="A219" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -5077,7 +5077,7 @@
     </row>
     <row r="224" spans="1:7">
       <c r="A224" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B224" s="1">
         <v>0.2824771975296116</v>
@@ -5154,7 +5154,7 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -5196,13 +5196,13 @@
         <v>2</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -5213,13 +5213,13 @@
         <v>3</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -5230,13 +5230,13 @@
         <v>4</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -5247,13 +5247,13 @@
         <v>5</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -5264,13 +5264,13 @@
         <v>6</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -5287,7 +5287,7 @@
         <v>23</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -5309,7 +5309,7 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -5357,7 +5357,7 @@
     </row>
     <row r="243" spans="1:7">
       <c r="A243" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B243" s="1">
         <v>2.475108324951747</v>
@@ -5403,7 +5403,7 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B245" s="1">
         <v>1.172146522488462</v>
@@ -5426,7 +5426,7 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -5468,7 +5468,7 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B250" s="1">
         <v>0.0004389868297785795</v>
@@ -5488,7 +5488,7 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B251" s="1">
         <v>0.03919733536927187</v>
@@ -5528,7 +5528,7 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -5570,7 +5570,7 @@
         <v>2</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>18</v>
@@ -5587,7 +5587,7 @@
         <v>3</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>19</v>
@@ -6075,10 +6075,10 @@
     </row>
     <row r="281" spans="1:8">
       <c r="A281" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C281" s="1">
         <v>0.132899369457811</v>
@@ -6519,10 +6519,10 @@
     </row>
     <row r="300" spans="1:8">
       <c r="A300" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C300" s="1">
         <v>0.1221421410218785</v>
@@ -6963,10 +6963,10 @@
     </row>
     <row r="319" spans="1:8">
       <c r="A319" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C319" s="1">
         <v>0.2552177671192801</v>
@@ -7407,10 +7407,10 @@
     </row>
     <row r="338" spans="1:8">
       <c r="A338" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C338" s="1">
         <v>0.4220748693433146</v>
@@ -7851,10 +7851,10 @@
     </row>
     <row r="357" spans="1:8">
       <c r="A357" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C357" s="1">
         <v>0.1773128236392056</v>
@@ -8295,10 +8295,10 @@
     </row>
     <row r="376" spans="1:8">
       <c r="A376" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C376" s="1">
         <v>-0.2548184232345599</v>
@@ -8561,7 +8561,7 @@
     <row r="391" spans="1:7">
       <c r="A391" s="2"/>
       <c r="B391" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C391" s="1">
         <v>0.3243426031463325</v>
@@ -8878,7 +8878,7 @@
     <row r="407" spans="1:7">
       <c r="A407" s="2"/>
       <c r="B407" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C407" s="1">
         <v>0.4183881489014909</v>
@@ -9192,7 +9192,7 @@
     <row r="423" spans="1:7">
       <c r="A423" s="2"/>
       <c r="B423" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C423" s="1">
         <v>0.1147765647959176</v>
@@ -9500,7 +9500,7 @@
     <row r="439" spans="1:7">
       <c r="A439" s="2"/>
       <c r="B439" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C439" s="1">
         <v>0.009820048795527999</v>
@@ -9817,7 +9817,7 @@
     <row r="455" spans="1:7">
       <c r="A455" s="2"/>
       <c r="B455" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C455" s="1">
         <v>0.3090265089901769</v>
@@ -10125,7 +10125,7 @@
     <row r="471" spans="1:7">
       <c r="A471" s="2"/>
       <c r="B471" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C471" s="1">
         <v>0.552131630609431</v>

--- a/assets_output/09_logistic_regression_blocks.xlsx
+++ b/assets_output/09_logistic_regression_blocks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="179">
   <si>
     <t>MNLogit: 'Route outcomes after 3.08 years', table 0</t>
   </si>
@@ -49,7 +49,7 @@
     <t>rt_outcome</t>
   </si>
   <si>
-    <t>2026-06-20 12:49</t>
+    <t>2026-06-21 13:14</t>
   </si>
   <si>
     <t>2679</t>
@@ -208,6 +208,9 @@
     <t>cli_outcome</t>
   </si>
   <si>
+    <t>2026-06-21 13:15</t>
+  </si>
+  <si>
     <t>2014</t>
   </si>
   <si>
@@ -394,15 +397,12 @@
     <t>Logit: 'Returns within 2 years after moving to independent accommodation', odds ratios</t>
   </si>
   <si>
-    <t>MNLogit: 'Outcomes from individual placements', table 0</t>
+    <t>MNLogit: 'Outcomes from individual placements (vs independent accommodation)', table 0</t>
   </si>
   <si>
     <t>pl_outcome</t>
   </si>
   <si>
-    <t>2026-06-20 12:50</t>
-  </si>
-  <si>
     <t>5016</t>
   </si>
   <si>
@@ -430,7 +430,7 @@
     <t>1.6272e-190</t>
   </si>
   <si>
-    <t>MNLogit: 'Outcomes from individual placements', table 1</t>
+    <t>MNLogit: 'Outcomes from individual placements (vs independent accommodation)', table 1</t>
   </si>
   <si>
     <t>pl_outcome=Internal move: forwards</t>
@@ -448,37 +448,37 @@
     <t>mental_health</t>
   </si>
   <si>
-    <t>MNLogit: 'Outcomes from individual placements', table 2</t>
+    <t>MNLogit: 'Outcomes from individual placements (vs independent accommodation)', table 2</t>
   </si>
   <si>
     <t>pl_outcome=Internal move: sideways</t>
   </si>
   <si>
-    <t>MNLogit: 'Outcomes from individual placements', table 3</t>
+    <t>MNLogit: 'Outcomes from individual placements (vs independent accommodation)', table 3</t>
   </si>
   <si>
     <t>pl_outcome=Internal move: backwards</t>
   </si>
   <si>
-    <t>MNLogit: 'Outcomes from individual placements', table 4</t>
+    <t>MNLogit: 'Outcomes from individual placements (vs independent accommodation)', table 4</t>
   </si>
   <si>
     <t>pl_outcome=Returned to homelessness</t>
   </si>
   <si>
-    <t>MNLogit: 'Outcomes from individual placements', table 5</t>
+    <t>MNLogit: 'Outcomes from individual placements (vs independent accommodation)', table 5</t>
   </si>
   <si>
     <t>pl_outcome=Insecure outcome (external)</t>
   </si>
   <si>
-    <t>MNLogit: 'Outcomes from individual placements', table 6</t>
+    <t>MNLogit: 'Outcomes from individual placements (vs independent accommodation)', table 6</t>
   </si>
   <si>
     <t>pl_outcome=Died</t>
   </si>
   <si>
-    <t>MNLogit: 'Outcomes from individual placements', odds ratios</t>
+    <t>MNLogit: 'Outcomes from individual placements (vs independent accommodation)', odds ratios</t>
   </si>
   <si>
     <t>Internal move: forwards</t>
@@ -491,6 +491,66 @@
   </si>
   <si>
     <t>Insecure outcome (external)</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes from individual placements (vs. forwards moves)', table 0</t>
+  </si>
+  <si>
+    <t>2026-06-21 13:16</t>
+  </si>
+  <si>
+    <t>5191</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>5113</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>17455.0005</t>
+  </si>
+  <si>
+    <t>17966.2657</t>
+  </si>
+  <si>
+    <t>-8649.5</t>
+  </si>
+  <si>
+    <t>-9247.8</t>
+  </si>
+  <si>
+    <t>2.4311e-203</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes from individual placements (vs. forwards moves)', table 1</t>
+  </si>
+  <si>
+    <t>pl_outcome=Independent accommodation</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes from individual placements (vs. forwards moves)', table 2</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes from individual placements (vs. forwards moves)', table 3</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes from individual placements (vs. forwards moves)', table 4</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes from individual placements (vs. forwards moves)', table 5</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes from individual placements (vs. forwards moves)', table 6</t>
+  </si>
+  <si>
+    <t>MNLogit: 'Outcomes from individual placements (vs. forwards moves)', odds ratios</t>
+  </si>
+  <si>
+    <t>Independent accommodation</t>
   </si>
 </sst>
 </file>
@@ -852,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H476"/>
+  <dimension ref="A1:H664"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="8" width="9.140625" style="1"/>
@@ -2690,7 +2750,7 @@
         <v>18</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2701,13 +2761,13 @@
         <v>3</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2718,13 +2778,13 @@
         <v>4</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2735,13 +2795,13 @@
         <v>5</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -2752,13 +2812,13 @@
         <v>6</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -2775,7 +2835,7 @@
         <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -2786,7 +2846,7 @@
         <v>8</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>24</v>
@@ -2797,12 +2857,12 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="B102" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>34</v>
@@ -3059,12 +3119,12 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="B114" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>34</v>
@@ -3321,12 +3381,12 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="B126" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>34</v>
@@ -3583,7 +3643,7 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -4151,7 +4211,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -4176,7 +4236,7 @@
         <v>1</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>17</v>
@@ -4193,13 +4253,13 @@
         <v>2</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -4210,13 +4270,13 @@
         <v>3</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -4227,13 +4287,13 @@
         <v>4</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -4244,13 +4304,13 @@
         <v>5</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -4261,13 +4321,13 @@
         <v>6</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -4284,7 +4344,7 @@
         <v>23</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -4295,7 +4355,7 @@
         <v>8</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>24</v>
@@ -4306,7 +4366,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -4317,10 +4377,10 @@
         <v>35</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>38</v>
@@ -4492,7 +4552,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -4654,7 +4714,7 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4679,7 +4739,7 @@
         <v>1</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>17</v>
@@ -4696,13 +4756,13 @@
         <v>2</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4713,13 +4773,13 @@
         <v>3</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -4730,13 +4790,13 @@
         <v>4</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -4747,13 +4807,13 @@
         <v>5</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -4764,13 +4824,13 @@
         <v>6</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -4787,7 +4847,7 @@
         <v>23</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -4798,7 +4858,7 @@
         <v>8</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>24</v>
@@ -4809,7 +4869,7 @@
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -4820,10 +4880,10 @@
         <v>35</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>38</v>
@@ -4880,7 +4940,7 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B213" s="1">
         <v>-1.11558867186674</v>
@@ -4995,7 +5055,7 @@
     </row>
     <row r="219" spans="1:7">
       <c r="A219" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -5077,7 +5137,7 @@
     </row>
     <row r="224" spans="1:7">
       <c r="A224" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B224" s="1">
         <v>0.2824771975296116</v>
@@ -5154,7 +5214,7 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -5179,7 +5239,7 @@
         <v>1</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>17</v>
@@ -5196,13 +5256,13 @@
         <v>2</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -5213,13 +5273,13 @@
         <v>3</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -5230,13 +5290,13 @@
         <v>4</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -5247,13 +5307,13 @@
         <v>5</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -5264,13 +5324,13 @@
         <v>6</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -5287,7 +5347,7 @@
         <v>23</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -5309,7 +5369,7 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -5320,10 +5380,10 @@
         <v>35</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>38</v>
@@ -5357,7 +5417,7 @@
     </row>
     <row r="243" spans="1:7">
       <c r="A243" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B243" s="1">
         <v>2.475108324951747</v>
@@ -5403,7 +5463,7 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B245" s="1">
         <v>1.172146522488462</v>
@@ -5426,7 +5486,7 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -5468,7 +5528,7 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B250" s="1">
         <v>0.0004389868297785795</v>
@@ -5488,7 +5548,7 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B251" s="1">
         <v>0.03919733536927187</v>
@@ -5528,7 +5588,7 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -5570,7 +5630,7 @@
         <v>2</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>18</v>
@@ -5587,7 +5647,7 @@
         <v>3</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>19</v>
@@ -5672,7 +5732,7 @@
         <v>8</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>24</v>
@@ -6075,10 +6135,10 @@
     </row>
     <row r="281" spans="1:8">
       <c r="A281" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C281" s="1">
         <v>0.132899369457811</v>
@@ -6519,10 +6579,10 @@
     </row>
     <row r="300" spans="1:8">
       <c r="A300" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C300" s="1">
         <v>0.1221421410218785</v>
@@ -6963,10 +7023,10 @@
     </row>
     <row r="319" spans="1:8">
       <c r="A319" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C319" s="1">
         <v>0.2552177671192801</v>
@@ -7407,10 +7467,10 @@
     </row>
     <row r="338" spans="1:8">
       <c r="A338" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C338" s="1">
         <v>0.4220748693433146</v>
@@ -7851,10 +7911,10 @@
     </row>
     <row r="357" spans="1:8">
       <c r="A357" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C357" s="1">
         <v>0.1773128236392056</v>
@@ -8295,10 +8355,10 @@
     </row>
     <row r="376" spans="1:8">
       <c r="A376" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C376" s="1">
         <v>-0.2548184232345599</v>
@@ -8561,7 +8621,7 @@
     <row r="391" spans="1:7">
       <c r="A391" s="2"/>
       <c r="B391" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C391" s="1">
         <v>0.3243426031463325</v>
@@ -8878,7 +8938,7 @@
     <row r="407" spans="1:7">
       <c r="A407" s="2"/>
       <c r="B407" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C407" s="1">
         <v>0.4183881489014909</v>
@@ -9192,7 +9252,7 @@
     <row r="423" spans="1:7">
       <c r="A423" s="2"/>
       <c r="B423" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C423" s="1">
         <v>0.1147765647959176</v>
@@ -9500,7 +9560,7 @@
     <row r="439" spans="1:7">
       <c r="A439" s="2"/>
       <c r="B439" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C439" s="1">
         <v>0.009820048795527999</v>
@@ -9817,7 +9877,7 @@
     <row r="455" spans="1:7">
       <c r="A455" s="2"/>
       <c r="B455" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C455" s="1">
         <v>0.3090265089901769</v>
@@ -10125,7 +10185,7 @@
     <row r="471" spans="1:7">
       <c r="A471" s="2"/>
       <c r="B471" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C471" s="1">
         <v>0.552131630609431</v>
@@ -10236,8 +10296,3893 @@
         <v>2.136383465068589</v>
       </c>
     </row>
+    <row r="478" spans="1:7">
+      <c r="A478" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7">
+      <c r="B479" s="2">
+        <v>0</v>
+      </c>
+      <c r="C479" s="2">
+        <v>1</v>
+      </c>
+      <c r="D479" s="2">
+        <v>2</v>
+      </c>
+      <c r="E479" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7">
+      <c r="A480" s="2">
+        <v>0</v>
+      </c>
+      <c r="B480" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C480" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D480" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E480" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8">
+      <c r="A481" s="2">
+        <v>1</v>
+      </c>
+      <c r="B481" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C481" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D481" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E481" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8">
+      <c r="A482" s="2">
+        <v>2</v>
+      </c>
+      <c r="B482" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C482" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D482" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E482" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8">
+      <c r="A483" s="2">
+        <v>3</v>
+      </c>
+      <c r="B483" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C483" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D483" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E483" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8">
+      <c r="A484" s="2">
+        <v>4</v>
+      </c>
+      <c r="B484" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C484" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D484" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E484" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8">
+      <c r="A485" s="2">
+        <v>5</v>
+      </c>
+      <c r="B485" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C485" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D485" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E485" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8">
+      <c r="A486" s="2">
+        <v>6</v>
+      </c>
+      <c r="B486" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C486" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D486" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E486" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8">
+      <c r="A487" s="2">
+        <v>7</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C487" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D487" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E487" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8">
+      <c r="A489" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8">
+      <c r="B490" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C490" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D490" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E490" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F490" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G490" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H490" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8">
+      <c r="A491" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B491" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C491" s="1">
+        <v>0.2249915310175884</v>
+      </c>
+      <c r="D491" s="1">
+        <v>0.103953880740101</v>
+      </c>
+      <c r="E491" s="1">
+        <v>2.164339892034413</v>
+      </c>
+      <c r="F491" s="1">
+        <v>0.03043827325881311</v>
+      </c>
+      <c r="G491" s="1">
+        <v>0.02124566871381847</v>
+      </c>
+      <c r="H491" s="1">
+        <v>0.4287373933213583</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8">
+      <c r="A492" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C492" s="1">
+        <v>0.1720144409370326</v>
+      </c>
+      <c r="D492" s="1">
+        <v>0.104765067980059</v>
+      </c>
+      <c r="E492" s="1">
+        <v>1.641906450819788</v>
+      </c>
+      <c r="F492" s="1">
+        <v>0.1006093927893698</v>
+      </c>
+      <c r="G492" s="1">
+        <v>-0.03332131914177355</v>
+      </c>
+      <c r="H492" s="1">
+        <v>0.3773502010158387</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8">
+      <c r="A493" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B493" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C493" s="1">
+        <v>-0.07852664660079063</v>
+      </c>
+      <c r="D493" s="1">
+        <v>0.09589490935179851</v>
+      </c>
+      <c r="E493" s="1">
+        <v>-0.8188823278690327</v>
+      </c>
+      <c r="F493" s="1">
+        <v>0.4128535534896671</v>
+      </c>
+      <c r="G493" s="1">
+        <v>-0.2664772152310489</v>
+      </c>
+      <c r="H493" s="1">
+        <v>0.1094239220294677</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8">
+      <c r="A494" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B494" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C494" s="1">
+        <v>0.213347653103811</v>
+      </c>
+      <c r="D494" s="1">
+        <v>0.1383477753656325</v>
+      </c>
+      <c r="E494" s="1">
+        <v>1.542111194343133</v>
+      </c>
+      <c r="F494" s="1">
+        <v>0.1230465751327812</v>
+      </c>
+      <c r="G494" s="1">
+        <v>-0.05780900395406638</v>
+      </c>
+      <c r="H494" s="1">
+        <v>0.4845043101616884</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8">
+      <c r="A495" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B495" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C495" s="1">
+        <v>-0.0975134458701325</v>
+      </c>
+      <c r="D495" s="1">
+        <v>0.235669782311117</v>
+      </c>
+      <c r="E495" s="1">
+        <v>-0.4137715277447032</v>
+      </c>
+      <c r="F495" s="1">
+        <v>0.679041437636994</v>
+      </c>
+      <c r="G495" s="1">
+        <v>-0.5594177314443165</v>
+      </c>
+      <c r="H495" s="1">
+        <v>0.3643908397040515</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8">
+      <c r="A496" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B496" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C496" s="1">
+        <v>-0.525759190566162</v>
+      </c>
+      <c r="D496" s="1">
+        <v>0.1475290550568114</v>
+      </c>
+      <c r="E496" s="1">
+        <v>-3.56376708549851</v>
+      </c>
+      <c r="F496" s="1">
+        <v>0.0003655703611464461</v>
+      </c>
+      <c r="G496" s="1">
+        <v>-0.8149108251507392</v>
+      </c>
+      <c r="H496" s="1">
+        <v>-0.2366075559815849</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8">
+      <c r="A497" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B497" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C497" s="1">
+        <v>-0.1008073201356094</v>
+      </c>
+      <c r="D497" s="1">
+        <v>0.09546461901523623</v>
+      </c>
+      <c r="E497" s="1">
+        <v>-1.055965248439534</v>
+      </c>
+      <c r="F497" s="1">
+        <v>0.2909840920523293</v>
+      </c>
+      <c r="G497" s="1">
+        <v>-0.28791453520331</v>
+      </c>
+      <c r="H497" s="1">
+        <v>0.08629989493209123</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8">
+      <c r="A498" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B498" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C498" s="1">
+        <v>-0.2458702992489558</v>
+      </c>
+      <c r="D498" s="1">
+        <v>0.09664387816431816</v>
+      </c>
+      <c r="E498" s="1">
+        <v>-2.544085604997312</v>
+      </c>
+      <c r="F498" s="1">
+        <v>0.01095642293665167</v>
+      </c>
+      <c r="G498" s="1">
+        <v>-0.4352888197772964</v>
+      </c>
+      <c r="H498" s="1">
+        <v>-0.0564517787206153</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8">
+      <c r="A499" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B499" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C499" s="1">
+        <v>-0.8785684007948122</v>
+      </c>
+      <c r="D499" s="1">
+        <v>0.09649497345459762</v>
+      </c>
+      <c r="E499" s="1">
+        <v>-9.104810015914376</v>
+      </c>
+      <c r="F499" s="1">
+        <v>8.641755080100111E-20</v>
+      </c>
+      <c r="G499" s="1">
+        <v>-1.067695073454972</v>
+      </c>
+      <c r="H499" s="1">
+        <v>-0.6894417281346523</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8">
+      <c r="A500" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B500" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C500" s="1">
+        <v>-0.08132550156481841</v>
+      </c>
+      <c r="D500" s="1">
+        <v>0.1382832423833657</v>
+      </c>
+      <c r="E500" s="1">
+        <v>-0.5881081479081747</v>
+      </c>
+      <c r="F500" s="1">
+        <v>0.5564597044586419</v>
+      </c>
+      <c r="G500" s="1">
+        <v>-0.3523556763016379</v>
+      </c>
+      <c r="H500" s="1">
+        <v>0.1897046731720011</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8">
+      <c r="A501" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B501" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C501" s="1">
+        <v>-1.345701620395633</v>
+      </c>
+      <c r="D501" s="1">
+        <v>0.5382528342111568</v>
+      </c>
+      <c r="E501" s="1">
+        <v>-2.500129186254715</v>
+      </c>
+      <c r="F501" s="1">
+        <v>0.01241480255182997</v>
+      </c>
+      <c r="G501" s="1">
+        <v>-2.400657790026109</v>
+      </c>
+      <c r="H501" s="1">
+        <v>-0.2907454507651572</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8">
+      <c r="A502" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B502" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C502" s="1">
+        <v>-0.09975885052689878</v>
+      </c>
+      <c r="D502" s="1">
+        <v>0.1318545116874724</v>
+      </c>
+      <c r="E502" s="1">
+        <v>-0.7565827611826567</v>
+      </c>
+      <c r="F502" s="1">
+        <v>0.4492998724301147</v>
+      </c>
+      <c r="G502" s="1">
+        <v>-0.3581889446334604</v>
+      </c>
+      <c r="H502" s="1">
+        <v>0.1586712435796629</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8">
+      <c r="A503" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B503" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C503" s="1">
+        <v>-0.5144379452912305</v>
+      </c>
+      <c r="D503" s="1">
+        <v>0.1815404455641338</v>
+      </c>
+      <c r="E503" s="1">
+        <v>-2.833737372917773</v>
+      </c>
+      <c r="F503" s="1">
+        <v>0.004600712496250168</v>
+      </c>
+      <c r="G503" s="1">
+        <v>-0.870250680334287</v>
+      </c>
+      <c r="H503" s="1">
+        <v>-0.1586252102481741</v>
+      </c>
+    </row>
+    <row r="505" spans="1:8">
+      <c r="A505" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="506" spans="1:8">
+      <c r="B506" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C506" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D506" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E506" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F506" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G506" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H506" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8">
+      <c r="A507" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C507" s="1">
+        <v>-1.564522656474258</v>
+      </c>
+      <c r="D507" s="1">
+        <v>0.1268952915924901</v>
+      </c>
+      <c r="E507" s="1">
+        <v>-12.32924119437422</v>
+      </c>
+      <c r="F507" s="1">
+        <v>6.303753463585649E-35</v>
+      </c>
+      <c r="G507" s="1">
+        <v>-1.813232857803247</v>
+      </c>
+      <c r="H507" s="1">
+        <v>-1.315812455145269</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8">
+      <c r="A508" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B508" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C508" s="1">
+        <v>-0.2751810024799334</v>
+      </c>
+      <c r="D508" s="1">
+        <v>0.1098995809319774</v>
+      </c>
+      <c r="E508" s="1">
+        <v>-2.503931317538484</v>
+      </c>
+      <c r="F508" s="1">
+        <v>0.01228218742131392</v>
+      </c>
+      <c r="G508" s="1">
+        <v>-0.490580223022654</v>
+      </c>
+      <c r="H508" s="1">
+        <v>-0.05978178193721284</v>
+      </c>
+    </row>
+    <row r="509" spans="1:8">
+      <c r="A509" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B509" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C509" s="1">
+        <v>0.3520332992925154</v>
+      </c>
+      <c r="D509" s="1">
+        <v>0.09125598429002252</v>
+      </c>
+      <c r="E509" s="1">
+        <v>3.857646181029741</v>
+      </c>
+      <c r="F509" s="1">
+        <v>0.0001144842107323911</v>
+      </c>
+      <c r="G509" s="1">
+        <v>0.1731748567103183</v>
+      </c>
+      <c r="H509" s="1">
+        <v>0.5308917418747126</v>
+      </c>
+    </row>
+    <row r="510" spans="1:8">
+      <c r="A510" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B510" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C510" s="1">
+        <v>-0.6150788002864479</v>
+      </c>
+      <c r="D510" s="1">
+        <v>0.20272506463271</v>
+      </c>
+      <c r="E510" s="1">
+        <v>-3.034054034713594</v>
+      </c>
+      <c r="F510" s="1">
+        <v>0.002412912081644074</v>
+      </c>
+      <c r="G510" s="1">
+        <v>-1.012412625730114</v>
+      </c>
+      <c r="H510" s="1">
+        <v>-0.2177449748427815</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8">
+      <c r="A511" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B511" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C511" s="1">
+        <v>-0.3205837031620951</v>
+      </c>
+      <c r="D511" s="1">
+        <v>0.2666424776891327</v>
+      </c>
+      <c r="E511" s="1">
+        <v>-1.202297945700348</v>
+      </c>
+      <c r="F511" s="1">
+        <v>0.2292481125687863</v>
+      </c>
+      <c r="G511" s="1">
+        <v>-0.8431933561813201</v>
+      </c>
+      <c r="H511" s="1">
+        <v>0.2020259498571299</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8">
+      <c r="A512" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B512" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C512" s="1">
+        <v>0.599932705289018</v>
+      </c>
+      <c r="D512" s="1">
+        <v>0.1063692071787075</v>
+      </c>
+      <c r="E512" s="1">
+        <v>5.640097554559095</v>
+      </c>
+      <c r="F512" s="1">
+        <v>1.699538476781488E-08</v>
+      </c>
+      <c r="G512" s="1">
+        <v>0.3914528901546719</v>
+      </c>
+      <c r="H512" s="1">
+        <v>0.8084125204233641</v>
+      </c>
+    </row>
+    <row r="513" spans="1:8">
+      <c r="A513" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B513" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C513" s="1">
+        <v>0.174499156682957</v>
+      </c>
+      <c r="D513" s="1">
+        <v>0.08870653098542031</v>
+      </c>
+      <c r="E513" s="1">
+        <v>1.967151175279726</v>
+      </c>
+      <c r="F513" s="1">
+        <v>0.0491657849146158</v>
+      </c>
+      <c r="G513" s="1">
+        <v>0.000637550758046862</v>
+      </c>
+      <c r="H513" s="1">
+        <v>0.3483607626078672</v>
+      </c>
+    </row>
+    <row r="514" spans="1:8">
+      <c r="A514" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B514" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C514" s="1">
+        <v>0.07792513011951603</v>
+      </c>
+      <c r="D514" s="1">
+        <v>0.1038844712090115</v>
+      </c>
+      <c r="E514" s="1">
+        <v>0.7501133635529967</v>
+      </c>
+      <c r="F514" s="1">
+        <v>0.4531864316378061</v>
+      </c>
+      <c r="G514" s="1">
+        <v>-0.1256846920031346</v>
+      </c>
+      <c r="H514" s="1">
+        <v>0.2815349522421666</v>
+      </c>
+    </row>
+    <row r="515" spans="1:8">
+      <c r="A515" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C515" s="1">
+        <v>1.262442661138902</v>
+      </c>
+      <c r="D515" s="1">
+        <v>0.104279670996257</v>
+      </c>
+      <c r="E515" s="1">
+        <v>12.1063161120274</v>
+      </c>
+      <c r="F515" s="1">
+        <v>9.778824029820875E-34</v>
+      </c>
+      <c r="G515" s="1">
+        <v>1.058058261666552</v>
+      </c>
+      <c r="H515" s="1">
+        <v>1.466827060611252</v>
+      </c>
+    </row>
+    <row r="516" spans="1:8">
+      <c r="A516" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C516" s="1">
+        <v>0.7258116961408411</v>
+      </c>
+      <c r="D516" s="1">
+        <v>0.1044928608339838</v>
+      </c>
+      <c r="E516" s="1">
+        <v>6.946041005557272</v>
+      </c>
+      <c r="F516" s="1">
+        <v>3.756796141150703E-12</v>
+      </c>
+      <c r="G516" s="1">
+        <v>0.5210094522646768</v>
+      </c>
+      <c r="H516" s="1">
+        <v>0.9306139400170054</v>
+      </c>
+    </row>
+    <row r="517" spans="1:8">
+      <c r="A517" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C517" s="1">
+        <v>0.3476180579097375</v>
+      </c>
+      <c r="D517" s="1">
+        <v>0.2336072475304196</v>
+      </c>
+      <c r="E517" s="1">
+        <v>1.488044834158974</v>
+      </c>
+      <c r="F517" s="1">
+        <v>0.1367390703151118</v>
+      </c>
+      <c r="G517" s="1">
+        <v>-0.1102437337774183</v>
+      </c>
+      <c r="H517" s="1">
+        <v>0.8054798495968933</v>
+      </c>
+    </row>
+    <row r="518" spans="1:8">
+      <c r="A518" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C518" s="1">
+        <v>-0.01724535193601182</v>
+      </c>
+      <c r="D518" s="1">
+        <v>0.1242742669182388</v>
+      </c>
+      <c r="E518" s="1">
+        <v>-0.1387684865391939</v>
+      </c>
+      <c r="F518" s="1">
+        <v>0.8896330971005005</v>
+      </c>
+      <c r="G518" s="1">
+        <v>-0.2608184393008774</v>
+      </c>
+      <c r="H518" s="1">
+        <v>0.2263277354288538</v>
+      </c>
+    </row>
+    <row r="519" spans="1:8">
+      <c r="A519" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C519" s="1">
+        <v>-0.02898443468592734</v>
+      </c>
+      <c r="D519" s="1">
+        <v>0.1354511552089917</v>
+      </c>
+      <c r="E519" s="1">
+        <v>-0.2139844037594687</v>
+      </c>
+      <c r="F519" s="1">
+        <v>0.83055921949477</v>
+      </c>
+      <c r="G519" s="1">
+        <v>-0.294463820559896</v>
+      </c>
+      <c r="H519" s="1">
+        <v>0.2364949511880413</v>
+      </c>
+    </row>
+    <row r="521" spans="1:8">
+      <c r="A521" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="522" spans="1:8">
+      <c r="B522" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C522" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D522" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E522" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F522" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G522" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H522" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8">
+      <c r="A523" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C523" s="1">
+        <v>-1.285838296902032</v>
+      </c>
+      <c r="D523" s="1">
+        <v>0.1311472820027768</v>
+      </c>
+      <c r="E523" s="1">
+        <v>-9.804536375178605</v>
+      </c>
+      <c r="F523" s="1">
+        <v>1.076401634377507E-22</v>
+      </c>
+      <c r="G523" s="1">
+        <v>-1.542882246297792</v>
+      </c>
+      <c r="H523" s="1">
+        <v>-1.028794347506271</v>
+      </c>
+    </row>
+    <row r="524" spans="1:8">
+      <c r="A524" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C524" s="1">
+        <v>-0.2121496299955544</v>
+      </c>
+      <c r="D524" s="1">
+        <v>0.1269000986881279</v>
+      </c>
+      <c r="E524" s="1">
+        <v>-1.671784594249508</v>
+      </c>
+      <c r="F524" s="1">
+        <v>0.09456680576091746</v>
+      </c>
+      <c r="G524" s="1">
+        <v>-0.4608692530588636</v>
+      </c>
+      <c r="H524" s="1">
+        <v>0.03656999306775477</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8">
+      <c r="A525" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C525" s="1">
+        <v>0.1785060895041023</v>
+      </c>
+      <c r="D525" s="1">
+        <v>0.1054426663177848</v>
+      </c>
+      <c r="E525" s="1">
+        <v>1.692920861524098</v>
+      </c>
+      <c r="F525" s="1">
+        <v>0.09047053184849052</v>
+      </c>
+      <c r="G525" s="1">
+        <v>-0.02815773891263063</v>
+      </c>
+      <c r="H525" s="1">
+        <v>0.3851699179208352</v>
+      </c>
+    </row>
+    <row r="526" spans="1:8">
+      <c r="A526" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C526" s="1">
+        <v>-0.7164695252610598</v>
+      </c>
+      <c r="D526" s="1">
+        <v>0.2339286018208551</v>
+      </c>
+      <c r="E526" s="1">
+        <v>-3.062770091746795</v>
+      </c>
+      <c r="F526" s="1">
+        <v>0.002192984741371619</v>
+      </c>
+      <c r="G526" s="1">
+        <v>-1.174961159783747</v>
+      </c>
+      <c r="H526" s="1">
+        <v>-0.2579778907383729</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8">
+      <c r="A527" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C527" s="1">
+        <v>0.1885684036585996</v>
+      </c>
+      <c r="D527" s="1">
+        <v>0.2587859989751609</v>
+      </c>
+      <c r="E527" s="1">
+        <v>0.7286654007765658</v>
+      </c>
+      <c r="F527" s="1">
+        <v>0.4662063620866697</v>
+      </c>
+      <c r="G527" s="1">
+        <v>-0.3186428340359351</v>
+      </c>
+      <c r="H527" s="1">
+        <v>0.6957796413531343</v>
+      </c>
+    </row>
+    <row r="528" spans="1:8">
+      <c r="A528" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C528" s="1">
+        <v>0.6004042002639752</v>
+      </c>
+      <c r="D528" s="1">
+        <v>0.1209533802064972</v>
+      </c>
+      <c r="E528" s="1">
+        <v>4.963930724705151</v>
+      </c>
+      <c r="F528" s="1">
+        <v>6.908059231390752E-07</v>
+      </c>
+      <c r="G528" s="1">
+        <v>0.3633399312508609</v>
+      </c>
+      <c r="H528" s="1">
+        <v>0.8374684692770895</v>
+      </c>
+    </row>
+    <row r="529" spans="1:8">
+      <c r="A529" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C529" s="1">
+        <v>-0.1580344194412602</v>
+      </c>
+      <c r="D529" s="1">
+        <v>0.1047321434260525</v>
+      </c>
+      <c r="E529" s="1">
+        <v>-1.508939035061786</v>
+      </c>
+      <c r="F529" s="1">
+        <v>0.131314363173481</v>
+      </c>
+      <c r="G529" s="1">
+        <v>-0.3633056485800066</v>
+      </c>
+      <c r="H529" s="1">
+        <v>0.04723680969748609</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8">
+      <c r="A530" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C530" s="1">
+        <v>-0.1430212518678175</v>
+      </c>
+      <c r="D530" s="1">
+        <v>0.1141747530555115</v>
+      </c>
+      <c r="E530" s="1">
+        <v>-1.252652167316542</v>
+      </c>
+      <c r="F530" s="1">
+        <v>0.2103323207642823</v>
+      </c>
+      <c r="G530" s="1">
+        <v>-0.3667996558003745</v>
+      </c>
+      <c r="H530" s="1">
+        <v>0.08075715206473952</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8">
+      <c r="A531" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C531" s="1">
+        <v>0.533234381099385</v>
+      </c>
+      <c r="D531" s="1">
+        <v>0.1103218186410626</v>
+      </c>
+      <c r="E531" s="1">
+        <v>4.833444441613939</v>
+      </c>
+      <c r="F531" s="1">
+        <v>1.341907416072246E-06</v>
+      </c>
+      <c r="G531" s="1">
+        <v>0.3170075898539428</v>
+      </c>
+      <c r="H531" s="1">
+        <v>0.7494611723448272</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8">
+      <c r="A532" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C532" s="1">
+        <v>1.023314050932608</v>
+      </c>
+      <c r="D532" s="1">
+        <v>0.1164189779738178</v>
+      </c>
+      <c r="E532" s="1">
+        <v>8.789924707660191</v>
+      </c>
+      <c r="F532" s="1">
+        <v>1.496602319378977E-18</v>
+      </c>
+      <c r="G532" s="1">
+        <v>0.7951370469869637</v>
+      </c>
+      <c r="H532" s="1">
+        <v>1.251491054878253</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8">
+      <c r="A533" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B533" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C533" s="1">
+        <v>-0.1383993577784189</v>
+      </c>
+      <c r="D533" s="1">
+        <v>0.303679025727264</v>
+      </c>
+      <c r="E533" s="1">
+        <v>-0.4557422345747257</v>
+      </c>
+      <c r="F533" s="1">
+        <v>0.6485753473899263</v>
+      </c>
+      <c r="G533" s="1">
+        <v>-0.7335993110640689</v>
+      </c>
+      <c r="H533" s="1">
+        <v>0.4568005955072311</v>
+      </c>
+    </row>
+    <row r="534" spans="1:8">
+      <c r="A534" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C534" s="1">
+        <v>0.291266449624504</v>
+      </c>
+      <c r="D534" s="1">
+        <v>0.1405039440260273</v>
+      </c>
+      <c r="E534" s="1">
+        <v>2.073012623549905</v>
+      </c>
+      <c r="F534" s="1">
+        <v>0.03817110476886406</v>
+      </c>
+      <c r="G534" s="1">
+        <v>0.01588377964765875</v>
+      </c>
+      <c r="H534" s="1">
+        <v>0.5666491196013492</v>
+      </c>
+    </row>
+    <row r="535" spans="1:8">
+      <c r="A535" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C535" s="1">
+        <v>-0.3479353151065283</v>
+      </c>
+      <c r="D535" s="1">
+        <v>0.1739309024485958</v>
+      </c>
+      <c r="E535" s="1">
+        <v>-2.000422640303142</v>
+      </c>
+      <c r="F535" s="1">
+        <v>0.04545464566362853</v>
+      </c>
+      <c r="G535" s="1">
+        <v>-0.6888336197043256</v>
+      </c>
+      <c r="H535" s="1">
+        <v>-0.007037010508730956</v>
+      </c>
+    </row>
+    <row r="537" spans="1:8">
+      <c r="A537" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="538" spans="1:8">
+      <c r="B538" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C538" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D538" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E538" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F538" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G538" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H538" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="539" spans="1:8">
+      <c r="A539" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B539" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C539" s="1">
+        <v>-1.608813445389444</v>
+      </c>
+      <c r="D539" s="1">
+        <v>0.1414699763169429</v>
+      </c>
+      <c r="E539" s="1">
+        <v>-11.37211928123273</v>
+      </c>
+      <c r="F539" s="1">
+        <v>5.75724982403861E-30</v>
+      </c>
+      <c r="G539" s="1">
+        <v>-1.886089503864387</v>
+      </c>
+      <c r="H539" s="1">
+        <v>-1.331537386914502</v>
+      </c>
+    </row>
+    <row r="540" spans="1:8">
+      <c r="A540" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C540" s="1">
+        <v>0.154227424551831</v>
+      </c>
+      <c r="D540" s="1">
+        <v>0.1198855560981439</v>
+      </c>
+      <c r="E540" s="1">
+        <v>1.286455429422818</v>
+      </c>
+      <c r="F540" s="1">
+        <v>0.19828416430527</v>
+      </c>
+      <c r="G540" s="1">
+        <v>-0.08074394766708728</v>
+      </c>
+      <c r="H540" s="1">
+        <v>0.3891987967707493</v>
+      </c>
+    </row>
+    <row r="541" spans="1:8">
+      <c r="A541" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C541" s="1">
+        <v>0.09753952427747316</v>
+      </c>
+      <c r="D541" s="1">
+        <v>0.1077465967920705</v>
+      </c>
+      <c r="E541" s="1">
+        <v>0.905267796677653</v>
+      </c>
+      <c r="F541" s="1">
+        <v>0.3653235325354613</v>
+      </c>
+      <c r="G541" s="1">
+        <v>-0.113639924891744</v>
+      </c>
+      <c r="H541" s="1">
+        <v>0.3087189734466903</v>
+      </c>
+    </row>
+    <row r="542" spans="1:8">
+      <c r="A542" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C542" s="1">
+        <v>0.1000252205395829</v>
+      </c>
+      <c r="D542" s="1">
+        <v>0.1852392373633804</v>
+      </c>
+      <c r="E542" s="1">
+        <v>0.5399785810139418</v>
+      </c>
+      <c r="F542" s="1">
+        <v>0.5892118038207506</v>
+      </c>
+      <c r="G542" s="1">
+        <v>-0.263037013216309</v>
+      </c>
+      <c r="H542" s="1">
+        <v>0.4630874542954748</v>
+      </c>
+    </row>
+    <row r="543" spans="1:8">
+      <c r="A543" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C543" s="1">
+        <v>0.2876073902288768</v>
+      </c>
+      <c r="D543" s="1">
+        <v>0.2593859825735187</v>
+      </c>
+      <c r="E543" s="1">
+        <v>1.108800820211475</v>
+      </c>
+      <c r="F543" s="1">
+        <v>0.2675161165776037</v>
+      </c>
+      <c r="G543" s="1">
+        <v>-0.220779793709754</v>
+      </c>
+      <c r="H543" s="1">
+        <v>0.7959945741675076</v>
+      </c>
+    </row>
+    <row r="544" spans="1:8">
+      <c r="A544" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C544" s="1">
+        <v>0.1573664407356352</v>
+      </c>
+      <c r="D544" s="1">
+        <v>0.1355040510575941</v>
+      </c>
+      <c r="E544" s="1">
+        <v>1.161341225649031</v>
+      </c>
+      <c r="F544" s="1">
+        <v>0.2455031605052839</v>
+      </c>
+      <c r="G544" s="1">
+        <v>-0.1082166190965258</v>
+      </c>
+      <c r="H544" s="1">
+        <v>0.4229495005677962</v>
+      </c>
+    </row>
+    <row r="545" spans="1:8">
+      <c r="A545" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C545" s="1">
+        <v>0.006702317118651681</v>
+      </c>
+      <c r="D545" s="1">
+        <v>0.1047058391616192</v>
+      </c>
+      <c r="E545" s="1">
+        <v>0.06401092023441296</v>
+      </c>
+      <c r="F545" s="1">
+        <v>0.9489615315521314</v>
+      </c>
+      <c r="G545" s="1">
+        <v>-0.1985173566091656</v>
+      </c>
+      <c r="H545" s="1">
+        <v>0.2119219908464689</v>
+      </c>
+    </row>
+    <row r="546" spans="1:8">
+      <c r="A546" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C546" s="1">
+        <v>0.08888038077609614</v>
+      </c>
+      <c r="D546" s="1">
+        <v>0.1208520775446927</v>
+      </c>
+      <c r="E546" s="1">
+        <v>0.7354476859798048</v>
+      </c>
+      <c r="F546" s="1">
+        <v>0.4620668891808699</v>
+      </c>
+      <c r="G546" s="1">
+        <v>-0.1479853386683433</v>
+      </c>
+      <c r="H546" s="1">
+        <v>0.3257461002205355</v>
+      </c>
+    </row>
+    <row r="547" spans="1:8">
+      <c r="A547" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B547" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C547" s="1">
+        <v>0.7761601501414654</v>
+      </c>
+      <c r="D547" s="1">
+        <v>0.1136431490427941</v>
+      </c>
+      <c r="E547" s="1">
+        <v>6.829801503029366</v>
+      </c>
+      <c r="F547" s="1">
+        <v>8.503220591470087E-12</v>
+      </c>
+      <c r="G547" s="1">
+        <v>0.5534236709278715</v>
+      </c>
+      <c r="H547" s="1">
+        <v>0.9988966293550594</v>
+      </c>
+    </row>
+    <row r="548" spans="1:8">
+      <c r="A548" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B548" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C548" s="1">
+        <v>0.1495229487029993</v>
+      </c>
+      <c r="D548" s="1">
+        <v>0.1330276603822068</v>
+      </c>
+      <c r="E548" s="1">
+        <v>1.123998935810788</v>
+      </c>
+      <c r="F548" s="1">
+        <v>0.2610134774064551</v>
+      </c>
+      <c r="G548" s="1">
+        <v>-0.1112064745937517</v>
+      </c>
+      <c r="H548" s="1">
+        <v>0.4102523719997503</v>
+      </c>
+    </row>
+    <row r="549" spans="1:8">
+      <c r="A549" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B549" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C549" s="1">
+        <v>0.1355284035128653</v>
+      </c>
+      <c r="D549" s="1">
+        <v>0.2623993830032211</v>
+      </c>
+      <c r="E549" s="1">
+        <v>0.5164966546861186</v>
+      </c>
+      <c r="F549" s="1">
+        <v>0.6055075748093981</v>
+      </c>
+      <c r="G549" s="1">
+        <v>-0.3787649367389797</v>
+      </c>
+      <c r="H549" s="1">
+        <v>0.6498217437647102</v>
+      </c>
+    </row>
+    <row r="550" spans="1:8">
+      <c r="A550" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B550" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C550" s="1">
+        <v>0.129542118501986</v>
+      </c>
+      <c r="D550" s="1">
+        <v>0.1385908124910919</v>
+      </c>
+      <c r="E550" s="1">
+        <v>0.9347092795946523</v>
+      </c>
+      <c r="F550" s="1">
+        <v>0.3499381433206767</v>
+      </c>
+      <c r="G550" s="1">
+        <v>-0.1420908825686979</v>
+      </c>
+      <c r="H550" s="1">
+        <v>0.40117511957267</v>
+      </c>
+    </row>
+    <row r="551" spans="1:8">
+      <c r="A551" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B551" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C551" s="1">
+        <v>0.1313752178525543</v>
+      </c>
+      <c r="D551" s="1">
+        <v>0.1520212273213681</v>
+      </c>
+      <c r="E551" s="1">
+        <v>0.8641899566751379</v>
+      </c>
+      <c r="F551" s="1">
+        <v>0.3874835484867725</v>
+      </c>
+      <c r="G551" s="1">
+        <v>-0.1665809125829035</v>
+      </c>
+      <c r="H551" s="1">
+        <v>0.4293313482880122</v>
+      </c>
+    </row>
+    <row r="553" spans="1:8">
+      <c r="A553" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="554" spans="1:8">
+      <c r="B554" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C554" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D554" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E554" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F554" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G554" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H554" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="555" spans="1:8">
+      <c r="A555" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B555" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C555" s="1">
+        <v>-1.347728288940703</v>
+      </c>
+      <c r="D555" s="1">
+        <v>0.1387446624185872</v>
+      </c>
+      <c r="E555" s="1">
+        <v>-9.713730715453828</v>
+      </c>
+      <c r="F555" s="1">
+        <v>2.635115730555844E-22</v>
+      </c>
+      <c r="G555" s="1">
+        <v>-1.619662830328301</v>
+      </c>
+      <c r="H555" s="1">
+        <v>-1.075793747553104</v>
+      </c>
+    </row>
+    <row r="556" spans="1:8">
+      <c r="A556" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B556" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C556" s="1">
+        <v>-0.04163407751758721</v>
+      </c>
+      <c r="D556" s="1">
+        <v>0.1322882452205772</v>
+      </c>
+      <c r="E556" s="1">
+        <v>-0.3147224263816232</v>
+      </c>
+      <c r="F556" s="1">
+        <v>0.7529724151289838</v>
+      </c>
+      <c r="G556" s="1">
+        <v>-0.3009142737279213</v>
+      </c>
+      <c r="H556" s="1">
+        <v>0.2176461186927469</v>
+      </c>
+    </row>
+    <row r="557" spans="1:8">
+      <c r="A557" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B557" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C557" s="1">
+        <v>0.304569205652149</v>
+      </c>
+      <c r="D557" s="1">
+        <v>0.1133375920597473</v>
+      </c>
+      <c r="E557" s="1">
+        <v>2.687274364286756</v>
+      </c>
+      <c r="F557" s="1">
+        <v>0.007203775417692744</v>
+      </c>
+      <c r="G557" s="1">
+        <v>0.08243160712055156</v>
+      </c>
+      <c r="H557" s="1">
+        <v>0.5267068041837465</v>
+      </c>
+    </row>
+    <row r="558" spans="1:8">
+      <c r="A558" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C558" s="1">
+        <v>-0.4877078073534579</v>
+      </c>
+      <c r="D558" s="1">
+        <v>0.2234224874805275</v>
+      </c>
+      <c r="E558" s="1">
+        <v>-2.182894895017961</v>
+      </c>
+      <c r="F558" s="1">
+        <v>0.02904355107345591</v>
+      </c>
+      <c r="G558" s="1">
+        <v>-0.9256078361516429</v>
+      </c>
+      <c r="H558" s="1">
+        <v>-0.0498077785552728</v>
+      </c>
+    </row>
+    <row r="559" spans="1:8">
+      <c r="A559" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C559" s="1">
+        <v>-0.175897156978274</v>
+      </c>
+      <c r="D559" s="1">
+        <v>0.311396529884221</v>
+      </c>
+      <c r="E559" s="1">
+        <v>-0.5648655013711088</v>
+      </c>
+      <c r="F559" s="1">
+        <v>0.5721652503803307</v>
+      </c>
+      <c r="G559" s="1">
+        <v>-0.7862231404620978</v>
+      </c>
+      <c r="H559" s="1">
+        <v>0.4344288265055499</v>
+      </c>
+    </row>
+    <row r="560" spans="1:8">
+      <c r="A560" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B560" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C560" s="1">
+        <v>0.6569371090209135</v>
+      </c>
+      <c r="D560" s="1">
+        <v>0.1310466025230827</v>
+      </c>
+      <c r="E560" s="1">
+        <v>5.01300374349804</v>
+      </c>
+      <c r="F560" s="1">
+        <v>5.358685390828512E-07</v>
+      </c>
+      <c r="G560" s="1">
+        <v>0.4000904877793356</v>
+      </c>
+      <c r="H560" s="1">
+        <v>0.9137837302624914</v>
+      </c>
+    </row>
+    <row r="561" spans="1:8">
+      <c r="A561" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B561" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C561" s="1">
+        <v>0.05300476067247347</v>
+      </c>
+      <c r="D561" s="1">
+        <v>0.1128499364410048</v>
+      </c>
+      <c r="E561" s="1">
+        <v>0.4696924282290854</v>
+      </c>
+      <c r="F561" s="1">
+        <v>0.6385747782972211</v>
+      </c>
+      <c r="G561" s="1">
+        <v>-0.16817705040953</v>
+      </c>
+      <c r="H561" s="1">
+        <v>0.274186571754477</v>
+      </c>
+    </row>
+    <row r="562" spans="1:8">
+      <c r="A562" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C562" s="1">
+        <v>-0.04264627882691358</v>
+      </c>
+      <c r="D562" s="1">
+        <v>0.1239023550325133</v>
+      </c>
+      <c r="E562" s="1">
+        <v>-0.3441926411787957</v>
+      </c>
+      <c r="F562" s="1">
+        <v>0.7307014160917791</v>
+      </c>
+      <c r="G562" s="1">
+        <v>-0.2854904322903347</v>
+      </c>
+      <c r="H562" s="1">
+        <v>0.2001978746365075</v>
+      </c>
+    </row>
+    <row r="563" spans="1:8">
+      <c r="A563" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C563" s="1">
+        <v>0.1128019117950421</v>
+      </c>
+      <c r="D563" s="1">
+        <v>0.1143875374259375</v>
+      </c>
+      <c r="E563" s="1">
+        <v>0.9861381260006405</v>
+      </c>
+      <c r="F563" s="1">
+        <v>0.3240653368093933</v>
+      </c>
+      <c r="G563" s="1">
+        <v>-0.1113935418400228</v>
+      </c>
+      <c r="H563" s="1">
+        <v>0.3369973654301071</v>
+      </c>
+    </row>
+    <row r="564" spans="1:8">
+      <c r="A564" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B564" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C564" s="1">
+        <v>0.4219396208815869</v>
+      </c>
+      <c r="D564" s="1">
+        <v>0.137693573417812</v>
+      </c>
+      <c r="E564" s="1">
+        <v>3.064337793030252</v>
+      </c>
+      <c r="F564" s="1">
+        <v>0.002181524385068261</v>
+      </c>
+      <c r="G564" s="1">
+        <v>0.1520651760800537</v>
+      </c>
+      <c r="H564" s="1">
+        <v>0.6918140656831202</v>
+      </c>
+    </row>
+    <row r="565" spans="1:8">
+      <c r="A565" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C565" s="1">
+        <v>-0.5644110210722605</v>
+      </c>
+      <c r="D565" s="1">
+        <v>0.3782105996043711</v>
+      </c>
+      <c r="E565" s="1">
+        <v>-1.492319415856312</v>
+      </c>
+      <c r="F565" s="1">
+        <v>0.1356154291607063</v>
+      </c>
+      <c r="G565" s="1">
+        <v>-1.305690174868127</v>
+      </c>
+      <c r="H565" s="1">
+        <v>0.1768681327236057</v>
+      </c>
+    </row>
+    <row r="566" spans="1:8">
+      <c r="A566" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C566" s="1">
+        <v>0.06083883373787775</v>
+      </c>
+      <c r="D566" s="1">
+        <v>0.1539556572827789</v>
+      </c>
+      <c r="E566" s="1">
+        <v>0.3951711474046822</v>
+      </c>
+      <c r="F566" s="1">
+        <v>0.6927165844976992</v>
+      </c>
+      <c r="G566" s="1">
+        <v>-0.2409087097525606</v>
+      </c>
+      <c r="H566" s="1">
+        <v>0.3625863772283161</v>
+      </c>
+    </row>
+    <row r="567" spans="1:8">
+      <c r="A567" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C567" s="1">
+        <v>-0.04854675083489295</v>
+      </c>
+      <c r="D567" s="1">
+        <v>0.1803060764910035</v>
+      </c>
+      <c r="E567" s="1">
+        <v>-0.2692463381139306</v>
+      </c>
+      <c r="F567" s="1">
+        <v>0.7877401237191684</v>
+      </c>
+      <c r="G567" s="1">
+        <v>-0.4019401669509839</v>
+      </c>
+      <c r="H567" s="1">
+        <v>0.304846665281198</v>
+      </c>
+    </row>
+    <row r="569" spans="1:8">
+      <c r="A569" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="570" spans="1:8">
+      <c r="B570" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C570" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D570" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E570" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F570" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G570" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H570" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="571" spans="1:8">
+      <c r="A571" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C571" s="1">
+        <v>-3.220011683599902</v>
+      </c>
+      <c r="D571" s="1">
+        <v>0.334120011020034</v>
+      </c>
+      <c r="E571" s="1">
+        <v>-9.637290726076353</v>
+      </c>
+      <c r="F571" s="1">
+        <v>5.563698113841918E-22</v>
+      </c>
+      <c r="G571" s="1">
+        <v>-3.874874871713295</v>
+      </c>
+      <c r="H571" s="1">
+        <v>-2.56514849548651</v>
+      </c>
+    </row>
+    <row r="572" spans="1:8">
+      <c r="A572" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C572" s="1">
+        <v>-0.6210889478804754</v>
+      </c>
+      <c r="D572" s="1">
+        <v>0.3445620725585516</v>
+      </c>
+      <c r="E572" s="1">
+        <v>-1.802545890406825</v>
+      </c>
+      <c r="F572" s="1">
+        <v>0.07145956144800504</v>
+      </c>
+      <c r="G572" s="1">
+        <v>-1.296418200533713</v>
+      </c>
+      <c r="H572" s="1">
+        <v>0.05424030477276254</v>
+      </c>
+    </row>
+    <row r="573" spans="1:8">
+      <c r="A573" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C573" s="1">
+        <v>-0.8570839528149715</v>
+      </c>
+      <c r="D573" s="1">
+        <v>0.3362116975673475</v>
+      </c>
+      <c r="E573" s="1">
+        <v>-2.549238943845155</v>
+      </c>
+      <c r="F573" s="1">
+        <v>0.01079583038040089</v>
+      </c>
+      <c r="G573" s="1">
+        <v>-1.516046771228045</v>
+      </c>
+      <c r="H573" s="1">
+        <v>-0.1981211344018976</v>
+      </c>
+    </row>
+    <row r="574" spans="1:8">
+      <c r="A574" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C574" s="1">
+        <v>-0.3302478916274166</v>
+      </c>
+      <c r="D574" s="1">
+        <v>0.5318169749932339</v>
+      </c>
+      <c r="E574" s="1">
+        <v>-0.6209803506772574</v>
+      </c>
+      <c r="F574" s="1">
+        <v>0.5346125517160372</v>
+      </c>
+      <c r="G574" s="1">
+        <v>-1.372590008981194</v>
+      </c>
+      <c r="H574" s="1">
+        <v>0.7120942257263604</v>
+      </c>
+    </row>
+    <row r="575" spans="1:8">
+      <c r="A575" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C575" s="1">
+        <v>0.0352677992662145</v>
+      </c>
+      <c r="D575" s="1">
+        <v>0.6182661250172221</v>
+      </c>
+      <c r="E575" s="1">
+        <v>0.05704307229388007</v>
+      </c>
+      <c r="F575" s="1">
+        <v>0.9545108842500244</v>
+      </c>
+      <c r="G575" s="1">
+        <v>-1.176511538628679</v>
+      </c>
+      <c r="H575" s="1">
+        <v>1.247047137161108</v>
+      </c>
+    </row>
+    <row r="576" spans="1:8">
+      <c r="A576" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C576" s="1">
+        <v>-0.1038711015539725</v>
+      </c>
+      <c r="D576" s="1">
+        <v>0.3170212224799095</v>
+      </c>
+      <c r="E576" s="1">
+        <v>-0.3276471547912068</v>
+      </c>
+      <c r="F576" s="1">
+        <v>0.7431784638610279</v>
+      </c>
+      <c r="G576" s="1">
+        <v>-0.725221279949455</v>
+      </c>
+      <c r="H576" s="1">
+        <v>0.51747907684151</v>
+      </c>
+    </row>
+    <row r="577" spans="1:8">
+      <c r="A577" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C577" s="1">
+        <v>0.7122488802726732</v>
+      </c>
+      <c r="D577" s="1">
+        <v>0.2344532080234607</v>
+      </c>
+      <c r="E577" s="1">
+        <v>3.037914841418598</v>
+      </c>
+      <c r="F577" s="1">
+        <v>0.002382212641185517</v>
+      </c>
+      <c r="G577" s="1">
+        <v>0.2527290364868129</v>
+      </c>
+      <c r="H577" s="1">
+        <v>1.171768724058533</v>
+      </c>
+    </row>
+    <row r="578" spans="1:8">
+      <c r="A578" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C578" s="1">
+        <v>-0.4000488552381247</v>
+      </c>
+      <c r="D578" s="1">
+        <v>0.2478392100757799</v>
+      </c>
+      <c r="E578" s="1">
+        <v>-1.614146749078989</v>
+      </c>
+      <c r="F578" s="1">
+        <v>0.1064955992418278</v>
+      </c>
+      <c r="G578" s="1">
+        <v>-0.8858047809435099</v>
+      </c>
+      <c r="H578" s="1">
+        <v>0.08570707046726045</v>
+      </c>
+    </row>
+    <row r="579" spans="1:8">
+      <c r="A579" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C579" s="1">
+        <v>1.242454074241694</v>
+      </c>
+      <c r="D579" s="1">
+        <v>0.2929321910595102</v>
+      </c>
+      <c r="E579" s="1">
+        <v>4.241439186822882</v>
+      </c>
+      <c r="F579" s="1">
+        <v>2.220910688436206E-05</v>
+      </c>
+      <c r="G579" s="1">
+        <v>0.6683175298526481</v>
+      </c>
+      <c r="H579" s="1">
+        <v>1.81659061863074</v>
+      </c>
+    </row>
+    <row r="580" spans="1:8">
+      <c r="A580" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C580" s="1">
+        <v>-0.3003199431712367</v>
+      </c>
+      <c r="D580" s="1">
+        <v>0.3268526082213848</v>
+      </c>
+      <c r="E580" s="1">
+        <v>-0.9188237622011665</v>
+      </c>
+      <c r="F580" s="1">
+        <v>0.3581877614335142</v>
+      </c>
+      <c r="G580" s="1">
+        <v>-0.9409392835381313</v>
+      </c>
+      <c r="H580" s="1">
+        <v>0.3402993971956579</v>
+      </c>
+    </row>
+    <row r="581" spans="1:8">
+      <c r="A581" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C581" s="1">
+        <v>0.4607900789240711</v>
+      </c>
+      <c r="D581" s="1">
+        <v>0.8149821623054956</v>
+      </c>
+      <c r="E581" s="1">
+        <v>0.5653989746481644</v>
+      </c>
+      <c r="F581" s="1">
+        <v>0.571802421835031</v>
+      </c>
+      <c r="G581" s="1">
+        <v>-1.136545607237277</v>
+      </c>
+      <c r="H581" s="1">
+        <v>2.058125765085419</v>
+      </c>
+    </row>
+    <row r="582" spans="1:8">
+      <c r="A582" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C582" s="1">
+        <v>-0.4937137273535617</v>
+      </c>
+      <c r="D582" s="1">
+        <v>0.416020178557125</v>
+      </c>
+      <c r="E582" s="1">
+        <v>-1.18675427972244</v>
+      </c>
+      <c r="F582" s="1">
+        <v>0.2353245577495998</v>
+      </c>
+      <c r="G582" s="1">
+        <v>-1.309098294167449</v>
+      </c>
+      <c r="H582" s="1">
+        <v>0.3216708394603258</v>
+      </c>
+    </row>
+    <row r="583" spans="1:8">
+      <c r="A583" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B583" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C583" s="1">
+        <v>-0.4431338191330692</v>
+      </c>
+      <c r="D583" s="1">
+        <v>0.4207380126862647</v>
+      </c>
+      <c r="E583" s="1">
+        <v>-1.053229814686377</v>
+      </c>
+      <c r="F583" s="1">
+        <v>0.2922356770200806</v>
+      </c>
+      <c r="G583" s="1">
+        <v>-1.267765170925104</v>
+      </c>
+      <c r="H583" s="1">
+        <v>0.381497532658966</v>
+      </c>
+    </row>
+    <row r="585" spans="1:8">
+      <c r="A585" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="586" spans="1:8">
+      <c r="C586" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D586" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E586" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F586" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G586" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="587" spans="1:8">
+      <c r="A587" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B587" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C587" s="1">
+        <v>5.563698113841918E-22</v>
+      </c>
+      <c r="D587" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E587" s="1">
+        <v>0.03995459144446616</v>
+      </c>
+      <c r="F587" s="1">
+        <v>0.0207569349909226</v>
+      </c>
+      <c r="G587" s="1">
+        <v>0.07690776013859134</v>
+      </c>
+    </row>
+    <row r="588" spans="1:8">
+      <c r="A588" s="2"/>
+      <c r="B588" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C588" s="1">
+        <v>0.01079583038040089</v>
+      </c>
+      <c r="D588" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E588" s="1">
+        <v>0.4243978438104394</v>
+      </c>
+      <c r="F588" s="1">
+        <v>0.2195782163473776</v>
+      </c>
+      <c r="G588" s="1">
+        <v>0.8202704841449596</v>
+      </c>
+    </row>
+    <row r="589" spans="1:8">
+      <c r="A589" s="2"/>
+      <c r="B589" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C589" s="1">
+        <v>0.07145956144800504</v>
+      </c>
+      <c r="E589" s="1">
+        <v>0.5373589629730714</v>
+      </c>
+      <c r="F589" s="1">
+        <v>0.2735096975482971</v>
+      </c>
+      <c r="G589" s="1">
+        <v>1.055738270620206</v>
+      </c>
+    </row>
+    <row r="590" spans="1:8">
+      <c r="A590" s="2"/>
+      <c r="B590" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C590" s="1">
+        <v>0.1064955992418278</v>
+      </c>
+      <c r="E590" s="1">
+        <v>0.6702872981901289</v>
+      </c>
+      <c r="F590" s="1">
+        <v>0.4123821623932147</v>
+      </c>
+      <c r="G590" s="1">
+        <v>1.08948713859893</v>
+      </c>
+    </row>
+    <row r="591" spans="1:8">
+      <c r="A591" s="2"/>
+      <c r="B591" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C591" s="1">
+        <v>0.7431784638610279</v>
+      </c>
+      <c r="E591" s="1">
+        <v>0.901341471448728</v>
+      </c>
+      <c r="F591" s="1">
+        <v>0.4842174094957814</v>
+      </c>
+      <c r="G591" s="1">
+        <v>1.677792727443097</v>
+      </c>
+    </row>
+    <row r="592" spans="1:8">
+      <c r="A592" s="2"/>
+      <c r="B592" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C592" s="1">
+        <v>0.002382212641185517</v>
+      </c>
+      <c r="D592" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E592" s="1">
+        <v>2.038570608738161</v>
+      </c>
+      <c r="F592" s="1">
+        <v>1.287534354732079</v>
+      </c>
+      <c r="G592" s="1">
+        <v>3.227696497213736</v>
+      </c>
+    </row>
+    <row r="593" spans="1:7">
+      <c r="A593" s="2"/>
+      <c r="B593" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C593" s="1">
+        <v>0.2922356770200806</v>
+      </c>
+      <c r="E593" s="1">
+        <v>0.6420212866070356</v>
+      </c>
+      <c r="F593" s="1">
+        <v>0.2814599342758922</v>
+      </c>
+      <c r="G593" s="1">
+        <v>1.464476048845076</v>
+      </c>
+    </row>
+    <row r="594" spans="1:7">
+      <c r="A594" s="2"/>
+      <c r="B594" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C594" s="1">
+        <v>0.2353245577495998</v>
+      </c>
+      <c r="E594" s="1">
+        <v>0.6103554861634233</v>
+      </c>
+      <c r="F594" s="1">
+        <v>0.2700634644280019</v>
+      </c>
+      <c r="G594" s="1">
+        <v>1.379430647084457</v>
+      </c>
+    </row>
+    <row r="595" spans="1:7">
+      <c r="A595" s="2"/>
+      <c r="B595" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C595" s="1">
+        <v>0.3581877614335142</v>
+      </c>
+      <c r="E595" s="1">
+        <v>0.7405812388632619</v>
+      </c>
+      <c r="F595" s="1">
+        <v>0.3902610973256945</v>
+      </c>
+      <c r="G595" s="1">
+        <v>1.405368290907364</v>
+      </c>
+    </row>
+    <row r="596" spans="1:7">
+      <c r="A596" s="2"/>
+      <c r="B596" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C596" s="1">
+        <v>0.571802421835031</v>
+      </c>
+      <c r="E596" s="1">
+        <v>1.585326023003487</v>
+      </c>
+      <c r="F596" s="1">
+        <v>0.3209257127026455</v>
+      </c>
+      <c r="G596" s="1">
+        <v>7.831278391646729</v>
+      </c>
+    </row>
+    <row r="597" spans="1:7">
+      <c r="A597" s="2"/>
+      <c r="B597" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C597" s="1">
+        <v>2.220910688436206E-05</v>
+      </c>
+      <c r="D597" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E597" s="1">
+        <v>3.464104210955284</v>
+      </c>
+      <c r="F597" s="1">
+        <v>1.950952139068036</v>
+      </c>
+      <c r="G597" s="1">
+        <v>6.150852060415233</v>
+      </c>
+    </row>
+    <row r="598" spans="1:7">
+      <c r="A598" s="2"/>
+      <c r="B598" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C598" s="1">
+        <v>0.9545108842500244</v>
+      </c>
+      <c r="E598" s="1">
+        <v>1.035897084136515</v>
+      </c>
+      <c r="F598" s="1">
+        <v>0.3083525404802004</v>
+      </c>
+      <c r="G598" s="1">
+        <v>3.480051655327413</v>
+      </c>
+    </row>
+    <row r="599" spans="1:7">
+      <c r="A599" s="2"/>
+      <c r="B599" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C599" s="1">
+        <v>0.5346125517160372</v>
+      </c>
+      <c r="E599" s="1">
+        <v>0.7187455403448569</v>
+      </c>
+      <c r="F599" s="1">
+        <v>0.2534496718033936</v>
+      </c>
+      <c r="G599" s="1">
+        <v>2.038255358903579</v>
+      </c>
+    </row>
+    <row r="600" spans="1:7">
+      <c r="A600" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B600" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C600" s="1">
+        <v>0.03043827325881311</v>
+      </c>
+      <c r="D600" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E600" s="1">
+        <v>1.252312110337718</v>
+      </c>
+      <c r="F600" s="1">
+        <v>1.021472964764968</v>
+      </c>
+      <c r="G600" s="1">
+        <v>1.535317796745953</v>
+      </c>
+    </row>
+    <row r="601" spans="1:7">
+      <c r="A601" s="2"/>
+      <c r="B601" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C601" s="1">
+        <v>0.4128535534896671</v>
+      </c>
+      <c r="E601" s="1">
+        <v>0.9244774254224465</v>
+      </c>
+      <c r="F601" s="1">
+        <v>0.7660734583340914</v>
+      </c>
+      <c r="G601" s="1">
+        <v>1.115635192445201</v>
+      </c>
+    </row>
+    <row r="602" spans="1:7">
+      <c r="A602" s="2"/>
+      <c r="B602" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C602" s="1">
+        <v>0.1006093927893698</v>
+      </c>
+      <c r="E602" s="1">
+        <v>1.18769498451855</v>
+      </c>
+      <c r="F602" s="1">
+        <v>0.9672277208713215</v>
+      </c>
+      <c r="G602" s="1">
+        <v>1.45841495835104</v>
+      </c>
+    </row>
+    <row r="603" spans="1:7">
+      <c r="A603" s="2"/>
+      <c r="B603" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C603" s="1">
+        <v>0.01095642293665167</v>
+      </c>
+      <c r="D603" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E603" s="1">
+        <v>0.7820236474024518</v>
+      </c>
+      <c r="F603" s="1">
+        <v>0.6470777512348328</v>
+      </c>
+      <c r="G603" s="1">
+        <v>0.945112057908928</v>
+      </c>
+    </row>
+    <row r="604" spans="1:7">
+      <c r="A604" s="2"/>
+      <c r="B604" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C604" s="1">
+        <v>0.0003655703611464461</v>
+      </c>
+      <c r="D604" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E604" s="1">
+        <v>0.5911064315491679</v>
+      </c>
+      <c r="F604" s="1">
+        <v>0.4426788014166658</v>
+      </c>
+      <c r="G604" s="1">
+        <v>0.789300983694307</v>
+      </c>
+    </row>
+    <row r="605" spans="1:7">
+      <c r="A605" s="2"/>
+      <c r="B605" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C605" s="1">
+        <v>0.2909840920523293</v>
+      </c>
+      <c r="E605" s="1">
+        <v>0.904107219360633</v>
+      </c>
+      <c r="F605" s="1">
+        <v>0.7498256731993821</v>
+      </c>
+      <c r="G605" s="1">
+        <v>1.090133204711787</v>
+      </c>
+    </row>
+    <row r="606" spans="1:7">
+      <c r="A606" s="2"/>
+      <c r="B606" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C606" s="1">
+        <v>0.004600712496250168</v>
+      </c>
+      <c r="D606" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E606" s="1">
+        <v>0.5978365170354801</v>
+      </c>
+      <c r="F606" s="1">
+        <v>0.4188465394957133</v>
+      </c>
+      <c r="G606" s="1">
+        <v>0.8533161131793756</v>
+      </c>
+    </row>
+    <row r="607" spans="1:7">
+      <c r="A607" s="2"/>
+      <c r="B607" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C607" s="1">
+        <v>0.4492998724301147</v>
+      </c>
+      <c r="E607" s="1">
+        <v>0.9050556454142124</v>
+      </c>
+      <c r="F607" s="1">
+        <v>0.6989410013783011</v>
+      </c>
+      <c r="G607" s="1">
+        <v>1.171952596400602</v>
+      </c>
+    </row>
+    <row r="608" spans="1:7">
+      <c r="A608" s="2"/>
+      <c r="B608" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C608" s="1">
+        <v>0.5564597044586419</v>
+      </c>
+      <c r="E608" s="1">
+        <v>0.9218935648034727</v>
+      </c>
+      <c r="F608" s="1">
+        <v>0.7030300263827154</v>
+      </c>
+      <c r="G608" s="1">
+        <v>1.208892526538252</v>
+      </c>
+    </row>
+    <row r="609" spans="1:7">
+      <c r="A609" s="2"/>
+      <c r="B609" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C609" s="1">
+        <v>0.01241480255182997</v>
+      </c>
+      <c r="D609" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E609" s="1">
+        <v>0.2603569720001682</v>
+      </c>
+      <c r="F609" s="1">
+        <v>0.09065829954651919</v>
+      </c>
+      <c r="G609" s="1">
+        <v>0.7477059817817746</v>
+      </c>
+    </row>
+    <row r="610" spans="1:7">
+      <c r="A610" s="2"/>
+      <c r="B610" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C610" s="1">
+        <v>8.641755080100111E-20</v>
+      </c>
+      <c r="D610" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E610" s="1">
+        <v>0.4153771398150439</v>
+      </c>
+      <c r="F610" s="1">
+        <v>0.3438000387044616</v>
+      </c>
+      <c r="G610" s="1">
+        <v>0.5018561630507677</v>
+      </c>
+    </row>
+    <row r="611" spans="1:7">
+      <c r="A611" s="2"/>
+      <c r="B611" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C611" s="1">
+        <v>0.679041437636994</v>
+      </c>
+      <c r="E611" s="1">
+        <v>0.907090144857518</v>
+      </c>
+      <c r="F611" s="1">
+        <v>0.5715417577746217</v>
+      </c>
+      <c r="G611" s="1">
+        <v>1.439636771425713</v>
+      </c>
+    </row>
+    <row r="612" spans="1:7">
+      <c r="A612" s="2"/>
+      <c r="B612" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C612" s="1">
+        <v>0.1230465751327812</v>
+      </c>
+      <c r="E612" s="1">
+        <v>1.237814906643693</v>
+      </c>
+      <c r="F612" s="1">
+        <v>0.9438301980585345</v>
+      </c>
+      <c r="G612" s="1">
+        <v>1.623370121300475</v>
+      </c>
+    </row>
+    <row r="613" spans="1:7">
+      <c r="A613" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C613" s="1">
+        <v>2.635115730555844E-22</v>
+      </c>
+      <c r="D613" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E613" s="1">
+        <v>0.2598298490467053</v>
+      </c>
+      <c r="F613" s="1">
+        <v>0.1979654357731759</v>
+      </c>
+      <c r="G613" s="1">
+        <v>0.3410269585291988</v>
+      </c>
+    </row>
+    <row r="614" spans="1:7">
+      <c r="A614" s="2"/>
+      <c r="B614" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C614" s="1">
+        <v>0.007203775417692744</v>
+      </c>
+      <c r="D614" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E614" s="1">
+        <v>1.356040702488492</v>
+      </c>
+      <c r="F614" s="1">
+        <v>1.085924401402571</v>
+      </c>
+      <c r="G614" s="1">
+        <v>1.69334659432134</v>
+      </c>
+    </row>
+    <row r="615" spans="1:7">
+      <c r="A615" s="2"/>
+      <c r="B615" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C615" s="1">
+        <v>0.7529724151289838</v>
+      </c>
+      <c r="E615" s="1">
+        <v>0.9592207167867117</v>
+      </c>
+      <c r="F615" s="1">
+        <v>0.7401412195747047</v>
+      </c>
+      <c r="G615" s="1">
+        <v>1.243147063261141</v>
+      </c>
+    </row>
+    <row r="616" spans="1:7">
+      <c r="A616" s="2"/>
+      <c r="B616" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C616" s="1">
+        <v>0.7307014160917791</v>
+      </c>
+      <c r="E616" s="1">
+        <v>0.9582502835410031</v>
+      </c>
+      <c r="F616" s="1">
+        <v>0.7516455326701644</v>
+      </c>
+      <c r="G616" s="1">
+        <v>1.221644466700176</v>
+      </c>
+    </row>
+    <row r="617" spans="1:7">
+      <c r="A617" s="2"/>
+      <c r="B617" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C617" s="1">
+        <v>5.358685390828512E-07</v>
+      </c>
+      <c r="D617" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E617" s="1">
+        <v>1.928875342590763</v>
+      </c>
+      <c r="F617" s="1">
+        <v>1.491959695653061</v>
+      </c>
+      <c r="G617" s="1">
+        <v>2.493740345731034</v>
+      </c>
+    </row>
+    <row r="618" spans="1:7">
+      <c r="A618" s="2"/>
+      <c r="B618" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C618" s="1">
+        <v>0.6385747782972211</v>
+      </c>
+      <c r="E618" s="1">
+        <v>1.054434664925491</v>
+      </c>
+      <c r="F618" s="1">
+        <v>0.845204177690837</v>
+      </c>
+      <c r="G618" s="1">
+        <v>1.315460207063985</v>
+      </c>
+    </row>
+    <row r="619" spans="1:7">
+      <c r="A619" s="2"/>
+      <c r="B619" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C619" s="1">
+        <v>0.7877401237191684</v>
+      </c>
+      <c r="E619" s="1">
+        <v>0.9526128028209225</v>
+      </c>
+      <c r="F619" s="1">
+        <v>0.6690207740455918</v>
+      </c>
+      <c r="G619" s="1">
+        <v>1.356417001240222</v>
+      </c>
+    </row>
+    <row r="620" spans="1:7">
+      <c r="A620" s="2"/>
+      <c r="B620" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C620" s="1">
+        <v>0.6927165844976992</v>
+      </c>
+      <c r="E620" s="1">
+        <v>1.062727624545608</v>
+      </c>
+      <c r="F620" s="1">
+        <v>0.7859133693395327</v>
+      </c>
+      <c r="G620" s="1">
+        <v>1.437041343273585</v>
+      </c>
+    </row>
+    <row r="621" spans="1:7">
+      <c r="A621" s="2"/>
+      <c r="B621" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C621" s="1">
+        <v>0.002181524385068261</v>
+      </c>
+      <c r="D621" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E621" s="1">
+        <v>1.524916448792745</v>
+      </c>
+      <c r="F621" s="1">
+        <v>1.164236114305562</v>
+      </c>
+      <c r="G621" s="1">
+        <v>1.997335546652153</v>
+      </c>
+    </row>
+    <row r="622" spans="1:7">
+      <c r="A622" s="2"/>
+      <c r="B622" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C622" s="1">
+        <v>0.1356154291607063</v>
+      </c>
+      <c r="E622" s="1">
+        <v>0.5686949975076856</v>
+      </c>
+      <c r="F622" s="1">
+        <v>0.2709854431474749</v>
+      </c>
+      <c r="G622" s="1">
+        <v>1.193473702623425</v>
+      </c>
+    </row>
+    <row r="623" spans="1:7">
+      <c r="A623" s="2"/>
+      <c r="B623" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C623" s="1">
+        <v>0.3240653368093933</v>
+      </c>
+      <c r="E623" s="1">
+        <v>1.119410169033908</v>
+      </c>
+      <c r="F623" s="1">
+        <v>0.8945866223798794</v>
+      </c>
+      <c r="G623" s="1">
+        <v>1.400735373398431</v>
+      </c>
+    </row>
+    <row r="624" spans="1:7">
+      <c r="A624" s="2"/>
+      <c r="B624" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C624" s="1">
+        <v>0.5721652503803307</v>
+      </c>
+      <c r="E624" s="1">
+        <v>0.8387042337796062</v>
+      </c>
+      <c r="F624" s="1">
+        <v>0.4555621443778501</v>
+      </c>
+      <c r="G624" s="1">
+        <v>1.544080868967912</v>
+      </c>
+    </row>
+    <row r="625" spans="1:7">
+      <c r="A625" s="2"/>
+      <c r="B625" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C625" s="1">
+        <v>0.02904355107345591</v>
+      </c>
+      <c r="D625" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E625" s="1">
+        <v>0.6140322625452493</v>
+      </c>
+      <c r="F625" s="1">
+        <v>0.3962904661805755</v>
+      </c>
+      <c r="G625" s="1">
+        <v>0.9514122887696125</v>
+      </c>
+    </row>
+    <row r="626" spans="1:7">
+      <c r="A626" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B626" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C626" s="1">
+        <v>5.75724982403861E-30</v>
+      </c>
+      <c r="D626" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E626" s="1">
+        <v>0.2001249324129587</v>
+      </c>
+      <c r="F626" s="1">
+        <v>0.1516637311617033</v>
+      </c>
+      <c r="G626" s="1">
+        <v>0.2640709698127507</v>
+      </c>
+    </row>
+    <row r="627" spans="1:7">
+      <c r="A627" s="2"/>
+      <c r="B627" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C627" s="1">
+        <v>0.3653235325354613</v>
+      </c>
+      <c r="E627" s="1">
+        <v>1.10245501444012</v>
+      </c>
+      <c r="F627" s="1">
+        <v>0.892579293611852</v>
+      </c>
+      <c r="G627" s="1">
+        <v>1.361679648590076</v>
+      </c>
+    </row>
+    <row r="628" spans="1:7">
+      <c r="A628" s="2"/>
+      <c r="B628" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C628" s="1">
+        <v>0.19828416430527</v>
+      </c>
+      <c r="E628" s="1">
+        <v>1.166756205614445</v>
+      </c>
+      <c r="F628" s="1">
+        <v>0.9224298515240792</v>
+      </c>
+      <c r="G628" s="1">
+        <v>1.475797906031103</v>
+      </c>
+    </row>
+    <row r="629" spans="1:7">
+      <c r="A629" s="2"/>
+      <c r="B629" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C629" s="1">
+        <v>0.4620668891808699</v>
+      </c>
+      <c r="E629" s="1">
+        <v>1.092949910686558</v>
+      </c>
+      <c r="F629" s="1">
+        <v>0.8624437594233449</v>
+      </c>
+      <c r="G629" s="1">
+        <v>1.385063656867851</v>
+      </c>
+    </row>
+    <row r="630" spans="1:7">
+      <c r="A630" s="2"/>
+      <c r="B630" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C630" s="1">
+        <v>0.2455031605052839</v>
+      </c>
+      <c r="E630" s="1">
+        <v>1.170424426516768</v>
+      </c>
+      <c r="F630" s="1">
+        <v>0.8974331742100226</v>
+      </c>
+      <c r="G630" s="1">
+        <v>1.526457208797716</v>
+      </c>
+    </row>
+    <row r="631" spans="1:7">
+      <c r="A631" s="2"/>
+      <c r="B631" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C631" s="1">
+        <v>0.9489615315521314</v>
+      </c>
+      <c r="E631" s="1">
+        <v>1.006724827909416</v>
+      </c>
+      <c r="F631" s="1">
+        <v>0.8199455391426391</v>
+      </c>
+      <c r="G631" s="1">
+        <v>1.236051457989496</v>
+      </c>
+    </row>
+    <row r="632" spans="1:7">
+      <c r="A632" s="2"/>
+      <c r="B632" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C632" s="1">
+        <v>0.3874835484867725</v>
+      </c>
+      <c r="E632" s="1">
+        <v>1.140395597832054</v>
+      </c>
+      <c r="F632" s="1">
+        <v>0.8465543172678562</v>
+      </c>
+      <c r="G632" s="1">
+        <v>1.536229977246976</v>
+      </c>
+    </row>
+    <row r="633" spans="1:7">
+      <c r="A633" s="2"/>
+      <c r="B633" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C633" s="1">
+        <v>0.3499381433206767</v>
+      </c>
+      <c r="E633" s="1">
+        <v>1.138307054241064</v>
+      </c>
+      <c r="F633" s="1">
+        <v>0.8675424084204794</v>
+      </c>
+      <c r="G633" s="1">
+        <v>1.493578800480897</v>
+      </c>
+    </row>
+    <row r="634" spans="1:7">
+      <c r="A634" s="2"/>
+      <c r="B634" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C634" s="1">
+        <v>0.2610134774064551</v>
+      </c>
+      <c r="E634" s="1">
+        <v>1.161280120378791</v>
+      </c>
+      <c r="F634" s="1">
+        <v>0.8947539858895064</v>
+      </c>
+      <c r="G634" s="1">
+        <v>1.507198111720417</v>
+      </c>
+    </row>
+    <row r="635" spans="1:7">
+      <c r="A635" s="2"/>
+      <c r="B635" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C635" s="1">
+        <v>0.6055075748093981</v>
+      </c>
+      <c r="E635" s="1">
+        <v>1.14514172142013</v>
+      </c>
+      <c r="F635" s="1">
+        <v>0.6847065431039845</v>
+      </c>
+      <c r="G635" s="1">
+        <v>1.915199402348792</v>
+      </c>
+    </row>
+    <row r="636" spans="1:7">
+      <c r="A636" s="2"/>
+      <c r="B636" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C636" s="1">
+        <v>8.503220591470087E-12</v>
+      </c>
+      <c r="D636" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E636" s="1">
+        <v>2.173111801264366</v>
+      </c>
+      <c r="F636" s="1">
+        <v>1.73919727562023</v>
+      </c>
+      <c r="G636" s="1">
+        <v>2.715284210130997</v>
+      </c>
+    </row>
+    <row r="637" spans="1:7">
+      <c r="A637" s="2"/>
+      <c r="B637" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C637" s="1">
+        <v>0.2675161165776037</v>
+      </c>
+      <c r="E637" s="1">
+        <v>1.333233760754325</v>
+      </c>
+      <c r="F637" s="1">
+        <v>0.801893242785563</v>
+      </c>
+      <c r="G637" s="1">
+        <v>2.216644518216063</v>
+      </c>
+    </row>
+    <row r="638" spans="1:7">
+      <c r="A638" s="2"/>
+      <c r="B638" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C638" s="1">
+        <v>0.5892118038207506</v>
+      </c>
+      <c r="E638" s="1">
+        <v>1.105198791434022</v>
+      </c>
+      <c r="F638" s="1">
+        <v>0.7687134442276027</v>
+      </c>
+      <c r="G638" s="1">
+        <v>1.588972298792745</v>
+      </c>
+    </row>
+    <row r="639" spans="1:7">
+      <c r="A639" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B639" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C639" s="1">
+        <v>6.303753463585649E-35</v>
+      </c>
+      <c r="D639" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E639" s="1">
+        <v>0.2091878438075394</v>
+      </c>
+      <c r="F639" s="1">
+        <v>0.1631259205336</v>
+      </c>
+      <c r="G639" s="1">
+        <v>0.2682562884776737</v>
+      </c>
+    </row>
+    <row r="640" spans="1:7">
+      <c r="A640" s="2"/>
+      <c r="B640" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C640" s="1">
+        <v>0.0001144842107323911</v>
+      </c>
+      <c r="D640" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E640" s="1">
+        <v>1.421955873054784</v>
+      </c>
+      <c r="F640" s="1">
+        <v>1.189074004475948</v>
+      </c>
+      <c r="G640" s="1">
+        <v>1.700447993399802</v>
+      </c>
+    </row>
+    <row r="641" spans="1:7">
+      <c r="A641" s="2"/>
+      <c r="B641" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C641" s="1">
+        <v>0.01228218742131392</v>
+      </c>
+      <c r="D641" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E641" s="1">
+        <v>0.7594346512287379</v>
+      </c>
+      <c r="F641" s="1">
+        <v>0.6122710373493028</v>
+      </c>
+      <c r="G641" s="1">
+        <v>0.9419700660410008</v>
+      </c>
+    </row>
+    <row r="642" spans="1:7">
+      <c r="A642" s="2"/>
+      <c r="B642" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C642" s="1">
+        <v>0.4531864316378061</v>
+      </c>
+      <c r="E642" s="1">
+        <v>1.08104171817588</v>
+      </c>
+      <c r="F642" s="1">
+        <v>0.8818928708240604</v>
+      </c>
+      <c r="G642" s="1">
+        <v>1.325162312906154</v>
+      </c>
+    </row>
+    <row r="643" spans="1:7">
+      <c r="A643" s="2"/>
+      <c r="B643" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C643" s="1">
+        <v>1.699538476781488E-08</v>
+      </c>
+      <c r="D643" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E643" s="1">
+        <v>1.821996185558173</v>
+      </c>
+      <c r="F643" s="1">
+        <v>1.479128244363792</v>
+      </c>
+      <c r="G643" s="1">
+        <v>2.244342309626032</v>
+      </c>
+    </row>
+    <row r="644" spans="1:7">
+      <c r="A644" s="2"/>
+      <c r="B644" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C644" s="1">
+        <v>0.0491657849146158</v>
+      </c>
+      <c r="D644" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E644" s="1">
+        <v>1.190649738289375</v>
+      </c>
+      <c r="F644" s="1">
+        <v>1.000637754036729</v>
+      </c>
+      <c r="G644" s="1">
+        <v>1.416743265551941</v>
+      </c>
+    </row>
+    <row r="645" spans="1:7">
+      <c r="A645" s="2"/>
+      <c r="B645" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C645" s="1">
+        <v>0.83055921949477</v>
+      </c>
+      <c r="E645" s="1">
+        <v>0.9714315849866472</v>
+      </c>
+      <c r="F645" s="1">
+        <v>0.7449308970368412</v>
+      </c>
+      <c r="G645" s="1">
+        <v>1.266801159763143</v>
+      </c>
+    </row>
+    <row r="646" spans="1:7">
+      <c r="A646" s="2"/>
+      <c r="B646" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C646" s="1">
+        <v>0.8896330971005005</v>
+      </c>
+      <c r="E646" s="1">
+        <v>0.9829024980175183</v>
+      </c>
+      <c r="F646" s="1">
+        <v>0.7704207850540145</v>
+      </c>
+      <c r="G646" s="1">
+        <v>1.253986573767405</v>
+      </c>
+    </row>
+    <row r="647" spans="1:7">
+      <c r="A647" s="2"/>
+      <c r="B647" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C647" s="1">
+        <v>3.756796141150703E-12</v>
+      </c>
+      <c r="D647" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E647" s="1">
+        <v>2.066407714590961</v>
+      </c>
+      <c r="F647" s="1">
+        <v>1.683726433595495</v>
+      </c>
+      <c r="G647" s="1">
+        <v>2.536065691979798</v>
+      </c>
+    </row>
+    <row r="648" spans="1:7">
+      <c r="A648" s="2"/>
+      <c r="B648" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C648" s="1">
+        <v>0.1367390703151118</v>
+      </c>
+      <c r="E648" s="1">
+        <v>1.415691434320921</v>
+      </c>
+      <c r="F648" s="1">
+        <v>0.8956158168656608</v>
+      </c>
+      <c r="G648" s="1">
+        <v>2.237770034280498</v>
+      </c>
+    </row>
+    <row r="649" spans="1:7">
+      <c r="A649" s="2"/>
+      <c r="B649" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C649" s="1">
+        <v>9.778824029820875E-34</v>
+      </c>
+      <c r="D649" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E649" s="1">
+        <v>3.534043423377875</v>
+      </c>
+      <c r="F649" s="1">
+        <v>2.880771849864578</v>
+      </c>
+      <c r="G649" s="1">
+        <v>4.335457151494842</v>
+      </c>
+    </row>
+    <row r="650" spans="1:7">
+      <c r="A650" s="2"/>
+      <c r="B650" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C650" s="1">
+        <v>0.2292481125687863</v>
+      </c>
+      <c r="E650" s="1">
+        <v>0.7257253052634283</v>
+      </c>
+      <c r="F650" s="1">
+        <v>0.4303341168085028</v>
+      </c>
+      <c r="G650" s="1">
+        <v>1.223879767204388</v>
+      </c>
+    </row>
+    <row r="651" spans="1:7">
+      <c r="A651" s="2"/>
+      <c r="B651" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C651" s="1">
+        <v>0.002412912081644074</v>
+      </c>
+      <c r="D651" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E651" s="1">
+        <v>0.5405982943304075</v>
+      </c>
+      <c r="F651" s="1">
+        <v>0.3633413146542173</v>
+      </c>
+      <c r="G651" s="1">
+        <v>0.8043305400352543</v>
+      </c>
+    </row>
+    <row r="652" spans="1:7">
+      <c r="A652" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B652" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C652" s="1">
+        <v>1.076401634377507E-22</v>
+      </c>
+      <c r="D652" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E652" s="1">
+        <v>0.2764187654845626</v>
+      </c>
+      <c r="F652" s="1">
+        <v>0.2137640919049212</v>
+      </c>
+      <c r="G652" s="1">
+        <v>0.3574376464780358</v>
+      </c>
+    </row>
+    <row r="653" spans="1:7">
+      <c r="A653" s="2"/>
+      <c r="B653" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C653" s="1">
+        <v>0.09047053184849052</v>
+      </c>
+      <c r="E653" s="1">
+        <v>1.195430162828195</v>
+      </c>
+      <c r="F653" s="1">
+        <v>0.972234995414249</v>
+      </c>
+      <c r="G653" s="1">
+        <v>1.469864056467701</v>
+      </c>
+    </row>
+    <row r="654" spans="1:7">
+      <c r="A654" s="2"/>
+      <c r="B654" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C654" s="1">
+        <v>0.09456680576091746</v>
+      </c>
+      <c r="E654" s="1">
+        <v>0.8088436612379578</v>
+      </c>
+      <c r="F654" s="1">
+        <v>0.6307351386972072</v>
+      </c>
+      <c r="G654" s="1">
+        <v>1.037246901569717</v>
+      </c>
+    </row>
+    <row r="655" spans="1:7">
+      <c r="A655" s="2"/>
+      <c r="B655" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C655" s="1">
+        <v>0.2103323207642823</v>
+      </c>
+      <c r="E655" s="1">
+        <v>0.8667356489483163</v>
+      </c>
+      <c r="F655" s="1">
+        <v>0.6929484593430764</v>
+      </c>
+      <c r="G655" s="1">
+        <v>1.084107591306336</v>
+      </c>
+    </row>
+    <row r="656" spans="1:7">
+      <c r="A656" s="2"/>
+      <c r="B656" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C656" s="1">
+        <v>6.908059231390752E-07</v>
+      </c>
+      <c r="D656" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E656" s="1">
+        <v>1.822855450157607</v>
+      </c>
+      <c r="F656" s="1">
+        <v>1.438124639668288</v>
+      </c>
+      <c r="G656" s="1">
+        <v>2.310510438744527</v>
+      </c>
+    </row>
+    <row r="657" spans="1:7">
+      <c r="A657" s="2"/>
+      <c r="B657" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C657" s="1">
+        <v>0.131314363173481</v>
+      </c>
+      <c r="E657" s="1">
+        <v>0.8538203934418375</v>
+      </c>
+      <c r="F657" s="1">
+        <v>0.6953738609813233</v>
+      </c>
+      <c r="G657" s="1">
+        <v>1.048370243926604</v>
+      </c>
+    </row>
+    <row r="658" spans="1:7">
+      <c r="A658" s="2"/>
+      <c r="B658" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C658" s="1">
+        <v>0.04545464566362853</v>
+      </c>
+      <c r="D658" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E658" s="1">
+        <v>0.7061445516222113</v>
+      </c>
+      <c r="F658" s="1">
+        <v>0.5021614388253089</v>
+      </c>
+      <c r="G658" s="1">
+        <v>0.9929876912735229</v>
+      </c>
+    </row>
+    <row r="659" spans="1:7">
+      <c r="A659" s="2"/>
+      <c r="B659" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C659" s="1">
+        <v>0.03817110476886406</v>
+      </c>
+      <c r="D659" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E659" s="1">
+        <v>1.338121078312889</v>
+      </c>
+      <c r="F659" s="1">
+        <v>1.016010597434499</v>
+      </c>
+      <c r="G659" s="1">
+        <v>1.762351716356664</v>
+      </c>
+    </row>
+    <row r="660" spans="1:7">
+      <c r="A660" s="2"/>
+      <c r="B660" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C660" s="1">
+        <v>1.496602319378977E-18</v>
+      </c>
+      <c r="D660" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E660" s="1">
+        <v>2.782400518402144</v>
+      </c>
+      <c r="F660" s="1">
+        <v>2.214744500067124</v>
+      </c>
+      <c r="G660" s="1">
+        <v>3.495551132227617</v>
+      </c>
+    </row>
+    <row r="661" spans="1:7">
+      <c r="A661" s="2"/>
+      <c r="B661" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C661" s="1">
+        <v>0.6485753473899263</v>
+      </c>
+      <c r="E661" s="1">
+        <v>0.8707508811625326</v>
+      </c>
+      <c r="F661" s="1">
+        <v>0.480177567563645</v>
+      </c>
+      <c r="G661" s="1">
+        <v>1.579013990371032</v>
+      </c>
+    </row>
+    <row r="662" spans="1:7">
+      <c r="A662" s="2"/>
+      <c r="B662" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C662" s="1">
+        <v>1.341907416072246E-06</v>
+      </c>
+      <c r="D662" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E662" s="1">
+        <v>1.704436199208412</v>
+      </c>
+      <c r="F662" s="1">
+        <v>1.373012992853989</v>
+      </c>
+      <c r="G662" s="1">
+        <v>2.115859625722389</v>
+      </c>
+    </row>
+    <row r="663" spans="1:7">
+      <c r="A663" s="2"/>
+      <c r="B663" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C663" s="1">
+        <v>0.4662063620866697</v>
+      </c>
+      <c r="E663" s="1">
+        <v>1.20751967892552</v>
+      </c>
+      <c r="F663" s="1">
+        <v>0.7271352108810394</v>
+      </c>
+      <c r="G663" s="1">
+        <v>2.005271857521062</v>
+      </c>
+    </row>
+    <row r="664" spans="1:7">
+      <c r="A664" s="2"/>
+      <c r="B664" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C664" s="1">
+        <v>0.002192984741371619</v>
+      </c>
+      <c r="D664" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E664" s="1">
+        <v>0.4884737595781748</v>
+      </c>
+      <c r="F664" s="1">
+        <v>0.3088309745169134</v>
+      </c>
+      <c r="G664" s="1">
+        <v>0.7726123138058778</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="A56:A66"/>
     <mergeCell ref="A67:A77"/>
     <mergeCell ref="A78:A88"/>
@@ -10250,6 +14195,12 @@
     <mergeCell ref="A429:A444"/>
     <mergeCell ref="A445:A460"/>
     <mergeCell ref="A461:A476"/>
+    <mergeCell ref="A587:A599"/>
+    <mergeCell ref="A600:A612"/>
+    <mergeCell ref="A613:A625"/>
+    <mergeCell ref="A626:A638"/>
+    <mergeCell ref="A639:A651"/>
+    <mergeCell ref="A652:A664"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets_output/09_logistic_regression_blocks.xlsx
+++ b/assets_output/09_logistic_regression_blocks.xlsx
@@ -49,7 +49,7 @@
     <t>rt_outcome</t>
   </si>
   <si>
-    <t>2026-06-21 13:14</t>
+    <t>2026-06-21 14:26</t>
   </si>
   <si>
     <t>2679</t>
@@ -208,7 +208,7 @@
     <t>cli_outcome</t>
   </si>
   <si>
-    <t>2026-06-21 13:15</t>
+    <t>2026-06-21 14:27</t>
   </si>
   <si>
     <t>2014</t>
@@ -496,7 +496,7 @@
     <t>MNLogit: 'Outcomes from individual placements (vs. forwards moves)', table 0</t>
   </si>
   <si>
-    <t>2026-06-21 13:16</t>
+    <t>2026-06-21 14:28</t>
   </si>
   <si>
     <t>5191</t>
@@ -912,10 +912,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H664"/>
+  <dimension ref="A1:J664"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="8" width="9.140625" style="1"/>
+    <col min="2" max="10" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">

--- a/assets_output/09_logistic_regression_blocks.xlsx
+++ b/assets_output/09_logistic_regression_blocks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="555">
   <si>
     <t>MNLogit: 'Route outcomes after 3.08 years', table 0</t>
   </si>
@@ -49,7 +49,7 @@
     <t>rt_outcome</t>
   </si>
   <si>
-    <t>2026-06-21 14:26</t>
+    <t>2026-06-21 14:49</t>
   </si>
   <si>
     <t>2679</t>
@@ -193,6 +193,15 @@
     <t>odds_r</t>
   </si>
   <si>
+    <t>odds_r_d%</t>
+  </si>
+  <si>
+    <t>[0.025_d%</t>
+  </si>
+  <si>
+    <t>0.975]_d%</t>
+  </si>
+  <si>
     <t>Died</t>
   </si>
   <si>
@@ -202,15 +211,198 @@
     <t>Returned to homelessness</t>
   </si>
   <si>
+    <t>-97.8%</t>
+  </si>
+  <si>
+    <t>-59.7%</t>
+  </si>
+  <si>
+    <t>111.2%</t>
+  </si>
+  <si>
+    <t>1570.4%</t>
+  </si>
+  <si>
+    <t>552.8%</t>
+  </si>
+  <si>
+    <t>-59.2%</t>
+  </si>
+  <si>
+    <t>35.2%</t>
+  </si>
+  <si>
+    <t>183.8%</t>
+  </si>
+  <si>
+    <t>30.5%</t>
+  </si>
+  <si>
+    <t>51.0%</t>
+  </si>
+  <si>
+    <t>63.2%</t>
+  </si>
+  <si>
+    <t>646.1%</t>
+  </si>
+  <si>
+    <t>255.1%</t>
+  </si>
+  <si>
+    <t>-42.8%</t>
+  </si>
+  <si>
+    <t>-74.3%</t>
+  </si>
+  <si>
+    <t>-29.3%</t>
+  </si>
+  <si>
+    <t>264.3%</t>
+  </si>
+  <si>
+    <t>201.5%</t>
+  </si>
+  <si>
+    <t>807.8%</t>
+  </si>
+  <si>
+    <t>457.4%</t>
+  </si>
+  <si>
+    <t>-57.7%</t>
+  </si>
+  <si>
+    <t>-99.0%</t>
+  </si>
+  <si>
+    <t>-82.5%</t>
+  </si>
+  <si>
+    <t>15.5%</t>
+  </si>
+  <si>
+    <t>95.6%</t>
+  </si>
+  <si>
+    <t>220.4%</t>
+  </si>
+  <si>
+    <t>-67.2%</t>
+  </si>
+  <si>
+    <t>8.6%</t>
+  </si>
+  <si>
+    <t>108.9%</t>
+  </si>
+  <si>
+    <t>4.8%</t>
+  </si>
+  <si>
+    <t>2.2%</t>
+  </si>
+  <si>
+    <t>22.3%</t>
+  </si>
+  <si>
+    <t>68.8%</t>
+  </si>
+  <si>
+    <t>186.0%</t>
+  </si>
+  <si>
+    <t>-60.3%</t>
+  </si>
+  <si>
+    <t>-79.8%</t>
+  </si>
+  <si>
+    <t>-45.5%</t>
+  </si>
+  <si>
+    <t>167.4%</t>
+  </si>
+  <si>
+    <t>127.1%</t>
+  </si>
+  <si>
+    <t>103.4%</t>
+  </si>
+  <si>
+    <t>340.9%</t>
+  </si>
+  <si>
+    <t>-73.1%</t>
+  </si>
+  <si>
+    <t>-95.4%</t>
+  </si>
+  <si>
+    <t>-7.3%</t>
+  </si>
+  <si>
+    <t>286.4%</t>
+  </si>
+  <si>
+    <t>14166.1%</t>
+  </si>
+  <si>
+    <t>1229.9%</t>
+  </si>
+  <si>
+    <t>-49.2%</t>
+  </si>
+  <si>
+    <t>68.2%</t>
+  </si>
+  <si>
+    <t>285.7%</t>
+  </si>
+  <si>
+    <t>62.4%</t>
+  </si>
+  <si>
+    <t>123.3%</t>
+  </si>
+  <si>
+    <t>117.9%</t>
+  </si>
+  <si>
+    <t>3197.3%</t>
+  </si>
+  <si>
+    <t>341.0%</t>
+  </si>
+  <si>
+    <t>-17.5%</t>
+  </si>
+  <si>
+    <t>-8.1%</t>
+  </si>
+  <si>
+    <t>396.2%</t>
+  </si>
+  <si>
+    <t>300.4%</t>
+  </si>
+  <si>
+    <t>3950.7%</t>
+  </si>
+  <si>
+    <t>604.7%</t>
+  </si>
+  <si>
+    <t>-33.6%</t>
+  </si>
+  <si>
     <t>MNLogit: 'Outcomes 3.08 years after a person's first route started', table 0</t>
   </si>
   <si>
     <t>cli_outcome</t>
   </si>
   <si>
-    <t>2026-06-21 14:27</t>
-  </si>
-  <si>
     <t>2014</t>
   </si>
   <si>
@@ -262,6 +454,162 @@
     <t>MNLogit: 'Outcomes 3.08 years after a person's first route started', odds ratios</t>
   </si>
   <si>
+    <t>-98.0%</t>
+  </si>
+  <si>
+    <t>-64.4%</t>
+  </si>
+  <si>
+    <t>272.8%</t>
+  </si>
+  <si>
+    <t>-74.1%</t>
+  </si>
+  <si>
+    <t>39.2%</t>
+  </si>
+  <si>
+    <t>200.8%</t>
+  </si>
+  <si>
+    <t>34.1%</t>
+  </si>
+  <si>
+    <t>75.6%</t>
+  </si>
+  <si>
+    <t>688.2%</t>
+  </si>
+  <si>
+    <t>276.0%</t>
+  </si>
+  <si>
+    <t>-49.8%</t>
+  </si>
+  <si>
+    <t>-86.2%</t>
+  </si>
+  <si>
+    <t>44.3%</t>
+  </si>
+  <si>
+    <t>305.5%</t>
+  </si>
+  <si>
+    <t>243.8%</t>
+  </si>
+  <si>
+    <t>632.3%</t>
+  </si>
+  <si>
+    <t>320.2%</t>
+  </si>
+  <si>
+    <t>-58.6%</t>
+  </si>
+  <si>
+    <t>-86.6%</t>
+  </si>
+  <si>
+    <t>75.5%</t>
+  </si>
+  <si>
+    <t>-79.4%</t>
+  </si>
+  <si>
+    <t>10.3%</t>
+  </si>
+  <si>
+    <t>118.2%</t>
+  </si>
+  <si>
+    <t>6.3%</t>
+  </si>
+  <si>
+    <t>29.3%</t>
+  </si>
+  <si>
+    <t>73.6%</t>
+  </si>
+  <si>
+    <t>199.0%</t>
+  </si>
+  <si>
+    <t>-66.9%</t>
+  </si>
+  <si>
+    <t>-89.6%</t>
+  </si>
+  <si>
+    <t>10.5%</t>
+  </si>
+  <si>
+    <t>187.9%</t>
+  </si>
+  <si>
+    <t>150.3%</t>
+  </si>
+  <si>
+    <t>51.4%</t>
+  </si>
+  <si>
+    <t>219.5%</t>
+  </si>
+  <si>
+    <t>-76.4%</t>
+  </si>
+  <si>
+    <t>-95.6%</t>
+  </si>
+  <si>
+    <t>-5.5%</t>
+  </si>
+  <si>
+    <t>692.0%</t>
+  </si>
+  <si>
+    <t>-67.4%</t>
+  </si>
+  <si>
+    <t>314.5%</t>
+  </si>
+  <si>
+    <t>69.1%</t>
+  </si>
+  <si>
+    <t>138.4%</t>
+  </si>
+  <si>
+    <t>3478.9%</t>
+  </si>
+  <si>
+    <t>372.8%</t>
+  </si>
+  <si>
+    <t>-23.8%</t>
+  </si>
+  <si>
+    <t>-81.8%</t>
+  </si>
+  <si>
+    <t>88.5%</t>
+  </si>
+  <si>
+    <t>471.2%</t>
+  </si>
+  <si>
+    <t>372.3%</t>
+  </si>
+  <si>
+    <t>3441.8%</t>
+  </si>
+  <si>
+    <t>452.6%</t>
+  </si>
+  <si>
+    <t>-27.4%</t>
+  </si>
+  <si>
     <t>Logit: 'People with multiple returns during 7.5 yrs', table 0</t>
   </si>
   <si>
@@ -310,12 +658,75 @@
     <t>Logit: 'People with multiple returns during 7.5 yrs', odds ratios</t>
   </si>
   <si>
+    <t>-98.7%</t>
+  </si>
+  <si>
+    <t>65.3%</t>
+  </si>
+  <si>
+    <t>119.0%</t>
+  </si>
+  <si>
+    <t>47.3%</t>
+  </si>
+  <si>
+    <t>69.5%</t>
+  </si>
+  <si>
+    <t>116.5%</t>
+  </si>
+  <si>
+    <t>565.4%</t>
+  </si>
+  <si>
+    <t>-99.1%</t>
+  </si>
+  <si>
+    <t>26.6%</t>
+  </si>
+  <si>
+    <t>65.6%</t>
+  </si>
+  <si>
+    <t>13.1%</t>
+  </si>
+  <si>
+    <t>28.8%</t>
+  </si>
+  <si>
+    <t>13.7%</t>
+  </si>
+  <si>
+    <t>356.7%</t>
+  </si>
+  <si>
+    <t>115.7%</t>
+  </si>
+  <si>
+    <t>189.7%</t>
+  </si>
+  <si>
+    <t>91.8%</t>
+  </si>
+  <si>
+    <t>123.0%</t>
+  </si>
+  <si>
+    <t>312.1%</t>
+  </si>
+  <si>
+    <t>869.5%</t>
+  </si>
+  <si>
     <t>Logit: 'People with a route in top 10% of route durations', table 0</t>
   </si>
   <si>
     <t>has_longer_term_rt</t>
   </si>
   <si>
+    <t>2026-06-21 14:50</t>
+  </si>
+  <si>
     <t>3032</t>
   </si>
   <si>
@@ -352,6 +763,54 @@
     <t>Logit: 'People with a route in top 10% of route durations', odds ratios</t>
   </si>
   <si>
+    <t>-68.2%</t>
+  </si>
+  <si>
+    <t>-42.7%</t>
+  </si>
+  <si>
+    <t>-41.1%</t>
+  </si>
+  <si>
+    <t>-53.9%</t>
+  </si>
+  <si>
+    <t>-70.1%</t>
+  </si>
+  <si>
+    <t>-72.5%</t>
+  </si>
+  <si>
+    <t>-54.0%</t>
+  </si>
+  <si>
+    <t>-66.8%</t>
+  </si>
+  <si>
+    <t>15.8%</t>
+  </si>
+  <si>
+    <t>-78.8%</t>
+  </si>
+  <si>
+    <t>-63.3%</t>
+  </si>
+  <si>
+    <t>-28.5%</t>
+  </si>
+  <si>
+    <t>-24.4%</t>
+  </si>
+  <si>
+    <t>-35.9%</t>
+  </si>
+  <si>
+    <t>130.0%</t>
+  </si>
+  <si>
+    <t>-57.8%</t>
+  </si>
+  <si>
     <t>Logit: 'Returns within 2 years after moving to independent accommodation', table 0</t>
   </si>
   <si>
@@ -397,6 +856,39 @@
     <t>Logit: 'Returns within 2 years after moving to independent accommodation', odds ratios</t>
   </si>
   <si>
+    <t>-99.5%</t>
+  </si>
+  <si>
+    <t>1088.3%</t>
+  </si>
+  <si>
+    <t>222.9%</t>
+  </si>
+  <si>
+    <t>1313.6%</t>
+  </si>
+  <si>
+    <t>-99.9%</t>
+  </si>
+  <si>
+    <t>6.0%</t>
+  </si>
+  <si>
+    <t>306.7%</t>
+  </si>
+  <si>
+    <t>-98.4%</t>
+  </si>
+  <si>
+    <t>4623.1%</t>
+  </si>
+  <si>
+    <t>883.8%</t>
+  </si>
+  <si>
+    <t>4813.4%</t>
+  </si>
+  <si>
     <t>MNLogit: 'Outcomes from individual placements (vs independent accommodation)', table 0</t>
   </si>
   <si>
@@ -493,12 +985,387 @@
     <t>Insecure outcome (external)</t>
   </si>
   <si>
+    <t>25.0%</t>
+  </si>
+  <si>
+    <t>58.0%</t>
+  </si>
+  <si>
+    <t>270.0%</t>
+  </si>
+  <si>
+    <t>136.0%</t>
+  </si>
+  <si>
+    <t>-82.6%</t>
+  </si>
+  <si>
+    <t>55.8%</t>
+  </si>
+  <si>
+    <t>-39.6%</t>
+  </si>
+  <si>
+    <t>34.3%</t>
+  </si>
+  <si>
+    <t>214.3%</t>
+  </si>
+  <si>
+    <t>35.7%</t>
+  </si>
+  <si>
+    <t>56.4%</t>
+  </si>
+  <si>
+    <t>124.4%</t>
+  </si>
+  <si>
+    <t>434.3%</t>
+  </si>
+  <si>
+    <t>743.6%</t>
+  </si>
+  <si>
+    <t>-50.6%</t>
+  </si>
+  <si>
+    <t>-82.9%</t>
+  </si>
+  <si>
+    <t>31.4%</t>
+  </si>
+  <si>
+    <t>105.0%</t>
+  </si>
+  <si>
+    <t>91.3%</t>
+  </si>
+  <si>
+    <t>337.6%</t>
+  </si>
+  <si>
+    <t>417.6%</t>
+  </si>
+  <si>
+    <t>-77.5%</t>
+  </si>
+  <si>
+    <t>29.8%</t>
+  </si>
+  <si>
+    <t>-35.2%</t>
+  </si>
+  <si>
+    <t>209.9%</t>
+  </si>
+  <si>
+    <t>52.5%</t>
+  </si>
+  <si>
+    <t>208.2%</t>
+  </si>
+  <si>
+    <t>232.2%</t>
+  </si>
+  <si>
+    <t>309.5%</t>
+  </si>
+  <si>
+    <t>-56.9%</t>
+  </si>
+  <si>
+    <t>-77.3%</t>
+  </si>
+  <si>
+    <t>45.4%</t>
+  </si>
+  <si>
+    <t>-34.8%</t>
+  </si>
+  <si>
+    <t>241.4%</t>
+  </si>
+  <si>
+    <t>65.1%</t>
+  </si>
+  <si>
+    <t>164.5%</t>
+  </si>
+  <si>
+    <t>-96.3%</t>
+  </si>
+  <si>
+    <t>-56.6%</t>
+  </si>
+  <si>
+    <t>-67.8%</t>
+  </si>
+  <si>
+    <t>121.3%</t>
+  </si>
+  <si>
+    <t>629.3%</t>
+  </si>
+  <si>
+    <t>722.6%</t>
+  </si>
+  <si>
+    <t>3.0%</t>
+  </si>
+  <si>
+    <t>9.7%</t>
+  </si>
+  <si>
+    <t>28.5%</t>
+  </si>
+  <si>
+    <t>94.2%</t>
+  </si>
+  <si>
+    <t>-86.9%</t>
+  </si>
+  <si>
+    <t>25.9%</t>
+  </si>
+  <si>
+    <t>-52.9%</t>
+  </si>
+  <si>
+    <t>6.9%</t>
+  </si>
+  <si>
+    <t>133.6%</t>
+  </si>
+  <si>
+    <t>10.0%</t>
+  </si>
+  <si>
+    <t>6.7%</t>
+  </si>
+  <si>
+    <t>70.7%</t>
+  </si>
+  <si>
+    <t>85.0%</t>
+  </si>
+  <si>
+    <t>565.8%</t>
+  </si>
+  <si>
+    <t>-69.1%</t>
+  </si>
+  <si>
+    <t>-87.4%</t>
+  </si>
+  <si>
+    <t>1.7%</t>
+  </si>
+  <si>
+    <t>46.2%</t>
+  </si>
+  <si>
+    <t>27.9%</t>
+  </si>
+  <si>
+    <t>48.0%</t>
+  </si>
+  <si>
+    <t>301.6%</t>
+  </si>
+  <si>
+    <t>-83.1%</t>
+  </si>
+  <si>
+    <t>2.5%</t>
+  </si>
+  <si>
+    <t>-51.0%</t>
+  </si>
+  <si>
+    <t>125.8%</t>
+  </si>
+  <si>
+    <t>10.7%</t>
+  </si>
+  <si>
+    <t>130.8%</t>
+  </si>
+  <si>
+    <t>7.8%</t>
+  </si>
+  <si>
+    <t>219.3%</t>
+  </si>
+  <si>
+    <t>-74.9%</t>
+  </si>
+  <si>
+    <t>-83.2%</t>
+  </si>
+  <si>
+    <t>13.5%</t>
+  </si>
+  <si>
+    <t>-56.7%</t>
+  </si>
+  <si>
+    <t>146.0%</t>
+  </si>
+  <si>
+    <t>19.5%</t>
+  </si>
+  <si>
+    <t>-98.2%</t>
+  </si>
+  <si>
+    <t>-78.4%</t>
+  </si>
+  <si>
+    <t>-85.2%</t>
+  </si>
+  <si>
+    <t>36.5%</t>
+  </si>
+  <si>
+    <t>9.5%</t>
+  </si>
+  <si>
+    <t>347.5%</t>
+  </si>
+  <si>
+    <t>51.7%</t>
+  </si>
+  <si>
+    <t>133.0%</t>
+  </si>
+  <si>
+    <t>127.5%</t>
+  </si>
+  <si>
+    <t>964.9%</t>
+  </si>
+  <si>
+    <t>186.7%</t>
+  </si>
+  <si>
+    <t>-77.0%</t>
+  </si>
+  <si>
+    <t>92.8%</t>
+  </si>
+  <si>
+    <t>-22.5%</t>
+  </si>
+  <si>
+    <t>68.6%</t>
+  </si>
+  <si>
+    <t>323.0%</t>
+  </si>
+  <si>
+    <t>67.5%</t>
+  </si>
+  <si>
+    <t>129.4%</t>
+  </si>
+  <si>
+    <t>195.1%</t>
+  </si>
+  <si>
+    <t>1442.9%</t>
+  </si>
+  <si>
+    <t>968.8%</t>
+  </si>
+  <si>
+    <t>-21.0%</t>
+  </si>
+  <si>
+    <t>-76.8%</t>
+  </si>
+  <si>
+    <t>69.7%</t>
+  </si>
+  <si>
+    <t>187.4%</t>
+  </si>
+  <si>
+    <t>186.1%</t>
+  </si>
+  <si>
+    <t>1194.4%</t>
+  </si>
+  <si>
+    <t>567.0%</t>
+  </si>
+  <si>
+    <t>-70.0%</t>
+  </si>
+  <si>
+    <t>64.4%</t>
+  </si>
+  <si>
+    <t>-14.4%</t>
+  </si>
+  <si>
+    <t>325.3%</t>
+  </si>
+  <si>
+    <t>110.1%</t>
+  </si>
+  <si>
+    <t>311.7%</t>
+  </si>
+  <si>
+    <t>924.0%</t>
+  </si>
+  <si>
+    <t>425.2%</t>
+  </si>
+  <si>
+    <t>-26.1%</t>
+  </si>
+  <si>
+    <t>-69.5%</t>
+  </si>
+  <si>
+    <t>86.1%</t>
+  </si>
+  <si>
+    <t>-1.8%</t>
+  </si>
+  <si>
+    <t>373.9%</t>
+  </si>
+  <si>
+    <t>128.0%</t>
+  </si>
+  <si>
+    <t>241.2%</t>
+  </si>
+  <si>
+    <t>-92.6%</t>
+  </si>
+  <si>
+    <t>-13.0%</t>
+  </si>
+  <si>
+    <t>-29.6%</t>
+  </si>
+  <si>
+    <t>258.8%</t>
+  </si>
+  <si>
+    <t>4755.5%</t>
+  </si>
+  <si>
+    <t>1411.9%</t>
+  </si>
+  <si>
     <t>MNLogit: 'Outcomes from individual placements (vs. forwards moves)', table 0</t>
   </si>
   <si>
-    <t>2026-06-21 14:28</t>
-  </si>
-  <si>
     <t>5191</t>
   </si>
   <si>
@@ -551,6 +1418,267 @@
   </si>
   <si>
     <t>Independent accommodation</t>
+  </si>
+  <si>
+    <t>-96.0%</t>
+  </si>
+  <si>
+    <t>-57.6%</t>
+  </si>
+  <si>
+    <t>103.9%</t>
+  </si>
+  <si>
+    <t>246.4%</t>
+  </si>
+  <si>
+    <t>25.2%</t>
+  </si>
+  <si>
+    <t>-21.8%</t>
+  </si>
+  <si>
+    <t>-40.9%</t>
+  </si>
+  <si>
+    <t>-40.2%</t>
+  </si>
+  <si>
+    <t>-74.0%</t>
+  </si>
+  <si>
+    <t>-58.5%</t>
+  </si>
+  <si>
+    <t>35.6%</t>
+  </si>
+  <si>
+    <t>92.9%</t>
+  </si>
+  <si>
+    <t>-38.6%</t>
+  </si>
+  <si>
+    <t>-80.0%</t>
+  </si>
+  <si>
+    <t>117.3%</t>
+  </si>
+  <si>
+    <t>-79.1%</t>
+  </si>
+  <si>
+    <t>42.2%</t>
+  </si>
+  <si>
+    <t>-24.1%</t>
+  </si>
+  <si>
+    <t>82.2%</t>
+  </si>
+  <si>
+    <t>19.1%</t>
+  </si>
+  <si>
+    <t>106.6%</t>
+  </si>
+  <si>
+    <t>253.4%</t>
+  </si>
+  <si>
+    <t>-45.9%</t>
+  </si>
+  <si>
+    <t>-72.4%</t>
+  </si>
+  <si>
+    <t>82.3%</t>
+  </si>
+  <si>
+    <t>-29.4%</t>
+  </si>
+  <si>
+    <t>33.8%</t>
+  </si>
+  <si>
+    <t>178.2%</t>
+  </si>
+  <si>
+    <t>70.4%</t>
+  </si>
+  <si>
+    <t>-51.2%</t>
+  </si>
+  <si>
+    <t>-97.9%</t>
+  </si>
+  <si>
+    <t>-78.0%</t>
+  </si>
+  <si>
+    <t>95.1%</t>
+  </si>
+  <si>
+    <t>2.1%</t>
+  </si>
+  <si>
+    <t>-35.3%</t>
+  </si>
+  <si>
+    <t>-55.7%</t>
+  </si>
+  <si>
+    <t>-58.1%</t>
+  </si>
+  <si>
+    <t>-90.9%</t>
+  </si>
+  <si>
+    <t>-65.6%</t>
+  </si>
+  <si>
+    <t>-80.2%</t>
+  </si>
+  <si>
+    <t>49.2%</t>
+  </si>
+  <si>
+    <t>16.4%</t>
+  </si>
+  <si>
+    <t>-60.4%</t>
+  </si>
+  <si>
+    <t>-84.8%</t>
+  </si>
+  <si>
+    <t>73.9%</t>
+  </si>
+  <si>
+    <t>-83.7%</t>
+  </si>
+  <si>
+    <t>18.9%</t>
+  </si>
+  <si>
+    <t>-38.8%</t>
+  </si>
+  <si>
+    <t>47.9%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>68.4%</t>
+  </si>
+  <si>
+    <t>188.1%</t>
+  </si>
+  <si>
+    <t>-63.7%</t>
+  </si>
+  <si>
+    <t>-78.6%</t>
+  </si>
+  <si>
+    <t>43.8%</t>
+  </si>
+  <si>
+    <t>1.6%</t>
+  </si>
+  <si>
+    <t>121.5%</t>
+  </si>
+  <si>
+    <t>37.3%</t>
+  </si>
+  <si>
+    <t>-92.3%</t>
+  </si>
+  <si>
+    <t>-18.0%</t>
+  </si>
+  <si>
+    <t>222.8%</t>
+  </si>
+  <si>
+    <t>515.1%</t>
+  </si>
+  <si>
+    <t>53.5%</t>
+  </si>
+  <si>
+    <t>-21.1%</t>
+  </si>
+  <si>
+    <t>-14.7%</t>
+  </si>
+  <si>
+    <t>-25.2%</t>
+  </si>
+  <si>
+    <t>-65.9%</t>
+  </si>
+  <si>
+    <t>69.3%</t>
+  </si>
+  <si>
+    <t>149.4%</t>
+  </si>
+  <si>
+    <t>99.7%</t>
+  </si>
+  <si>
+    <t>-4.9%</t>
+  </si>
+  <si>
+    <t>-73.6%</t>
+  </si>
+  <si>
+    <t>171.5%</t>
+  </si>
+  <si>
+    <t>-73.2%</t>
+  </si>
+  <si>
+    <t>70.0%</t>
+  </si>
+  <si>
+    <t>-5.8%</t>
+  </si>
+  <si>
+    <t>41.7%</t>
+  </si>
+  <si>
+    <t>153.6%</t>
+  </si>
+  <si>
+    <t>333.5%</t>
+  </si>
+  <si>
+    <t>-19.6%</t>
+  </si>
+  <si>
+    <t>-64.3%</t>
+  </si>
+  <si>
+    <t>131.1%</t>
+  </si>
+  <si>
+    <t>-0.7%</t>
+  </si>
+  <si>
+    <t>76.2%</t>
+  </si>
+  <si>
+    <t>249.6%</t>
+  </si>
+  <si>
+    <t>111.6%</t>
+  </si>
+  <si>
+    <t>-22.7%</t>
   </si>
 </sst>
 </file>
@@ -1911,7 +3039,7 @@
         <v>1.351763038172491</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:10">
       <c r="A49" s="2" t="s">
         <v>47</v>
       </c>
@@ -1937,7 +3065,7 @@
         <v>2.587692101413705</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:10">
       <c r="A50" s="2" t="s">
         <v>48</v>
       </c>
@@ -1963,7 +3091,7 @@
         <v>0.6804843090684729</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:10">
       <c r="A51" s="2" t="s">
         <v>49</v>
       </c>
@@ -1989,7 +3117,7 @@
         <v>4.960468528318827</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:10">
       <c r="A52" s="2" t="s">
         <v>50</v>
       </c>
@@ -2015,12 +3143,12 @@
         <v>0.5639181848985116</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:10">
       <c r="C55" s="2" t="s">
         <v>56</v>
       </c>
@@ -2036,10 +3164,19 @@
       <c r="G55" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="56" spans="1:8">
+      <c r="H55" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>40</v>
@@ -2059,8 +3196,17 @@
       <c r="G56" s="1">
         <v>0.04581644818296126</v>
       </c>
-    </row>
-    <row r="57" spans="1:8">
+      <c r="H56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
         <v>42</v>
@@ -2080,8 +3226,17 @@
       <c r="G57" s="1">
         <v>0.926661341981682</v>
       </c>
-    </row>
-    <row r="58" spans="1:8">
+      <c r="H57" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" s="2"/>
       <c r="B58" s="2" t="s">
         <v>41</v>
@@ -2099,7 +3254,7 @@
         <v>1.373695712421397</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:10">
       <c r="A59" s="2"/>
       <c r="B59" s="2" t="s">
         <v>45</v>
@@ -2117,7 +3272,7 @@
         <v>2.701844901576165</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:10">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
         <v>46</v>
@@ -2137,8 +3292,17 @@
       <c r="G60" s="1">
         <v>3.86423231770467</v>
       </c>
-    </row>
-    <row r="61" spans="1:8">
+      <c r="H60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" s="2"/>
       <c r="B61" s="2" t="s">
         <v>50</v>
@@ -2156,7 +3320,7 @@
         <v>1.757545414730929</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:10">
       <c r="A62" s="2"/>
       <c r="B62" s="2" t="s">
         <v>48</v>
@@ -2174,7 +3338,7 @@
         <v>1.974833930645315</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:10">
       <c r="A63" s="2"/>
       <c r="B63" s="2" t="s">
         <v>49</v>
@@ -2194,8 +3358,17 @@
       <c r="G63" s="1">
         <v>142.6606207819088</v>
       </c>
-    </row>
-    <row r="64" spans="1:8">
+      <c r="H63" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" s="2"/>
       <c r="B64" s="2" t="s">
         <v>47</v>
@@ -2215,8 +3388,17 @@
       <c r="G64" s="1">
         <v>13.29904331468318</v>
       </c>
-    </row>
-    <row r="65" spans="1:7">
+      <c r="H64" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" s="2"/>
       <c r="B65" s="2" t="s">
         <v>44</v>
@@ -2234,7 +3416,7 @@
         <v>10.09228256693748</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:10">
       <c r="A66" s="2"/>
       <c r="B66" s="2" t="s">
         <v>43</v>
@@ -2252,9 +3434,9 @@
         <v>2.394283605175326</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:10">
       <c r="A67" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>40</v>
@@ -2274,8 +3456,17 @@
       <c r="G67" s="1">
         <v>0.5080470672184505</v>
       </c>
-    </row>
-    <row r="68" spans="1:7">
+      <c r="H67" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" s="2"/>
       <c r="B68" s="2" t="s">
         <v>42</v>
@@ -2295,8 +3486,17 @@
       <c r="G68" s="1">
         <v>1.681839528630254</v>
       </c>
-    </row>
-    <row r="69" spans="1:7">
+      <c r="H68" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" s="2"/>
       <c r="B69" s="2" t="s">
         <v>41</v>
@@ -2314,7 +3514,7 @@
         <v>1.013978308701296</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:10">
       <c r="A70" s="2"/>
       <c r="B70" s="2" t="s">
         <v>45</v>
@@ -2334,8 +3534,17 @@
       <c r="G70" s="1">
         <v>3.857018231515841</v>
       </c>
-    </row>
-    <row r="71" spans="1:7">
+      <c r="H70" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" s="2"/>
       <c r="B71" s="2" t="s">
         <v>46</v>
@@ -2355,8 +3564,17 @@
       <c r="G71" s="1">
         <v>1.624141156251794</v>
       </c>
-    </row>
-    <row r="72" spans="1:7">
+      <c r="H71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" s="2"/>
       <c r="B72" s="2" t="s">
         <v>50</v>
@@ -2376,8 +3594,17 @@
       <c r="G72" s="1">
         <v>2.232829484867051</v>
       </c>
-    </row>
-    <row r="73" spans="1:7">
+      <c r="H72" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73" s="2"/>
       <c r="B73" s="2" t="s">
         <v>48</v>
@@ -2397,8 +3624,17 @@
       <c r="G73" s="1">
         <v>2.179267220765974</v>
       </c>
-    </row>
-    <row r="74" spans="1:7">
+      <c r="H73" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74" s="2"/>
       <c r="B74" s="2" t="s">
         <v>49</v>
@@ -2418,8 +3654,17 @@
       <c r="G74" s="1">
         <v>32.9726072810721</v>
       </c>
-    </row>
-    <row r="75" spans="1:7">
+      <c r="H74" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75" s="2"/>
       <c r="B75" s="2" t="s">
         <v>47</v>
@@ -2439,8 +3684,17 @@
       <c r="G75" s="1">
         <v>4.409505404014768</v>
       </c>
-    </row>
-    <row r="76" spans="1:7">
+      <c r="H75" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
       <c r="A76" s="2"/>
       <c r="B76" s="2" t="s">
         <v>44</v>
@@ -2458,7 +3712,7 @@
         <v>1.610862188271773</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:10">
       <c r="A77" s="2"/>
       <c r="B77" s="2" t="s">
         <v>43</v>
@@ -2478,10 +3732,19 @@
       <c r="G77" s="1">
         <v>0.8249921521743914</v>
       </c>
-    </row>
-    <row r="78" spans="1:7">
+      <c r="H77" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
       <c r="A78" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>40</v>
@@ -2501,8 +3764,17 @@
       <c r="G78" s="1">
         <v>0.3276507612213397</v>
       </c>
-    </row>
-    <row r="79" spans="1:7">
+      <c r="H78" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79" s="2"/>
       <c r="B79" s="2" t="s">
         <v>42</v>
@@ -2520,7 +3792,7 @@
         <v>1.572247823258985</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:10">
       <c r="A80" s="2"/>
       <c r="B80" s="2" t="s">
         <v>41</v>
@@ -2540,8 +3812,17 @@
       <c r="G80" s="1">
         <v>0.9188581516919314</v>
       </c>
-    </row>
-    <row r="81" spans="1:7">
+      <c r="H80" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81" s="2"/>
       <c r="B81" s="2" t="s">
         <v>45</v>
@@ -2561,8 +3842,17 @@
       <c r="G81" s="1">
         <v>4.962497240457521</v>
       </c>
-    </row>
-    <row r="82" spans="1:7">
+      <c r="H81" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82" s="2"/>
       <c r="B82" s="2" t="s">
         <v>46</v>
@@ -2580,7 +3870,7 @@
         <v>1.423887029344143</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:10">
       <c r="A83" s="2"/>
       <c r="B83" s="2" t="s">
         <v>50</v>
@@ -2598,7 +3888,7 @@
         <v>1.942568158043056</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:10">
       <c r="A84" s="2"/>
       <c r="B84" s="2" t="s">
         <v>48</v>
@@ -2618,8 +3908,17 @@
       <c r="G84" s="1">
         <v>4.004102543708013</v>
       </c>
-    </row>
-    <row r="85" spans="1:7">
+      <c r="H84" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
       <c r="A85" s="2"/>
       <c r="B85" s="2" t="s">
         <v>49</v>
@@ -2639,8 +3938,17 @@
       <c r="G85" s="1">
         <v>40.50674143577799</v>
       </c>
-    </row>
-    <row r="86" spans="1:7">
+      <c r="H85" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86" s="2"/>
       <c r="B86" s="2" t="s">
         <v>47</v>
@@ -2660,8 +3968,17 @@
       <c r="G86" s="1">
         <v>7.04655893929631</v>
       </c>
-    </row>
-    <row r="87" spans="1:7">
+      <c r="H86" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87" s="2"/>
       <c r="B87" s="2" t="s">
         <v>44</v>
@@ -2679,7 +3996,7 @@
         <v>2.271698874493443</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:10">
       <c r="A88" s="2"/>
       <c r="B88" s="2" t="s">
         <v>43</v>
@@ -2699,13 +4016,22 @@
       <c r="G88" s="1">
         <v>0.6642218570413033</v>
       </c>
-    </row>
-    <row r="90" spans="1:7">
+      <c r="H88" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
       <c r="B91" s="2">
         <v>0</v>
       </c>
@@ -2719,7 +4045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:10">
       <c r="A92" s="2">
         <v>0</v>
       </c>
@@ -2736,7 +4062,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:10">
       <c r="A93" s="2">
         <v>1</v>
       </c>
@@ -2744,16 +4070,16 @@
         <v>2</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
       <c r="A94" s="2">
         <v>2</v>
       </c>
@@ -2761,16 +4087,16 @@
         <v>3</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
       <c r="A95" s="2">
         <v>3</v>
       </c>
@@ -2778,16 +4104,16 @@
         <v>4</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
       <c r="A96" s="2">
         <v>4</v>
       </c>
@@ -2795,13 +4121,13 @@
         <v>5</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -2812,13 +4138,13 @@
         <v>6</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -2835,7 +4161,7 @@
         <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -2846,7 +4172,7 @@
         <v>8</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>24</v>
@@ -2857,12 +4183,12 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>75</v>
+        <v>139</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="B102" s="2" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>34</v>
@@ -3119,12 +4445,12 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" t="s">
-        <v>77</v>
+        <v>141</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="B114" s="2" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>34</v>
@@ -3381,12 +4707,12 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="B126" s="2" t="s">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>34</v>
@@ -3459,7 +4785,7 @@
         <v>-0.05662752269617033</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:10">
       <c r="A129" s="2" t="s">
         <v>43</v>
       </c>
@@ -3485,7 +4811,7 @@
         <v>0.9658182630324635</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:10">
       <c r="A130" s="2" t="s">
         <v>44</v>
       </c>
@@ -3511,7 +4837,7 @@
         <v>2.188265962122714</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:10">
       <c r="A131" s="2" t="s">
         <v>45</v>
       </c>
@@ -3537,7 +4863,7 @@
         <v>1.506320001443703</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:10">
       <c r="A132" s="2" t="s">
         <v>46</v>
       </c>
@@ -3563,7 +4889,7 @@
         <v>1.182250792286782</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:10">
       <c r="A133" s="2" t="s">
         <v>47</v>
       </c>
@@ -3589,7 +4915,7 @@
         <v>2.06934081441574</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:10">
       <c r="A134" s="2" t="s">
         <v>48</v>
       </c>
@@ -3615,7 +4941,7 @@
         <v>1.035544504843304</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:10">
       <c r="A135" s="2" t="s">
         <v>49</v>
       </c>
@@ -3641,12 +4967,12 @@
         <v>4.777935751991526</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:10">
       <c r="A137" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
       <c r="C138" s="2" t="s">
         <v>56</v>
       </c>
@@ -3662,10 +4988,19 @@
       <c r="G138" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="139" spans="1:8">
+      <c r="H138" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
       <c r="A139" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>40</v>
@@ -3685,8 +5020,17 @@
       <c r="G139" s="1">
         <v>0.04391859575526413</v>
       </c>
-    </row>
-    <row r="140" spans="1:8">
+      <c r="H139" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10">
       <c r="A140" s="2"/>
       <c r="B140" s="2" t="s">
         <v>42</v>
@@ -3706,8 +5050,17 @@
       <c r="G140" s="1">
         <v>0.9449459747530107</v>
       </c>
-    </row>
-    <row r="141" spans="1:8">
+      <c r="H140" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
       <c r="A141" s="2"/>
       <c r="B141" s="2" t="s">
         <v>45</v>
@@ -3725,7 +5078,7 @@
         <v>4.510103045337493</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:10">
       <c r="A142" s="2"/>
       <c r="B142" s="2" t="s">
         <v>46</v>
@@ -3743,7 +5096,7 @@
         <v>3.26170737286919</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:10">
       <c r="A143" s="2"/>
       <c r="B143" s="2" t="s">
         <v>48</v>
@@ -3761,7 +5114,7 @@
         <v>2.816639491998655</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:10">
       <c r="A144" s="2"/>
       <c r="B144" s="2" t="s">
         <v>49</v>
@@ -3779,7 +5132,7 @@
         <v>118.8587427118707</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:10">
       <c r="A145" s="2"/>
       <c r="B145" s="2" t="s">
         <v>47</v>
@@ -3799,8 +5152,17 @@
       <c r="G145" s="1">
         <v>7.919600910083526</v>
       </c>
-    </row>
-    <row r="146" spans="1:7">
+      <c r="H145" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
       <c r="A146" s="2"/>
       <c r="B146" s="2" t="s">
         <v>44</v>
@@ -3818,7 +5180,7 @@
         <v>8.919732542544503</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:10">
       <c r="A147" s="2"/>
       <c r="B147" s="2" t="s">
         <v>43</v>
@@ -3836,9 +5198,9 @@
         <v>2.626936302140708</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:10">
       <c r="A148" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>40</v>
@@ -3858,8 +5220,17 @@
       <c r="G148" s="1">
         <v>0.3256495677815476</v>
       </c>
-    </row>
-    <row r="149" spans="1:7">
+      <c r="H148" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10">
       <c r="A149" s="2"/>
       <c r="B149" s="2" t="s">
         <v>42</v>
@@ -3879,8 +5250,17 @@
       <c r="G149" s="1">
         <v>1.755971071873098</v>
       </c>
-    </row>
-    <row r="150" spans="1:7">
+      <c r="H149" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
       <c r="A150" s="2"/>
       <c r="B150" s="2" t="s">
         <v>45</v>
@@ -3900,8 +5280,17 @@
       <c r="G150" s="1">
         <v>4.144763944612052</v>
       </c>
-    </row>
-    <row r="151" spans="1:7">
+      <c r="H150" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J150" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10">
       <c r="A151" s="2"/>
       <c r="B151" s="2" t="s">
         <v>46</v>
@@ -3921,8 +5310,17 @@
       <c r="G151" s="1">
         <v>1.691278386297725</v>
       </c>
-    </row>
-    <row r="152" spans="1:7">
+      <c r="H151" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10">
       <c r="A152" s="2"/>
       <c r="B152" s="2" t="s">
         <v>48</v>
@@ -3942,8 +5340,17 @@
       <c r="G152" s="1">
         <v>2.384295073945052</v>
       </c>
-    </row>
-    <row r="153" spans="1:7">
+      <c r="H152" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10">
       <c r="A153" s="2"/>
       <c r="B153" s="2" t="s">
         <v>49</v>
@@ -3963,8 +5370,17 @@
       <c r="G153" s="1">
         <v>35.78899032621171</v>
       </c>
-    </row>
-    <row r="154" spans="1:7">
+      <c r="H153" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10">
       <c r="A154" s="2"/>
       <c r="B154" s="2" t="s">
         <v>47</v>
@@ -3984,8 +5400,17 @@
       <c r="G154" s="1">
         <v>4.727868779576153</v>
       </c>
-    </row>
-    <row r="155" spans="1:7">
+      <c r="H154" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J154" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10">
       <c r="A155" s="2"/>
       <c r="B155" s="2" t="s">
         <v>44</v>
@@ -4003,7 +5428,7 @@
         <v>1.631469422503574</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:10">
       <c r="A156" s="2"/>
       <c r="B156" s="2" t="s">
         <v>43</v>
@@ -4023,10 +5448,19 @@
       <c r="G156" s="1">
         <v>0.7618872244974803</v>
       </c>
-    </row>
-    <row r="157" spans="1:7">
+      <c r="H156" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10">
       <c r="A157" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>40</v>
@@ -4046,8 +5480,17 @@
       <c r="G157" s="1">
         <v>0.1819923553546058</v>
       </c>
-    </row>
-    <row r="158" spans="1:7">
+      <c r="H157" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J157" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10">
       <c r="A158" s="2"/>
       <c r="B158" s="2" t="s">
         <v>42</v>
@@ -4067,8 +5510,17 @@
       <c r="G158" s="1">
         <v>1.885238060436522</v>
       </c>
-    </row>
-    <row r="159" spans="1:7">
+      <c r="H158" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J158" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10">
       <c r="A159" s="2"/>
       <c r="B159" s="2" t="s">
         <v>45</v>
@@ -4088,8 +5540,17 @@
       <c r="G159" s="1">
         <v>5.7115554648816</v>
       </c>
-    </row>
-    <row r="160" spans="1:7">
+      <c r="H159" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J159" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10">
       <c r="A160" s="2"/>
       <c r="B160" s="2" t="s">
         <v>46</v>
@@ -4107,7 +5568,7 @@
         <v>1.120591497376266</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" spans="1:10">
       <c r="A161" s="2"/>
       <c r="B161" s="2" t="s">
         <v>48</v>
@@ -4127,8 +5588,17 @@
       <c r="G161" s="1">
         <v>4.722713813072352</v>
       </c>
-    </row>
-    <row r="162" spans="1:7">
+      <c r="H161" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J161" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10">
       <c r="A162" s="2"/>
       <c r="B162" s="2" t="s">
         <v>49</v>
@@ -4148,8 +5618,17 @@
       <c r="G162" s="1">
         <v>35.41788153394327</v>
       </c>
-    </row>
-    <row r="163" spans="1:7">
+      <c r="H162" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J162" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10">
       <c r="A163" s="2"/>
       <c r="B163" s="2" t="s">
         <v>47</v>
@@ -4169,8 +5648,17 @@
       <c r="G163" s="1">
         <v>5.525967046081661</v>
       </c>
-    </row>
-    <row r="164" spans="1:7">
+      <c r="H163" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10">
       <c r="A164" s="2"/>
       <c r="B164" s="2" t="s">
         <v>44</v>
@@ -4188,7 +5676,7 @@
         <v>2.219110498639924</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" spans="1:10">
       <c r="A165" s="2"/>
       <c r="B165" s="2" t="s">
         <v>43</v>
@@ -4208,13 +5696,22 @@
       <c r="G165" s="1">
         <v>0.7258761921506366</v>
       </c>
-    </row>
-    <row r="167" spans="1:7">
+      <c r="H165" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J165" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10">
       <c r="A167" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10">
       <c r="B168" s="2">
         <v>0</v>
       </c>
@@ -4228,7 +5725,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:10">
       <c r="A169" s="2">
         <v>0</v>
       </c>
@@ -4236,7 +5733,7 @@
         <v>1</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>83</v>
+        <v>199</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>17</v>
@@ -4245,7 +5742,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:10">
       <c r="A170" s="2">
         <v>1</v>
       </c>
@@ -4253,16 +5750,16 @@
         <v>2</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10">
       <c r="A171" s="2">
         <v>2</v>
       </c>
@@ -4270,16 +5767,16 @@
         <v>3</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10">
       <c r="A172" s="2">
         <v>3</v>
       </c>
@@ -4287,16 +5784,16 @@
         <v>4</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>85</v>
+        <v>201</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10">
       <c r="A173" s="2">
         <v>4</v>
       </c>
@@ -4304,16 +5801,16 @@
         <v>5</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>86</v>
+        <v>202</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10">
       <c r="A174" s="2">
         <v>5</v>
       </c>
@@ -4321,16 +5818,16 @@
         <v>6</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10">
       <c r="A175" s="2">
         <v>6</v>
       </c>
@@ -4344,10 +5841,10 @@
         <v>23</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10">
       <c r="A176" s="2">
         <v>7</v>
       </c>
@@ -4355,7 +5852,7 @@
         <v>8</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>24</v>
@@ -4364,12 +5861,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
       <c r="B179" s="2" t="s">
         <v>34</v>
       </c>
@@ -4377,10 +5874,10 @@
         <v>35</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>95</v>
+        <v>211</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>96</v>
+        <v>212</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>38</v>
@@ -4389,7 +5886,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" spans="1:9">
       <c r="A180" s="2" t="s">
         <v>40</v>
       </c>
@@ -4412,7 +5909,7 @@
         <v>-3.934177682267821</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:9">
       <c r="A181" s="2" t="s">
         <v>42</v>
       </c>
@@ -4435,7 +5932,7 @@
         <v>0.7686950419567691</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" spans="1:9">
       <c r="A182" s="2" t="s">
         <v>45</v>
       </c>
@@ -4458,7 +5955,7 @@
         <v>1.063595321597824</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" spans="1:9">
       <c r="A183" s="2" t="s">
         <v>46</v>
       </c>
@@ -4481,7 +5978,7 @@
         <v>0.6510267756381717</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" spans="1:9">
       <c r="A184" s="2" t="s">
         <v>47</v>
       </c>
@@ -4504,7 +6001,7 @@
         <v>2.271626894140172</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" spans="1:9">
       <c r="A185" s="2" t="s">
         <v>48</v>
       </c>
@@ -4527,7 +6024,7 @@
         <v>0.8021283414405227</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:9">
       <c r="A186" s="2" t="s">
         <v>49</v>
       </c>
@@ -4550,12 +6047,12 @@
         <v>1.415999436260922</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
       <c r="B189" s="2" t="s">
         <v>56</v>
       </c>
@@ -4571,8 +6068,17 @@
       <c r="F189" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="190" spans="1:7">
+      <c r="G189" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H189" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I189" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
       <c r="A190" s="2" t="s">
         <v>40</v>
       </c>
@@ -4591,8 +6097,17 @@
       <c r="F190" s="1">
         <v>0.01956177871289536</v>
       </c>
-    </row>
-    <row r="191" spans="1:7">
+      <c r="G190" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I190" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
       <c r="A191" s="2" t="s">
         <v>42</v>
       </c>
@@ -4611,8 +6126,17 @@
       <c r="F191" s="1">
         <v>2.156949687590592</v>
       </c>
-    </row>
-    <row r="192" spans="1:7">
+      <c r="G191" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H191" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I191" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
       <c r="A192" s="2" t="s">
         <v>45</v>
       </c>
@@ -4631,8 +6155,17 @@
       <c r="F192" s="1">
         <v>2.896767098704769</v>
       </c>
-    </row>
-    <row r="193" spans="1:6">
+      <c r="G192" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H192" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I192" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
       <c r="A193" s="2" t="s">
         <v>46</v>
       </c>
@@ -4651,8 +6184,17 @@
       <c r="F193" s="1">
         <v>1.917508669763636</v>
       </c>
-    </row>
-    <row r="194" spans="1:6">
+      <c r="G193" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H193" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="I193" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
       <c r="A194" s="2" t="s">
         <v>48</v>
       </c>
@@ -4671,8 +6213,17 @@
       <c r="F194" s="1">
         <v>2.230282683725291</v>
       </c>
-    </row>
-    <row r="195" spans="1:6">
+      <c r="G194" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H194" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I194" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
       <c r="A195" s="2" t="s">
         <v>49</v>
       </c>
@@ -4691,8 +6242,17 @@
       <c r="F195" s="1">
         <v>4.120602688423305</v>
       </c>
-    </row>
-    <row r="196" spans="1:6">
+      <c r="G195" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="I195" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
       <c r="A196" s="2" t="s">
         <v>47</v>
       </c>
@@ -4711,13 +6271,22 @@
       <c r="F196" s="1">
         <v>9.695160991131335</v>
       </c>
-    </row>
-    <row r="198" spans="1:6">
+      <c r="G196" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I196" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
       <c r="A198" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
       <c r="B199" s="2">
         <v>0</v>
       </c>
@@ -4731,7 +6300,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:9">
       <c r="A200" s="2">
         <v>0</v>
       </c>
@@ -4739,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>83</v>
+        <v>199</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>17</v>
@@ -4748,7 +6317,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" spans="1:9">
       <c r="A201" s="2">
         <v>1</v>
       </c>
@@ -4756,16 +6325,16 @@
         <v>2</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>99</v>
+        <v>235</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
       <c r="A202" s="2">
         <v>2</v>
       </c>
@@ -4773,16 +6342,16 @@
         <v>3</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
       <c r="A203" s="2">
         <v>3</v>
       </c>
@@ -4790,16 +6359,16 @@
         <v>4</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>100</v>
+        <v>237</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
       <c r="A204" s="2">
         <v>4</v>
       </c>
@@ -4807,16 +6376,16 @@
         <v>5</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>86</v>
+        <v>202</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
       <c r="A205" s="2">
         <v>5</v>
       </c>
@@ -4824,16 +6393,16 @@
         <v>6</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>101</v>
+        <v>238</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
       <c r="A206" s="2">
         <v>6</v>
       </c>
@@ -4847,10 +6416,10 @@
         <v>23</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
       <c r="A207" s="2">
         <v>7</v>
       </c>
@@ -4858,7 +6427,7 @@
         <v>8</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>102</v>
+        <v>239</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>24</v>
@@ -4867,12 +6436,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" spans="1:9">
       <c r="A209" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
       <c r="B210" s="2" t="s">
         <v>34</v>
       </c>
@@ -4880,10 +6449,10 @@
         <v>35</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>95</v>
+        <v>211</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>96</v>
+        <v>212</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>38</v>
@@ -4892,7 +6461,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" spans="1:9">
       <c r="A211" s="2" t="s">
         <v>40</v>
       </c>
@@ -4915,7 +6484,7 @@
         <v>-1.00168802216207</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" spans="1:9">
       <c r="A212" s="2" t="s">
         <v>41</v>
       </c>
@@ -4938,9 +6507,9 @@
         <v>-0.2803730383390651</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" spans="1:9">
       <c r="A213" s="2" t="s">
-        <v>110</v>
+        <v>247</v>
       </c>
       <c r="B213" s="1">
         <v>-1.11558867186674</v>
@@ -4961,7 +6530,7 @@
         <v>0.9188105650384166</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" spans="1:9">
       <c r="A214" s="2" t="s">
         <v>42</v>
       </c>
@@ -4984,7 +6553,7 @@
         <v>-0.3358438058574164</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" spans="1:9">
       <c r="A215" s="2" t="s">
         <v>45</v>
       </c>
@@ -5007,7 +6576,7 @@
         <v>-0.44417072077279</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" spans="1:9">
       <c r="A216" s="2" t="s">
         <v>48</v>
       </c>
@@ -5030,7 +6599,7 @@
         <v>-0.8636210545847494</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" spans="1:9">
       <c r="A217" s="2" t="s">
         <v>50</v>
       </c>
@@ -5053,12 +6622,12 @@
         <v>0.8331163259360232</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" spans="1:9">
       <c r="A219" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9">
       <c r="B220" s="2" t="s">
         <v>56</v>
       </c>
@@ -5074,8 +6643,17 @@
       <c r="F220" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="221" spans="1:7">
+      <c r="G220" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H220" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I220" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
       <c r="A221" s="2" t="s">
         <v>40</v>
       </c>
@@ -5094,8 +6672,17 @@
       <c r="F221" s="1">
         <v>0.3672589763482915</v>
       </c>
-    </row>
-    <row r="222" spans="1:7">
+      <c r="G221" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="H221" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="I221" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
       <c r="A222" s="2" t="s">
         <v>42</v>
       </c>
@@ -5114,8 +6701,17 @@
       <c r="F222" s="1">
         <v>0.7147347344769852</v>
       </c>
-    </row>
-    <row r="223" spans="1:7">
+      <c r="G222" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="H222" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I222" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
       <c r="A223" s="2" t="s">
         <v>41</v>
       </c>
@@ -5134,10 +6730,19 @@
       <c r="F223" s="1">
         <v>0.7555018577241088</v>
       </c>
-    </row>
-    <row r="224" spans="1:7">
+      <c r="G223" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="H223" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I223" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9">
       <c r="A224" s="2" t="s">
-        <v>110</v>
+        <v>247</v>
       </c>
       <c r="B224" s="1">
         <v>0.2824771975296116</v>
@@ -5152,7 +6757,7 @@
         <v>2.506307526530421</v>
       </c>
     </row>
-    <row r="225" spans="1:6">
+    <row r="225" spans="1:9">
       <c r="A225" s="2" t="s">
         <v>45</v>
       </c>
@@ -5171,8 +6776,17 @@
       <c r="F225" s="1">
         <v>0.6413559187023679</v>
       </c>
-    </row>
-    <row r="226" spans="1:6">
+      <c r="G225" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H225" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I225" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9">
       <c r="A226" s="2" t="s">
         <v>50</v>
       </c>
@@ -5191,8 +6805,17 @@
       <c r="F226" s="1">
         <v>2.300476616278571</v>
       </c>
-    </row>
-    <row r="227" spans="1:6">
+      <c r="G226" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H226" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I226" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9">
       <c r="A227" s="2" t="s">
         <v>48</v>
       </c>
@@ -5211,13 +6834,22 @@
       <c r="F227" s="1">
         <v>0.4216325602322222</v>
       </c>
-    </row>
-    <row r="229" spans="1:6">
+      <c r="G227" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H227" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I227" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9">
       <c r="B230" s="2">
         <v>0</v>
       </c>
@@ -5231,7 +6863,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:6">
+    <row r="231" spans="1:9">
       <c r="A231" s="2">
         <v>0</v>
       </c>
@@ -5239,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>83</v>
+        <v>199</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>17</v>
@@ -5248,7 +6880,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="232" spans="1:6">
+    <row r="232" spans="1:9">
       <c r="A232" s="2">
         <v>1</v>
       </c>
@@ -5256,16 +6888,16 @@
         <v>2</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>113</v>
+        <v>266</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9">
       <c r="A233" s="2">
         <v>2</v>
       </c>
@@ -5273,16 +6905,16 @@
         <v>3</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
       <c r="A234" s="2">
         <v>3</v>
       </c>
@@ -5290,16 +6922,16 @@
         <v>4</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>114</v>
+        <v>267</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
       <c r="A235" s="2">
         <v>4</v>
       </c>
@@ -5307,16 +6939,16 @@
         <v>5</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>115</v>
+        <v>268</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9">
       <c r="A236" s="2">
         <v>5</v>
       </c>
@@ -5324,16 +6956,16 @@
         <v>6</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>116</v>
+        <v>269</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9">
       <c r="A237" s="2">
         <v>6</v>
       </c>
@@ -5347,10 +6979,10 @@
         <v>23</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9">
       <c r="A238" s="2">
         <v>7</v>
       </c>
@@ -5367,12 +6999,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="240" spans="1:6">
+    <row r="240" spans="1:9">
       <c r="A240" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9">
       <c r="B241" s="2" t="s">
         <v>34</v>
       </c>
@@ -5380,10 +7012,10 @@
         <v>35</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>95</v>
+        <v>211</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>96</v>
+        <v>212</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>38</v>
@@ -5392,7 +7024,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="242" spans="1:7">
+    <row r="242" spans="1:9">
       <c r="A242" s="2" t="s">
         <v>40</v>
       </c>
@@ -5415,9 +7047,9 @@
         <v>-4.137840278699032</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" spans="1:9">
       <c r="A243" s="2" t="s">
-        <v>124</v>
+        <v>277</v>
       </c>
       <c r="B243" s="1">
         <v>2.475108324951747</v>
@@ -5438,7 +7070,7 @@
         <v>3.855046688861173</v>
       </c>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" spans="1:9">
       <c r="A244" s="2" t="s">
         <v>47</v>
       </c>
@@ -5461,9 +7093,9 @@
         <v>3.894545994309081</v>
       </c>
     </row>
-    <row r="245" spans="1:7">
+    <row r="245" spans="1:9">
       <c r="A245" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="B245" s="1">
         <v>1.172146522488462</v>
@@ -5484,12 +7116,12 @@
         <v>2.286231512144015</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" spans="1:9">
       <c r="A247" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9">
       <c r="B248" s="2" t="s">
         <v>56</v>
       </c>
@@ -5505,8 +7137,17 @@
       <c r="F248" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="249" spans="1:7">
+      <c r="G248" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H248" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I248" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9">
       <c r="A249" s="2" t="s">
         <v>40</v>
       </c>
@@ -5525,10 +7166,19 @@
       <c r="F249" s="1">
         <v>0.01595727758806971</v>
       </c>
-    </row>
-    <row r="250" spans="1:7">
+      <c r="G249" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H249" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="I249" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9">
       <c r="A250" s="2" t="s">
-        <v>124</v>
+        <v>277</v>
       </c>
       <c r="B250" s="1">
         <v>0.0004389868297785795</v>
@@ -5545,10 +7195,19 @@
       <c r="F250" s="1">
         <v>47.23082204309095</v>
       </c>
-    </row>
-    <row r="251" spans="1:7">
+      <c r="G250" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H250" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I250" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9">
       <c r="A251" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="B251" s="1">
         <v>0.03919733536927187</v>
@@ -5565,8 +7224,17 @@
       <c r="F251" s="1">
         <v>9.83779412991184</v>
       </c>
-    </row>
-    <row r="252" spans="1:7">
+      <c r="G251" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H251" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="I251" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9">
       <c r="A252" s="2" t="s">
         <v>47</v>
       </c>
@@ -5585,13 +7253,22 @@
       <c r="F252" s="1">
         <v>49.13374129999909</v>
       </c>
-    </row>
-    <row r="254" spans="1:7">
+      <c r="G252" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="H252" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I252" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9">
       <c r="A254" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9">
       <c r="B255" s="2">
         <v>0</v>
       </c>
@@ -5605,7 +7282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="256" spans="1:7">
+    <row r="256" spans="1:9">
       <c r="A256" s="2">
         <v>0</v>
       </c>
@@ -5630,13 +7307,13 @@
         <v>2</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>128</v>
+        <v>292</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>132</v>
+        <v>296</v>
       </c>
     </row>
     <row r="258" spans="1:8">
@@ -5647,13 +7324,13 @@
         <v>3</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>133</v>
+        <v>297</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -5664,13 +7341,13 @@
         <v>4</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>129</v>
+        <v>293</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>134</v>
+        <v>298</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -5681,13 +7358,13 @@
         <v>5</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>130</v>
+        <v>294</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>135</v>
+        <v>299</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -5698,13 +7375,13 @@
         <v>6</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>131</v>
+        <v>295</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>136</v>
+        <v>300</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -5721,7 +7398,7 @@
         <v>23</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>137</v>
+        <v>301</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -5732,7 +7409,7 @@
         <v>8</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>24</v>
@@ -5743,12 +7420,12 @@
     </row>
     <row r="265" spans="1:8">
       <c r="A265" t="s">
-        <v>138</v>
+        <v>302</v>
       </c>
     </row>
     <row r="266" spans="1:8">
       <c r="B266" s="2" t="s">
-        <v>139</v>
+        <v>303</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>34</v>
@@ -5849,10 +7526,10 @@
     </row>
     <row r="270" spans="1:8">
       <c r="A270" s="2" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="C270" s="1">
         <v>-0.2400774390892043</v>
@@ -5875,10 +7552,10 @@
     </row>
     <row r="271" spans="1:8">
       <c r="A271" s="2" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="C271" s="1">
         <v>-0.1176120700428341</v>
@@ -5901,10 +7578,10 @@
     </row>
     <row r="272" spans="1:8">
       <c r="A272" s="2" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="C272" s="1">
         <v>-0.1751205985803271</v>
@@ -6031,10 +7708,10 @@
     </row>
     <row r="277" spans="1:8">
       <c r="A277" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C277" s="1">
         <v>0.22279739573138</v>
@@ -6135,10 +7812,10 @@
     </row>
     <row r="281" spans="1:8">
       <c r="A281" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C281" s="1">
         <v>0.132899369457811</v>
@@ -6187,12 +7864,12 @@
     </row>
     <row r="284" spans="1:8">
       <c r="A284" t="s">
-        <v>144</v>
+        <v>308</v>
       </c>
     </row>
     <row r="285" spans="1:8">
       <c r="B285" s="2" t="s">
-        <v>145</v>
+        <v>309</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>34</v>
@@ -6293,10 +7970,10 @@
     </row>
     <row r="289" spans="1:8">
       <c r="A289" s="2" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="C289" s="1">
         <v>-0.2245604989042624</v>
@@ -6319,10 +7996,10 @@
     </row>
     <row r="290" spans="1:8">
       <c r="A290" s="2" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="C290" s="1">
         <v>0.07570591408388391</v>
@@ -6345,10 +8022,10 @@
     </row>
     <row r="291" spans="1:8">
       <c r="A291" s="2" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="C291" s="1">
         <v>-0.0750698683456173</v>
@@ -6475,10 +8152,10 @@
     </row>
     <row r="296" spans="1:8">
       <c r="A296" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C296" s="1">
         <v>0.2946250460749842</v>
@@ -6579,10 +8256,10 @@
     </row>
     <row r="300" spans="1:8">
       <c r="A300" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C300" s="1">
         <v>0.1221421410218785</v>
@@ -6631,12 +8308,12 @@
     </row>
     <row r="303" spans="1:8">
       <c r="A303" t="s">
-        <v>146</v>
+        <v>310</v>
       </c>
     </row>
     <row r="304" spans="1:8">
       <c r="B304" s="2" t="s">
-        <v>147</v>
+        <v>311</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>34</v>
@@ -6737,10 +8414,10 @@
     </row>
     <row r="308" spans="1:8">
       <c r="A308" s="2" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="C308" s="1">
         <v>-0.1616432179310029</v>
@@ -6763,10 +8440,10 @@
     </row>
     <row r="309" spans="1:8">
       <c r="A309" s="2" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="C309" s="1">
         <v>0.1439189481221047</v>
@@ -6789,10 +8466,10 @@
     </row>
     <row r="310" spans="1:8">
       <c r="A310" s="2" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="C310" s="1">
         <v>-0.454602459227178</v>
@@ -6919,10 +8596,10 @@
     </row>
     <row r="315" spans="1:8">
       <c r="A315" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C315" s="1">
         <v>0.2729068272972504</v>
@@ -7023,10 +8700,10 @@
     </row>
     <row r="319" spans="1:8">
       <c r="A319" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C319" s="1">
         <v>0.2552177671192801</v>
@@ -7075,12 +8752,12 @@
     </row>
     <row r="322" spans="1:8">
       <c r="A322" t="s">
-        <v>148</v>
+        <v>312</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="B323" s="2" t="s">
-        <v>149</v>
+        <v>313</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>34</v>
@@ -7181,10 +8858,10 @@
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="2" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="C327" s="1">
         <v>-0.1393912094926013</v>
@@ -7207,10 +8884,10 @@
     </row>
     <row r="328" spans="1:8">
       <c r="A328" s="2" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="C328" s="1">
         <v>0.2116915001866709</v>
@@ -7233,10 +8910,10 @@
     </row>
     <row r="329" spans="1:8">
       <c r="A329" s="2" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="C329" s="1">
         <v>-0.1662823082119289</v>
@@ -7363,10 +9040,10 @@
     </row>
     <row r="334" spans="1:8">
       <c r="A334" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C334" s="1">
         <v>0.04543825622598766</v>
@@ -7467,10 +9144,10 @@
     </row>
     <row r="338" spans="1:8">
       <c r="A338" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C338" s="1">
         <v>0.4220748693433146</v>
@@ -7519,12 +9196,12 @@
     </row>
     <row r="341" spans="1:8">
       <c r="A341" t="s">
-        <v>150</v>
+        <v>314</v>
       </c>
     </row>
     <row r="342" spans="1:8">
       <c r="B342" s="2" t="s">
-        <v>151</v>
+        <v>315</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>34</v>
@@ -7625,10 +9302,10 @@
     </row>
     <row r="346" spans="1:8">
       <c r="A346" s="2" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="C346" s="1">
         <v>-0.4282699444923456</v>
@@ -7651,10 +9328,10 @@
     </row>
     <row r="347" spans="1:8">
       <c r="A347" s="2" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="C347" s="1">
         <v>0.07649754534760504</v>
@@ -7677,10 +9354,10 @@
     </row>
     <row r="348" spans="1:8">
       <c r="A348" s="2" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="C348" s="1">
         <v>0.1114521808446799</v>
@@ -7807,10 +9484,10 @@
     </row>
     <row r="353" spans="1:8">
       <c r="A353" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C353" s="1">
         <v>0.1459816904266676</v>
@@ -7911,10 +9588,10 @@
     </row>
     <row r="357" spans="1:8">
       <c r="A357" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C357" s="1">
         <v>0.1773128236392056</v>
@@ -7963,12 +9640,12 @@
     </row>
     <row r="360" spans="1:8">
       <c r="A360" t="s">
-        <v>152</v>
+        <v>316</v>
       </c>
     </row>
     <row r="361" spans="1:8">
       <c r="B361" s="2" t="s">
-        <v>153</v>
+        <v>317</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>34</v>
@@ -8069,10 +9746,10 @@
     </row>
     <row r="365" spans="1:8">
       <c r="A365" s="2" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="C365" s="1">
         <v>-0.5419460247488325</v>
@@ -8095,10 +9772,10 @@
     </row>
     <row r="366" spans="1:8">
       <c r="A366" s="2" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="C366" s="1">
         <v>-0.6101451309832834</v>
@@ -8121,10 +9798,10 @@
     </row>
     <row r="367" spans="1:8">
       <c r="A367" s="2" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="C367" s="1">
         <v>0.2973762510675574</v>
@@ -8171,7 +9848,7 @@
         <v>0.7591144298301369</v>
       </c>
     </row>
-    <row r="369" spans="1:8">
+    <row r="369" spans="1:10">
       <c r="A369" s="2" t="s">
         <v>44</v>
       </c>
@@ -8197,7 +9874,7 @@
         <v>1.344563850095496</v>
       </c>
     </row>
-    <row r="370" spans="1:8">
+    <row r="370" spans="1:10">
       <c r="A370" s="2" t="s">
         <v>45</v>
       </c>
@@ -8223,7 +9900,7 @@
         <v>1.148256588619847</v>
       </c>
     </row>
-    <row r="371" spans="1:8">
+    <row r="371" spans="1:10">
       <c r="A371" s="2" t="s">
         <v>46</v>
       </c>
@@ -8249,12 +9926,12 @@
         <v>1.27748703258986</v>
       </c>
     </row>
-    <row r="372" spans="1:8">
+    <row r="372" spans="1:10">
       <c r="A372" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C372" s="1">
         <v>-0.2364711863733688</v>
@@ -8275,7 +9952,7 @@
         <v>0.2644607121807914</v>
       </c>
     </row>
-    <row r="373" spans="1:8">
+    <row r="373" spans="1:10">
       <c r="A373" s="2" t="s">
         <v>47</v>
       </c>
@@ -8301,7 +9978,7 @@
         <v>2.715975734229473</v>
       </c>
     </row>
-    <row r="374" spans="1:8">
+    <row r="374" spans="1:10">
       <c r="A374" s="2" t="s">
         <v>48</v>
       </c>
@@ -8327,7 +10004,7 @@
         <v>0.4749084948005612</v>
       </c>
     </row>
-    <row r="375" spans="1:8">
+    <row r="375" spans="1:10">
       <c r="A375" s="2" t="s">
         <v>49</v>
       </c>
@@ -8353,12 +10030,12 @@
         <v>3.882701724248067</v>
       </c>
     </row>
-    <row r="376" spans="1:8">
+    <row r="376" spans="1:10">
       <c r="A376" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C376" s="1">
         <v>-0.2548184232345599</v>
@@ -8379,7 +10056,7 @@
         <v>0.5851765342471886</v>
       </c>
     </row>
-    <row r="377" spans="1:8">
+    <row r="377" spans="1:10">
       <c r="A377" s="2" t="s">
         <v>50</v>
       </c>
@@ -8405,12 +10082,12 @@
         <v>0.9518238887025006</v>
       </c>
     </row>
-    <row r="379" spans="1:8">
+    <row r="379" spans="1:10">
       <c r="A379" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="380" spans="1:8">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10">
       <c r="C380" s="2" t="s">
         <v>56</v>
       </c>
@@ -8426,10 +10103,19 @@
       <c r="G380" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="381" spans="1:8">
+      <c r="H380" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I380" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J380" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10">
       <c r="A381" s="2" t="s">
-        <v>155</v>
+        <v>319</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>40</v>
@@ -8447,7 +10133,7 @@
         <v>1.057556116902716</v>
       </c>
     </row>
-    <row r="382" spans="1:8">
+    <row r="382" spans="1:10">
       <c r="A382" s="2"/>
       <c r="B382" s="2" t="s">
         <v>42</v>
@@ -8465,10 +10151,10 @@
         <v>1.330034494134055</v>
       </c>
     </row>
-    <row r="383" spans="1:8">
+    <row r="383" spans="1:10">
       <c r="A383" s="2"/>
       <c r="B383" s="2" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="C383" s="1">
         <v>0.09347994300655801</v>
@@ -8483,10 +10169,10 @@
         <v>1.041284755739972</v>
       </c>
     </row>
-    <row r="384" spans="1:8">
+    <row r="384" spans="1:10">
       <c r="A384" s="2"/>
       <c r="B384" s="2" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="C384" s="1">
         <v>0.5646665678645088</v>
@@ -8501,10 +10187,10 @@
         <v>1.326629003845438</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" spans="1:10">
       <c r="A385" s="2"/>
       <c r="B385" s="2" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="C385" s="1">
         <v>0.4108693666872871</v>
@@ -8519,7 +10205,7 @@
         <v>1.274111474779386</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" spans="1:10">
       <c r="A386" s="2"/>
       <c r="B386" s="2" t="s">
         <v>41</v>
@@ -8537,10 +10223,10 @@
         <v>1.008246277799337</v>
       </c>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" spans="1:10">
       <c r="A387" s="2"/>
       <c r="B387" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C387" s="1">
         <v>0.02414498365719728</v>
@@ -8557,8 +10243,17 @@
       <c r="G387" s="1">
         <v>1.51658444705629</v>
       </c>
-    </row>
-    <row r="388" spans="1:7">
+      <c r="H387" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I387" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="J387" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10">
       <c r="A388" s="2"/>
       <c r="B388" s="2" t="s">
         <v>45</v>
@@ -8578,8 +10273,17 @@
       <c r="G388" s="1">
         <v>2.329738023318202</v>
       </c>
-    </row>
-    <row r="389" spans="1:7">
+      <c r="H388" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I388" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J388" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10">
       <c r="A389" s="2"/>
       <c r="B389" s="2" t="s">
         <v>46</v>
@@ -8597,7 +10301,7 @@
         <v>1.349107470566798</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" spans="1:10">
       <c r="A390" s="2"/>
       <c r="B390" s="2" t="s">
         <v>50</v>
@@ -8617,11 +10321,20 @@
       <c r="G390" s="1">
         <v>2.274659838973565</v>
       </c>
-    </row>
-    <row r="391" spans="1:7">
+      <c r="H390" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I390" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="J390" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10">
       <c r="A391" s="2"/>
       <c r="B391" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C391" s="1">
         <v>0.3243426031463325</v>
@@ -8636,7 +10349,7 @@
         <v>1.487638886350497</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" spans="1:10">
       <c r="A392" s="2"/>
       <c r="B392" s="2" t="s">
         <v>48</v>
@@ -8654,7 +10367,7 @@
         <v>1.389205332376352</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" spans="1:10">
       <c r="A393" s="2"/>
       <c r="B393" s="2" t="s">
         <v>49</v>
@@ -8674,8 +10387,17 @@
       <c r="G393" s="1">
         <v>10.64929458374827</v>
       </c>
-    </row>
-    <row r="394" spans="1:7">
+      <c r="H393" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="I393" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="J393" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10">
       <c r="A394" s="2"/>
       <c r="B394" s="2" t="s">
         <v>47</v>
@@ -8695,8 +10417,17 @@
       <c r="G394" s="1">
         <v>2.867319304345929</v>
       </c>
-    </row>
-    <row r="395" spans="1:7">
+      <c r="H394" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I394" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="J394" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="395" spans="1:10">
       <c r="A395" s="2"/>
       <c r="B395" s="2" t="s">
         <v>44</v>
@@ -8714,7 +10445,7 @@
         <v>1.772831512945269</v>
       </c>
     </row>
-    <row r="396" spans="1:7">
+    <row r="396" spans="1:10">
       <c r="A396" s="2"/>
       <c r="B396" s="2" t="s">
         <v>43</v>
@@ -8732,9 +10463,9 @@
         <v>1.295358878984673</v>
       </c>
     </row>
-    <row r="397" spans="1:7">
+    <row r="397" spans="1:10">
       <c r="A397" s="2" t="s">
-        <v>156</v>
+        <v>320</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>40</v>
@@ -8754,8 +10485,17 @@
       <c r="G397" s="1">
         <v>0.2299059601240609</v>
       </c>
-    </row>
-    <row r="398" spans="1:7">
+      <c r="H397" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="I397" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="J397" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="398" spans="1:10">
       <c r="A398" s="2"/>
       <c r="B398" s="2" t="s">
         <v>42</v>
@@ -8775,11 +10515,20 @@
       <c r="G398" s="1">
         <v>1.927646766922562</v>
       </c>
-    </row>
-    <row r="399" spans="1:7">
+      <c r="H398" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I398" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="J398" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="399" spans="1:10">
       <c r="A399" s="2"/>
       <c r="B399" s="2" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="C399" s="1">
         <v>0.2066074478032444</v>
@@ -8794,10 +10543,10 @@
         <v>1.131940848772801</v>
       </c>
     </row>
-    <row r="400" spans="1:7">
+    <row r="400" spans="1:10">
       <c r="A400" s="2"/>
       <c r="B400" s="2" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="C400" s="1">
         <v>0.7362165268098622</v>
@@ -8812,10 +10561,10 @@
         <v>1.675611125804623</v>
       </c>
     </row>
-    <row r="401" spans="1:7">
+    <row r="401" spans="1:10">
       <c r="A401" s="2"/>
       <c r="B401" s="2" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="C401" s="1">
         <v>0.7833204492609442</v>
@@ -8830,7 +10579,7 @@
         <v>1.584033416387729</v>
       </c>
     </row>
-    <row r="402" spans="1:7">
+    <row r="402" spans="1:10">
       <c r="A402" s="2"/>
       <c r="B402" s="2" t="s">
         <v>41</v>
@@ -8850,11 +10599,20 @@
       <c r="G402" s="1">
         <v>0.7754109463560023</v>
       </c>
-    </row>
-    <row r="403" spans="1:7">
+      <c r="H402" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I402" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="J402" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="403" spans="1:10">
       <c r="A403" s="2"/>
       <c r="B403" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C403" s="1">
         <v>0.01130037510911335</v>
@@ -8871,8 +10629,17 @@
       <c r="G403" s="1">
         <v>1.686361532093942</v>
       </c>
-    </row>
-    <row r="404" spans="1:7">
+      <c r="H403" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="I403" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="J403" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="404" spans="1:10">
       <c r="A404" s="2"/>
       <c r="B404" s="2" t="s">
         <v>45</v>
@@ -8892,8 +10659,17 @@
       <c r="G404" s="1">
         <v>4.229555554372413</v>
       </c>
-    </row>
-    <row r="405" spans="1:7">
+      <c r="H404" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="I404" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="J404" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10">
       <c r="A405" s="2"/>
       <c r="B405" s="2" t="s">
         <v>46</v>
@@ -8913,8 +10689,17 @@
       <c r="G405" s="1">
         <v>1.674823039014708</v>
       </c>
-    </row>
-    <row r="406" spans="1:7">
+      <c r="H405" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I405" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="J405" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10">
       <c r="A406" s="2"/>
       <c r="B406" s="2" t="s">
         <v>50</v>
@@ -8934,11 +10719,20 @@
       <c r="G406" s="1">
         <v>2.294409299759061</v>
       </c>
-    </row>
-    <row r="407" spans="1:7">
+      <c r="H406" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I406" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="J406" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="407" spans="1:10">
       <c r="A407" s="2"/>
       <c r="B407" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C407" s="1">
         <v>0.4183881489014909</v>
@@ -8953,7 +10747,7 @@
         <v>1.518882875691661</v>
       </c>
     </row>
-    <row r="408" spans="1:7">
+    <row r="408" spans="1:10">
       <c r="A408" s="2"/>
       <c r="B408" s="2" t="s">
         <v>48</v>
@@ -8973,8 +10767,17 @@
       <c r="G408" s="1">
         <v>2.951252013528499</v>
       </c>
-    </row>
-    <row r="409" spans="1:7">
+      <c r="H408" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="I408" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="J408" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="409" spans="1:10">
       <c r="A409" s="2"/>
       <c r="B409" s="2" t="s">
         <v>49</v>
@@ -8994,8 +10797,17 @@
       <c r="G409" s="1">
         <v>15.42931709970684</v>
       </c>
-    </row>
-    <row r="410" spans="1:7">
+      <c r="H409" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="I409" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="J409" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="410" spans="1:10">
       <c r="A410" s="2"/>
       <c r="B410" s="2" t="s">
         <v>47</v>
@@ -9015,8 +10827,17 @@
       <c r="G410" s="1">
         <v>10.68808606581954</v>
       </c>
-    </row>
-    <row r="411" spans="1:7">
+      <c r="H410" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="I410" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="J410" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="411" spans="1:10">
       <c r="A411" s="2"/>
       <c r="B411" s="2" t="s">
         <v>44</v>
@@ -9034,7 +10855,7 @@
         <v>1.338807514659046</v>
       </c>
     </row>
-    <row r="412" spans="1:7">
+    <row r="412" spans="1:10">
       <c r="A412" s="2"/>
       <c r="B412" s="2" t="s">
         <v>43</v>
@@ -9054,10 +10875,19 @@
       <c r="G412" s="1">
         <v>0.7903382111290592</v>
       </c>
-    </row>
-    <row r="413" spans="1:7">
+      <c r="H412" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="I412" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="J412" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="413" spans="1:10">
       <c r="A413" s="2" t="s">
-        <v>157</v>
+        <v>321</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>40</v>
@@ -9077,8 +10907,17 @@
       <c r="G413" s="1">
         <v>0.2320281339705463</v>
       </c>
-    </row>
-    <row r="414" spans="1:7">
+      <c r="H413" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="I413" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="J413" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="414" spans="1:10">
       <c r="A414" s="2"/>
       <c r="B414" s="2" t="s">
         <v>42</v>
@@ -9096,10 +10935,10 @@
         <v>1.539805165268419</v>
       </c>
     </row>
-    <row r="415" spans="1:7">
+    <row r="415" spans="1:10">
       <c r="A415" s="2"/>
       <c r="B415" s="2" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="C415" s="1">
         <v>0.4042359040636789</v>
@@ -9114,10 +10953,10 @@
         <v>1.24382873233706</v>
       </c>
     </row>
-    <row r="416" spans="1:7">
+    <row r="416" spans="1:10">
       <c r="A416" s="2"/>
       <c r="B416" s="2" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="C416" s="1">
         <v>0.5556032155100873</v>
@@ -9132,10 +10971,10 @@
         <v>1.863605173315618</v>
       </c>
     </row>
-    <row r="417" spans="1:7">
+    <row r="417" spans="1:10">
       <c r="A417" s="2"/>
       <c r="B417" s="2" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="C417" s="1">
         <v>0.1478754795258307</v>
@@ -9150,7 +10989,7 @@
         <v>1.174831544036443</v>
       </c>
     </row>
-    <row r="418" spans="1:7">
+    <row r="418" spans="1:10">
       <c r="A418" s="2"/>
       <c r="B418" s="2" t="s">
         <v>41</v>
@@ -9168,10 +11007,10 @@
         <v>1.208911355693121</v>
       </c>
     </row>
-    <row r="419" spans="1:7">
+    <row r="419" spans="1:10">
       <c r="A419" s="2"/>
       <c r="B419" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C419" s="1">
         <v>0.03649416325969631</v>
@@ -9188,8 +11027,17 @@
       <c r="G419" s="1">
         <v>1.696666114621857</v>
       </c>
-    </row>
-    <row r="420" spans="1:7">
+      <c r="H419" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="I419" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="J419" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="420" spans="1:10">
       <c r="A420" s="2"/>
       <c r="B420" s="2" t="s">
         <v>45</v>
@@ -9209,8 +11057,17 @@
       <c r="G420" s="1">
         <v>2.874332373519337</v>
       </c>
-    </row>
-    <row r="421" spans="1:7">
+      <c r="H420" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="I420" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="J420" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="421" spans="1:10">
       <c r="A421" s="2"/>
       <c r="B421" s="2" t="s">
         <v>46</v>
@@ -9228,7 +11085,7 @@
         <v>1.437320280777647</v>
       </c>
     </row>
-    <row r="422" spans="1:7">
+    <row r="422" spans="1:10">
       <c r="A422" s="2"/>
       <c r="B422" s="2" t="s">
         <v>50</v>
@@ -9248,11 +11105,20 @@
       <c r="G422" s="1">
         <v>2.861338116075448</v>
       </c>
-    </row>
-    <row r="423" spans="1:7">
+      <c r="H422" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="I422" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="J422" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10">
       <c r="A423" s="2"/>
       <c r="B423" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C423" s="1">
         <v>0.1147765647959176</v>
@@ -9267,7 +11133,7 @@
         <v>1.772510495959634</v>
       </c>
     </row>
-    <row r="424" spans="1:7">
+    <row r="424" spans="1:10">
       <c r="A424" s="2"/>
       <c r="B424" s="2" t="s">
         <v>48</v>
@@ -9285,7 +11151,7 @@
         <v>1.666036265758821</v>
       </c>
     </row>
-    <row r="425" spans="1:7">
+    <row r="425" spans="1:10">
       <c r="A425" s="2"/>
       <c r="B425" s="2" t="s">
         <v>49</v>
@@ -9305,8 +11171,17 @@
       <c r="G425" s="1">
         <v>12.94400648395515</v>
       </c>
-    </row>
-    <row r="426" spans="1:7">
+      <c r="H425" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I425" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="J425" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10">
       <c r="A426" s="2"/>
       <c r="B426" s="2" t="s">
         <v>47</v>
@@ -9326,8 +11201,17 @@
       <c r="G426" s="1">
         <v>6.66992342112064</v>
       </c>
-    </row>
-    <row r="427" spans="1:7">
+      <c r="H426" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="I426" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="J426" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10">
       <c r="A427" s="2"/>
       <c r="B427" s="2" t="s">
         <v>44</v>
@@ -9345,7 +11229,7 @@
         <v>2.54159806574412</v>
       </c>
     </row>
-    <row r="428" spans="1:7">
+    <row r="428" spans="1:10">
       <c r="A428" s="2"/>
       <c r="B428" s="2" t="s">
         <v>43</v>
@@ -9363,9 +11247,9 @@
         <v>1.666869673683081</v>
       </c>
     </row>
-    <row r="429" spans="1:7">
+    <row r="429" spans="1:10">
       <c r="A429" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>40</v>
@@ -9385,8 +11269,17 @@
       <c r="G429" s="1">
         <v>0.3000898918403729</v>
       </c>
-    </row>
-    <row r="430" spans="1:7">
+      <c r="H429" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="I429" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="J429" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10">
       <c r="A430" s="2"/>
       <c r="B430" s="2" t="s">
         <v>42</v>
@@ -9406,11 +11299,20 @@
       <c r="G430" s="1">
         <v>1.643696725699813</v>
       </c>
-    </row>
-    <row r="431" spans="1:7">
+      <c r="H430" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="I430" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="J430" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10">
       <c r="A431" s="2"/>
       <c r="B431" s="2" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="C431" s="1">
         <v>0.4655256003639501</v>
@@ -9425,10 +11327,10 @@
         <v>1.264872547841137</v>
       </c>
     </row>
-    <row r="432" spans="1:7">
+    <row r="432" spans="1:10">
       <c r="A432" s="2"/>
       <c r="B432" s="2" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="C432" s="1">
         <v>0.3784167034157245</v>
@@ -9443,10 +11345,10 @@
         <v>1.979293660602406</v>
       </c>
     </row>
-    <row r="433" spans="1:7">
+    <row r="433" spans="1:10">
       <c r="A433" s="2"/>
       <c r="B433" s="2" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="C433" s="1">
         <v>0.5905314400337227</v>
@@ -9461,7 +11363,7 @@
         <v>1.551805404905302</v>
       </c>
     </row>
-    <row r="434" spans="1:7">
+    <row r="434" spans="1:10">
       <c r="A434" s="2"/>
       <c r="B434" s="2" t="s">
         <v>41</v>
@@ -9481,11 +11383,20 @@
       <c r="G434" s="1">
         <v>0.8560587934709275</v>
       </c>
-    </row>
-    <row r="435" spans="1:7">
+      <c r="H434" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="I434" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="J434" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10">
       <c r="A435" s="2"/>
       <c r="B435" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C435" s="1">
         <v>0.7166184746234072</v>
@@ -9500,7 +11411,7 @@
         <v>1.337480463847848</v>
       </c>
     </row>
-    <row r="436" spans="1:7">
+    <row r="436" spans="1:10">
       <c r="A436" s="2"/>
       <c r="B436" s="2" t="s">
         <v>45</v>
@@ -9520,8 +11431,17 @@
       <c r="G436" s="1">
         <v>4.253070870513331</v>
       </c>
-    </row>
-    <row r="437" spans="1:7">
+      <c r="H436" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="I436" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="J436" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10">
       <c r="A437" s="2"/>
       <c r="B437" s="2" t="s">
         <v>46</v>
@@ -9539,7 +11459,7 @@
         <v>1.23621773233286</v>
       </c>
     </row>
-    <row r="438" spans="1:7">
+    <row r="438" spans="1:10">
       <c r="A438" s="2"/>
       <c r="B438" s="2" t="s">
         <v>50</v>
@@ -9557,10 +11477,10 @@
         <v>1.884700752100861</v>
       </c>
     </row>
-    <row r="439" spans="1:7">
+    <row r="439" spans="1:10">
       <c r="A439" s="2"/>
       <c r="B439" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C439" s="1">
         <v>0.009820048795527999</v>
@@ -9577,8 +11497,17 @@
       <c r="G439" s="1">
         <v>2.101085151754464</v>
       </c>
-    </row>
-    <row r="440" spans="1:7">
+      <c r="H439" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="I439" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="J439" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10">
       <c r="A440" s="2"/>
       <c r="B440" s="2" t="s">
         <v>48</v>
@@ -9598,8 +11527,17 @@
       <c r="G440" s="1">
         <v>4.116566386514474</v>
       </c>
-    </row>
-    <row r="441" spans="1:7">
+      <c r="H440" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="I440" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="J440" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="441" spans="1:10">
       <c r="A441" s="2"/>
       <c r="B441" s="2" t="s">
         <v>49</v>
@@ -9619,8 +11557,17 @@
       <c r="G441" s="1">
         <v>10.23990274899488</v>
       </c>
-    </row>
-    <row r="442" spans="1:7">
+      <c r="H441" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="I441" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="J441" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="442" spans="1:10">
       <c r="A442" s="2"/>
       <c r="B442" s="2" t="s">
         <v>47</v>
@@ -9640,8 +11587,17 @@
       <c r="G442" s="1">
         <v>5.252024835569056</v>
       </c>
-    </row>
-    <row r="443" spans="1:7">
+      <c r="H442" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="I442" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J442" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="443" spans="1:10">
       <c r="A443" s="2"/>
       <c r="B443" s="2" t="s">
         <v>44</v>
@@ -9659,7 +11615,7 @@
         <v>2.263010256730673</v>
       </c>
     </row>
-    <row r="444" spans="1:7">
+    <row r="444" spans="1:10">
       <c r="A444" s="2"/>
       <c r="B444" s="2" t="s">
         <v>43</v>
@@ -9679,10 +11635,19 @@
       <c r="G444" s="1">
         <v>0.7394981372931224</v>
       </c>
-    </row>
-    <row r="445" spans="1:7">
+      <c r="H444" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="I444" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="J444" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="445" spans="1:10">
       <c r="A445" s="2" t="s">
-        <v>158</v>
+        <v>322</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>40</v>
@@ -9702,8 +11667,17 @@
       <c r="G445" s="1">
         <v>0.3052536431392068</v>
       </c>
-    </row>
-    <row r="446" spans="1:7">
+      <c r="H445" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="I445" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="J445" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="446" spans="1:10">
       <c r="A446" s="2"/>
       <c r="B446" s="2" t="s">
         <v>42</v>
@@ -9723,11 +11697,20 @@
       <c r="G446" s="1">
         <v>1.861284310388194</v>
       </c>
-    </row>
-    <row r="447" spans="1:7">
+      <c r="H446" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="I446" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="J446" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="447" spans="1:10">
       <c r="A447" s="2"/>
       <c r="B447" s="2" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="C447" s="1">
         <v>0.04056012474485642</v>
@@ -9744,11 +11727,20 @@
       <c r="G447" s="1">
         <v>0.9817589201669454</v>
       </c>
-    </row>
-    <row r="448" spans="1:7">
+      <c r="H447" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="I447" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="J447" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="448" spans="1:10">
       <c r="A448" s="2"/>
       <c r="B448" s="2" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="C448" s="1">
         <v>0.7644146490792776</v>
@@ -9763,10 +11755,10 @@
         <v>1.780317161960072</v>
       </c>
     </row>
-    <row r="449" spans="1:7">
+    <row r="449" spans="1:10">
       <c r="A449" s="2"/>
       <c r="B449" s="2" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="C449" s="1">
         <v>0.6988411840326656</v>
@@ -9781,7 +11773,7 @@
         <v>1.966135472023448</v>
       </c>
     </row>
-    <row r="450" spans="1:7">
+    <row r="450" spans="1:10">
       <c r="A450" s="2"/>
       <c r="B450" s="2" t="s">
         <v>41</v>
@@ -9799,10 +11791,10 @@
         <v>1.031460042346314</v>
       </c>
     </row>
-    <row r="451" spans="1:7">
+    <row r="451" spans="1:10">
       <c r="A451" s="2"/>
       <c r="B451" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C451" s="1">
         <v>0.2707577976341119</v>
@@ -9817,7 +11809,7 @@
         <v>1.500469705086311</v>
       </c>
     </row>
-    <row r="452" spans="1:7">
+    <row r="452" spans="1:10">
       <c r="A452" s="2"/>
       <c r="B452" s="2" t="s">
         <v>45</v>
@@ -9837,8 +11829,17 @@
       <c r="G452" s="1">
         <v>4.739404119714528</v>
       </c>
-    </row>
-    <row r="453" spans="1:7">
+      <c r="H452" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="I452" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="J452" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="453" spans="1:10">
       <c r="A453" s="2"/>
       <c r="B453" s="2" t="s">
         <v>46</v>
@@ -9856,7 +11857,7 @@
         <v>1.493377503460522</v>
       </c>
     </row>
-    <row r="454" spans="1:7">
+    <row r="454" spans="1:10">
       <c r="A454" s="2"/>
       <c r="B454" s="2" t="s">
         <v>50</v>
@@ -9874,10 +11875,10 @@
         <v>2.427204155472792</v>
       </c>
     </row>
-    <row r="455" spans="1:7">
+    <row r="455" spans="1:10">
       <c r="A455" s="2"/>
       <c r="B455" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C455" s="1">
         <v>0.3090265089901769</v>
@@ -9892,7 +11893,7 @@
         <v>1.68024688672224</v>
       </c>
     </row>
-    <row r="456" spans="1:7">
+    <row r="456" spans="1:10">
       <c r="A456" s="2"/>
       <c r="B456" s="2" t="s">
         <v>48</v>
@@ -9912,8 +11913,17 @@
       <c r="G456" s="1">
         <v>2.279951786670332</v>
       </c>
-    </row>
-    <row r="457" spans="1:7">
+      <c r="H456" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="I456" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="J456" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="457" spans="1:10">
       <c r="A457" s="2"/>
       <c r="B457" s="2" t="s">
         <v>49</v>
@@ -9931,7 +11941,7 @@
         <v>7.264899765517726</v>
       </c>
     </row>
-    <row r="458" spans="1:7">
+    <row r="458" spans="1:10">
       <c r="A458" s="2"/>
       <c r="B458" s="2" t="s">
         <v>47</v>
@@ -9951,8 +11961,17 @@
       <c r="G458" s="1">
         <v>3.411504294159583</v>
       </c>
-    </row>
-    <row r="459" spans="1:7">
+      <c r="H458" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="I458" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="J458" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="459" spans="1:10">
       <c r="A459" s="2"/>
       <c r="B459" s="2" t="s">
         <v>44</v>
@@ -9970,7 +11989,7 @@
         <v>1.805920882868414</v>
       </c>
     </row>
-    <row r="460" spans="1:7">
+    <row r="460" spans="1:10">
       <c r="A460" s="2"/>
       <c r="B460" s="2" t="s">
         <v>43</v>
@@ -9988,9 +12007,9 @@
         <v>1.002357476472079</v>
       </c>
     </row>
-    <row r="461" spans="1:7">
+    <row r="461" spans="1:10">
       <c r="A461" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>40</v>
@@ -10010,8 +12029,17 @@
       <c r="G461" s="1">
         <v>0.07376886982752039</v>
       </c>
-    </row>
-    <row r="462" spans="1:7">
+      <c r="H461" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="I461" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J461" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="462" spans="1:10">
       <c r="A462" s="2"/>
       <c r="B462" s="2" t="s">
         <v>42</v>
@@ -10031,11 +12059,20 @@
       <c r="G462" s="1">
         <v>0.8700272847412457</v>
       </c>
-    </row>
-    <row r="463" spans="1:7">
+      <c r="H462" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="I462" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="J462" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="463" spans="1:10">
       <c r="A463" s="2"/>
       <c r="B463" s="2" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="C463" s="1">
         <v>0.2784767556646617</v>
@@ -10050,10 +12087,10 @@
         <v>1.549863171355959</v>
       </c>
     </row>
-    <row r="464" spans="1:7">
+    <row r="464" spans="1:10">
       <c r="A464" s="2"/>
       <c r="B464" s="2" t="s">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="C464" s="1">
         <v>0.4102613546328545</v>
@@ -10068,10 +12105,10 @@
         <v>2.321334478163678</v>
       </c>
     </row>
-    <row r="465" spans="1:7">
+    <row r="465" spans="1:10">
       <c r="A465" s="2"/>
       <c r="B465" s="2" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="C465" s="1">
         <v>0.6189607721958915</v>
@@ -10086,7 +12123,7 @@
         <v>4.346377350995618</v>
       </c>
     </row>
-    <row r="466" spans="1:7">
+    <row r="466" spans="1:10">
       <c r="A466" s="2"/>
       <c r="B466" s="2" t="s">
         <v>41</v>
@@ -10106,11 +12143,20 @@
       <c r="G466" s="1">
         <v>0.7038415006731092</v>
       </c>
-    </row>
-    <row r="467" spans="1:7">
+      <c r="H466" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="I466" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="J466" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="467" spans="1:10">
       <c r="A467" s="2"/>
       <c r="B467" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C467" s="1">
         <v>0.3548485778588462</v>
@@ -10125,7 +12171,7 @@
         <v>1.302728240835181</v>
       </c>
     </row>
-    <row r="468" spans="1:7">
+    <row r="468" spans="1:10">
       <c r="A468" s="2"/>
       <c r="B468" s="2" t="s">
         <v>45</v>
@@ -10143,7 +12189,7 @@
         <v>3.152691677079474</v>
       </c>
     </row>
-    <row r="469" spans="1:7">
+    <row r="469" spans="1:10">
       <c r="A469" s="2"/>
       <c r="B469" s="2" t="s">
         <v>46</v>
@@ -10163,8 +12209,17 @@
       <c r="G469" s="1">
         <v>3.587612834045422</v>
       </c>
-    </row>
-    <row r="470" spans="1:7">
+      <c r="H469" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="I469" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="J469" s="1" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="470" spans="1:10">
       <c r="A470" s="2"/>
       <c r="B470" s="2" t="s">
         <v>50</v>
@@ -10182,10 +12237,10 @@
         <v>2.590430009339411</v>
       </c>
     </row>
-    <row r="471" spans="1:7">
+    <row r="471" spans="1:10">
       <c r="A471" s="2"/>
       <c r="B471" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C471" s="1">
         <v>0.552131630609431</v>
@@ -10200,7 +12255,7 @@
         <v>1.795307890993761</v>
       </c>
     </row>
-    <row r="472" spans="1:7">
+    <row r="472" spans="1:10">
       <c r="A472" s="2"/>
       <c r="B472" s="2" t="s">
         <v>48</v>
@@ -10218,7 +12273,7 @@
         <v>1.60786706255785</v>
       </c>
     </row>
-    <row r="473" spans="1:7">
+    <row r="473" spans="1:10">
       <c r="A473" s="2"/>
       <c r="B473" s="2" t="s">
         <v>49</v>
@@ -10238,8 +12293,17 @@
       <c r="G473" s="1">
         <v>48.55522083843815</v>
       </c>
-    </row>
-    <row r="474" spans="1:7">
+      <c r="H473" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="I473" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="J473" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="474" spans="1:10">
       <c r="A474" s="2"/>
       <c r="B474" s="2" t="s">
         <v>47</v>
@@ -10259,8 +12323,17 @@
       <c r="G474" s="1">
         <v>15.11935534953158</v>
       </c>
-    </row>
-    <row r="475" spans="1:7">
+      <c r="H474" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="I474" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="J474" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="475" spans="1:10">
       <c r="A475" s="2"/>
       <c r="B475" s="2" t="s">
         <v>44</v>
@@ -10278,7 +12351,7 @@
         <v>3.836512880916578</v>
       </c>
     </row>
-    <row r="476" spans="1:7">
+    <row r="476" spans="1:10">
       <c r="A476" s="2"/>
       <c r="B476" s="2" t="s">
         <v>43</v>
@@ -10296,12 +12369,12 @@
         <v>2.136383465068589</v>
       </c>
     </row>
-    <row r="478" spans="1:7">
+    <row r="478" spans="1:10">
       <c r="A478" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="479" spans="1:7">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="479" spans="1:10">
       <c r="B479" s="2">
         <v>0</v>
       </c>
@@ -10315,7 +12388,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="480" spans="1:7">
+    <row r="480" spans="1:10">
       <c r="A480" s="2">
         <v>0</v>
       </c>
@@ -10340,13 +12413,13 @@
         <v>2</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>128</v>
+        <v>292</v>
       </c>
       <c r="D481" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>164</v>
+        <v>453</v>
       </c>
     </row>
     <row r="482" spans="1:8">
@@ -10357,13 +12430,13 @@
         <v>3</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>160</v>
+        <v>236</v>
       </c>
       <c r="D482" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>165</v>
+        <v>454</v>
       </c>
     </row>
     <row r="483" spans="1:8">
@@ -10374,13 +12447,13 @@
         <v>4</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>161</v>
+        <v>450</v>
       </c>
       <c r="D483" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>166</v>
+        <v>455</v>
       </c>
     </row>
     <row r="484" spans="1:8">
@@ -10391,13 +12464,13 @@
         <v>5</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>162</v>
+        <v>451</v>
       </c>
       <c r="D484" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>167</v>
+        <v>456</v>
       </c>
     </row>
     <row r="485" spans="1:8">
@@ -10408,13 +12481,13 @@
         <v>6</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>163</v>
+        <v>452</v>
       </c>
       <c r="D485" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>168</v>
+        <v>457</v>
       </c>
     </row>
     <row r="486" spans="1:8">
@@ -10431,7 +12504,7 @@
         <v>23</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>169</v>
+        <v>458</v>
       </c>
     </row>
     <row r="487" spans="1:8">
@@ -10442,7 +12515,7 @@
         <v>8</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="D487" s="1" t="s">
         <v>24</v>
@@ -10453,12 +12526,12 @@
     </row>
     <row r="489" spans="1:8">
       <c r="A489" t="s">
-        <v>170</v>
+        <v>459</v>
       </c>
     </row>
     <row r="490" spans="1:8">
       <c r="B490" s="2" t="s">
-        <v>171</v>
+        <v>460</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>34</v>
@@ -10663,10 +12736,10 @@
     </row>
     <row r="498" spans="1:8">
       <c r="A498" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C498" s="1">
         <v>-0.2458702992489558</v>
@@ -10767,10 +12840,10 @@
     </row>
     <row r="502" spans="1:8">
       <c r="A502" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C502" s="1">
         <v>-0.09975885052689878</v>
@@ -10819,12 +12892,12 @@
     </row>
     <row r="505" spans="1:8">
       <c r="A505" t="s">
-        <v>172</v>
+        <v>461</v>
       </c>
     </row>
     <row r="506" spans="1:8">
       <c r="B506" s="2" t="s">
-        <v>145</v>
+        <v>309</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>34</v>
@@ -11029,10 +13102,10 @@
     </row>
     <row r="514" spans="1:8">
       <c r="A514" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C514" s="1">
         <v>0.07792513011951603</v>
@@ -11133,10 +13206,10 @@
     </row>
     <row r="518" spans="1:8">
       <c r="A518" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C518" s="1">
         <v>-0.01724535193601182</v>
@@ -11185,12 +13258,12 @@
     </row>
     <row r="521" spans="1:8">
       <c r="A521" t="s">
-        <v>173</v>
+        <v>462</v>
       </c>
     </row>
     <row r="522" spans="1:8">
       <c r="B522" s="2" t="s">
-        <v>149</v>
+        <v>313</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>34</v>
@@ -11395,10 +13468,10 @@
     </row>
     <row r="530" spans="1:8">
       <c r="A530" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C530" s="1">
         <v>-0.1430212518678175</v>
@@ -11499,10 +13572,10 @@
     </row>
     <row r="534" spans="1:8">
       <c r="A534" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C534" s="1">
         <v>0.291266449624504</v>
@@ -11551,12 +13624,12 @@
     </row>
     <row r="537" spans="1:8">
       <c r="A537" t="s">
-        <v>174</v>
+        <v>463</v>
       </c>
     </row>
     <row r="538" spans="1:8">
       <c r="B538" s="2" t="s">
-        <v>147</v>
+        <v>311</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>34</v>
@@ -11761,10 +13834,10 @@
     </row>
     <row r="546" spans="1:8">
       <c r="A546" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C546" s="1">
         <v>0.08888038077609614</v>
@@ -11865,10 +13938,10 @@
     </row>
     <row r="550" spans="1:8">
       <c r="A550" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C550" s="1">
         <v>0.129542118501986</v>
@@ -11917,12 +13990,12 @@
     </row>
     <row r="553" spans="1:8">
       <c r="A553" t="s">
-        <v>175</v>
+        <v>464</v>
       </c>
     </row>
     <row r="554" spans="1:8">
       <c r="B554" s="2" t="s">
-        <v>151</v>
+        <v>315</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>34</v>
@@ -12127,10 +14200,10 @@
     </row>
     <row r="562" spans="1:8">
       <c r="A562" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C562" s="1">
         <v>-0.04264627882691358</v>
@@ -12231,10 +14304,10 @@
     </row>
     <row r="566" spans="1:8">
       <c r="A566" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C566" s="1">
         <v>0.06083883373787775</v>
@@ -12283,12 +14356,12 @@
     </row>
     <row r="569" spans="1:8">
       <c r="A569" t="s">
-        <v>176</v>
+        <v>465</v>
       </c>
     </row>
     <row r="570" spans="1:8">
       <c r="B570" s="2" t="s">
-        <v>153</v>
+        <v>317</v>
       </c>
       <c r="C570" s="2" t="s">
         <v>34</v>
@@ -12465,7 +14538,7 @@
         <v>0.51747907684151</v>
       </c>
     </row>
-    <row r="577" spans="1:8">
+    <row r="577" spans="1:10">
       <c r="A577" s="2" t="s">
         <v>46</v>
       </c>
@@ -12491,12 +14564,12 @@
         <v>1.171768724058533</v>
       </c>
     </row>
-    <row r="578" spans="1:8">
+    <row r="578" spans="1:10">
       <c r="A578" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C578" s="1">
         <v>-0.4000488552381247</v>
@@ -12517,7 +14590,7 @@
         <v>0.08570707046726045</v>
       </c>
     </row>
-    <row r="579" spans="1:8">
+    <row r="579" spans="1:10">
       <c r="A579" s="2" t="s">
         <v>47</v>
       </c>
@@ -12543,7 +14616,7 @@
         <v>1.81659061863074</v>
       </c>
     </row>
-    <row r="580" spans="1:8">
+    <row r="580" spans="1:10">
       <c r="A580" s="2" t="s">
         <v>48</v>
       </c>
@@ -12569,7 +14642,7 @@
         <v>0.3402993971956579</v>
       </c>
     </row>
-    <row r="581" spans="1:8">
+    <row r="581" spans="1:10">
       <c r="A581" s="2" t="s">
         <v>49</v>
       </c>
@@ -12595,12 +14668,12 @@
         <v>2.058125765085419</v>
       </c>
     </row>
-    <row r="582" spans="1:8">
+    <row r="582" spans="1:10">
       <c r="A582" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C582" s="1">
         <v>-0.4937137273535617</v>
@@ -12621,7 +14694,7 @@
         <v>0.3216708394603258</v>
       </c>
     </row>
-    <row r="583" spans="1:8">
+    <row r="583" spans="1:10">
       <c r="A583" s="2" t="s">
         <v>50</v>
       </c>
@@ -12647,12 +14720,12 @@
         <v>0.381497532658966</v>
       </c>
     </row>
-    <row r="585" spans="1:8">
+    <row r="585" spans="1:10">
       <c r="A585" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="586" spans="1:8">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="586" spans="1:10">
       <c r="C586" s="2" t="s">
         <v>56</v>
       </c>
@@ -12668,10 +14741,19 @@
       <c r="G586" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="587" spans="1:8">
+      <c r="H586" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I586" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J586" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="587" spans="1:10">
       <c r="A587" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>40</v>
@@ -12691,8 +14773,17 @@
       <c r="G587" s="1">
         <v>0.07690776013859134</v>
       </c>
-    </row>
-    <row r="588" spans="1:8">
+      <c r="H587" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="I587" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="J587" s="1" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="588" spans="1:10">
       <c r="A588" s="2"/>
       <c r="B588" s="2" t="s">
         <v>42</v>
@@ -12712,8 +14803,17 @@
       <c r="G588" s="1">
         <v>0.8202704841449596</v>
       </c>
-    </row>
-    <row r="589" spans="1:8">
+      <c r="H588" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="I588" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="J588" s="1" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="589" spans="1:10">
       <c r="A589" s="2"/>
       <c r="B589" s="2" t="s">
         <v>41</v>
@@ -12731,10 +14831,10 @@
         <v>1.055738270620206</v>
       </c>
     </row>
-    <row r="590" spans="1:8">
+    <row r="590" spans="1:10">
       <c r="A590" s="2"/>
       <c r="B590" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C590" s="1">
         <v>0.1064955992418278</v>
@@ -12749,7 +14849,7 @@
         <v>1.08948713859893</v>
       </c>
     </row>
-    <row r="591" spans="1:8">
+    <row r="591" spans="1:10">
       <c r="A591" s="2"/>
       <c r="B591" s="2" t="s">
         <v>45</v>
@@ -12767,7 +14867,7 @@
         <v>1.677792727443097</v>
       </c>
     </row>
-    <row r="592" spans="1:8">
+    <row r="592" spans="1:10">
       <c r="A592" s="2"/>
       <c r="B592" s="2" t="s">
         <v>46</v>
@@ -12787,8 +14887,17 @@
       <c r="G592" s="1">
         <v>3.227696497213736</v>
       </c>
-    </row>
-    <row r="593" spans="1:7">
+      <c r="H592" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="I592" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="J592" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="593" spans="1:10">
       <c r="A593" s="2"/>
       <c r="B593" s="2" t="s">
         <v>50</v>
@@ -12806,10 +14915,10 @@
         <v>1.464476048845076</v>
       </c>
     </row>
-    <row r="594" spans="1:7">
+    <row r="594" spans="1:10">
       <c r="A594" s="2"/>
       <c r="B594" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C594" s="1">
         <v>0.2353245577495998</v>
@@ -12824,7 +14933,7 @@
         <v>1.379430647084457</v>
       </c>
     </row>
-    <row r="595" spans="1:7">
+    <row r="595" spans="1:10">
       <c r="A595" s="2"/>
       <c r="B595" s="2" t="s">
         <v>48</v>
@@ -12842,7 +14951,7 @@
         <v>1.405368290907364</v>
       </c>
     </row>
-    <row r="596" spans="1:7">
+    <row r="596" spans="1:10">
       <c r="A596" s="2"/>
       <c r="B596" s="2" t="s">
         <v>49</v>
@@ -12860,7 +14969,7 @@
         <v>7.831278391646729</v>
       </c>
     </row>
-    <row r="597" spans="1:7">
+    <row r="597" spans="1:10">
       <c r="A597" s="2"/>
       <c r="B597" s="2" t="s">
         <v>47</v>
@@ -12880,8 +14989,17 @@
       <c r="G597" s="1">
         <v>6.150852060415233</v>
       </c>
-    </row>
-    <row r="598" spans="1:7">
+      <c r="H597" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="I597" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="J597" s="1" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="598" spans="1:10">
       <c r="A598" s="2"/>
       <c r="B598" s="2" t="s">
         <v>44</v>
@@ -12899,7 +15017,7 @@
         <v>3.480051655327413</v>
       </c>
     </row>
-    <row r="599" spans="1:7">
+    <row r="599" spans="1:10">
       <c r="A599" s="2"/>
       <c r="B599" s="2" t="s">
         <v>43</v>
@@ -12917,9 +15035,9 @@
         <v>2.038255358903579</v>
       </c>
     </row>
-    <row r="600" spans="1:7">
+    <row r="600" spans="1:10">
       <c r="A600" s="2" t="s">
-        <v>178</v>
+        <v>467</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>40</v>
@@ -12939,8 +15057,17 @@
       <c r="G600" s="1">
         <v>1.535317796745953</v>
       </c>
-    </row>
-    <row r="601" spans="1:7">
+      <c r="H600" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="I600" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="J600" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="601" spans="1:10">
       <c r="A601" s="2"/>
       <c r="B601" s="2" t="s">
         <v>42</v>
@@ -12958,7 +15085,7 @@
         <v>1.115635192445201</v>
       </c>
     </row>
-    <row r="602" spans="1:7">
+    <row r="602" spans="1:10">
       <c r="A602" s="2"/>
       <c r="B602" s="2" t="s">
         <v>41</v>
@@ -12976,10 +15103,10 @@
         <v>1.45841495835104</v>
       </c>
     </row>
-    <row r="603" spans="1:7">
+    <row r="603" spans="1:10">
       <c r="A603" s="2"/>
       <c r="B603" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C603" s="1">
         <v>0.01095642293665167</v>
@@ -12996,8 +15123,17 @@
       <c r="G603" s="1">
         <v>0.945112057908928</v>
       </c>
-    </row>
-    <row r="604" spans="1:7">
+      <c r="H603" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="I603" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="J603" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="604" spans="1:10">
       <c r="A604" s="2"/>
       <c r="B604" s="2" t="s">
         <v>45</v>
@@ -13017,8 +15153,17 @@
       <c r="G604" s="1">
         <v>0.789300983694307</v>
       </c>
-    </row>
-    <row r="605" spans="1:7">
+      <c r="H604" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="I604" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="J604" s="1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="605" spans="1:10">
       <c r="A605" s="2"/>
       <c r="B605" s="2" t="s">
         <v>46</v>
@@ -13036,7 +15181,7 @@
         <v>1.090133204711787</v>
       </c>
     </row>
-    <row r="606" spans="1:7">
+    <row r="606" spans="1:10">
       <c r="A606" s="2"/>
       <c r="B606" s="2" t="s">
         <v>50</v>
@@ -13056,11 +15201,20 @@
       <c r="G606" s="1">
         <v>0.8533161131793756</v>
       </c>
-    </row>
-    <row r="607" spans="1:7">
+      <c r="H606" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="I606" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="J606" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="607" spans="1:10">
       <c r="A607" s="2"/>
       <c r="B607" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C607" s="1">
         <v>0.4492998724301147</v>
@@ -13075,7 +15229,7 @@
         <v>1.171952596400602</v>
       </c>
     </row>
-    <row r="608" spans="1:7">
+    <row r="608" spans="1:10">
       <c r="A608" s="2"/>
       <c r="B608" s="2" t="s">
         <v>48</v>
@@ -13093,7 +15247,7 @@
         <v>1.208892526538252</v>
       </c>
     </row>
-    <row r="609" spans="1:7">
+    <row r="609" spans="1:10">
       <c r="A609" s="2"/>
       <c r="B609" s="2" t="s">
         <v>49</v>
@@ -13113,8 +15267,17 @@
       <c r="G609" s="1">
         <v>0.7477059817817746</v>
       </c>
-    </row>
-    <row r="610" spans="1:7">
+      <c r="H609" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="I609" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="J609" s="1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="610" spans="1:10">
       <c r="A610" s="2"/>
       <c r="B610" s="2" t="s">
         <v>47</v>
@@ -13134,8 +15297,17 @@
       <c r="G610" s="1">
         <v>0.5018561630507677</v>
       </c>
-    </row>
-    <row r="611" spans="1:7">
+      <c r="H610" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="I610" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="J610" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="611" spans="1:10">
       <c r="A611" s="2"/>
       <c r="B611" s="2" t="s">
         <v>44</v>
@@ -13153,7 +15325,7 @@
         <v>1.439636771425713</v>
       </c>
     </row>
-    <row r="612" spans="1:7">
+    <row r="612" spans="1:10">
       <c r="A612" s="2"/>
       <c r="B612" s="2" t="s">
         <v>43</v>
@@ -13171,9 +15343,9 @@
         <v>1.623370121300475</v>
       </c>
     </row>
-    <row r="613" spans="1:7">
+    <row r="613" spans="1:10">
       <c r="A613" s="2" t="s">
-        <v>158</v>
+        <v>322</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>40</v>
@@ -13193,8 +15365,17 @@
       <c r="G613" s="1">
         <v>0.3410269585291988</v>
       </c>
-    </row>
-    <row r="614" spans="1:7">
+      <c r="H613" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="I613" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="J613" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="614" spans="1:10">
       <c r="A614" s="2"/>
       <c r="B614" s="2" t="s">
         <v>42</v>
@@ -13214,8 +15395,17 @@
       <c r="G614" s="1">
         <v>1.69334659432134</v>
       </c>
-    </row>
-    <row r="615" spans="1:7">
+      <c r="H614" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="I614" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J614" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="615" spans="1:10">
       <c r="A615" s="2"/>
       <c r="B615" s="2" t="s">
         <v>41</v>
@@ -13233,10 +15423,10 @@
         <v>1.243147063261141</v>
       </c>
     </row>
-    <row r="616" spans="1:7">
+    <row r="616" spans="1:10">
       <c r="A616" s="2"/>
       <c r="B616" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C616" s="1">
         <v>0.7307014160917791</v>
@@ -13251,7 +15441,7 @@
         <v>1.221644466700176</v>
       </c>
     </row>
-    <row r="617" spans="1:7">
+    <row r="617" spans="1:10">
       <c r="A617" s="2"/>
       <c r="B617" s="2" t="s">
         <v>45</v>
@@ -13271,8 +15461,17 @@
       <c r="G617" s="1">
         <v>2.493740345731034</v>
       </c>
-    </row>
-    <row r="618" spans="1:7">
+      <c r="H617" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="I617" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="J617" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="618" spans="1:10">
       <c r="A618" s="2"/>
       <c r="B618" s="2" t="s">
         <v>46</v>
@@ -13290,7 +15489,7 @@
         <v>1.315460207063985</v>
       </c>
     </row>
-    <row r="619" spans="1:7">
+    <row r="619" spans="1:10">
       <c r="A619" s="2"/>
       <c r="B619" s="2" t="s">
         <v>50</v>
@@ -13308,10 +15507,10 @@
         <v>1.356417001240222</v>
       </c>
     </row>
-    <row r="620" spans="1:7">
+    <row r="620" spans="1:10">
       <c r="A620" s="2"/>
       <c r="B620" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C620" s="1">
         <v>0.6927165844976992</v>
@@ -13326,7 +15525,7 @@
         <v>1.437041343273585</v>
       </c>
     </row>
-    <row r="621" spans="1:7">
+    <row r="621" spans="1:10">
       <c r="A621" s="2"/>
       <c r="B621" s="2" t="s">
         <v>48</v>
@@ -13346,8 +15545,17 @@
       <c r="G621" s="1">
         <v>1.997335546652153</v>
       </c>
-    </row>
-    <row r="622" spans="1:7">
+      <c r="H621" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="I621" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="J621" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="622" spans="1:10">
       <c r="A622" s="2"/>
       <c r="B622" s="2" t="s">
         <v>49</v>
@@ -13365,7 +15573,7 @@
         <v>1.193473702623425</v>
       </c>
     </row>
-    <row r="623" spans="1:7">
+    <row r="623" spans="1:10">
       <c r="A623" s="2"/>
       <c r="B623" s="2" t="s">
         <v>47</v>
@@ -13383,7 +15591,7 @@
         <v>1.400735373398431</v>
       </c>
     </row>
-    <row r="624" spans="1:7">
+    <row r="624" spans="1:10">
       <c r="A624" s="2"/>
       <c r="B624" s="2" t="s">
         <v>44</v>
@@ -13401,7 +15609,7 @@
         <v>1.544080868967912</v>
       </c>
     </row>
-    <row r="625" spans="1:7">
+    <row r="625" spans="1:10">
       <c r="A625" s="2"/>
       <c r="B625" s="2" t="s">
         <v>43</v>
@@ -13421,10 +15629,19 @@
       <c r="G625" s="1">
         <v>0.9514122887696125</v>
       </c>
-    </row>
-    <row r="626" spans="1:7">
+      <c r="H625" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="I625" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J625" s="1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="626" spans="1:10">
       <c r="A626" s="2" t="s">
-        <v>157</v>
+        <v>321</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>40</v>
@@ -13444,8 +15661,17 @@
       <c r="G626" s="1">
         <v>0.2640709698127507</v>
       </c>
-    </row>
-    <row r="627" spans="1:7">
+      <c r="H626" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="I626" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="J626" s="1" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="627" spans="1:10">
       <c r="A627" s="2"/>
       <c r="B627" s="2" t="s">
         <v>42</v>
@@ -13463,7 +15689,7 @@
         <v>1.361679648590076</v>
       </c>
     </row>
-    <row r="628" spans="1:7">
+    <row r="628" spans="1:10">
       <c r="A628" s="2"/>
       <c r="B628" s="2" t="s">
         <v>41</v>
@@ -13481,10 +15707,10 @@
         <v>1.475797906031103</v>
       </c>
     </row>
-    <row r="629" spans="1:7">
+    <row r="629" spans="1:10">
       <c r="A629" s="2"/>
       <c r="B629" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C629" s="1">
         <v>0.4620668891808699</v>
@@ -13499,7 +15725,7 @@
         <v>1.385063656867851</v>
       </c>
     </row>
-    <row r="630" spans="1:7">
+    <row r="630" spans="1:10">
       <c r="A630" s="2"/>
       <c r="B630" s="2" t="s">
         <v>45</v>
@@ -13517,7 +15743,7 @@
         <v>1.526457208797716</v>
       </c>
     </row>
-    <row r="631" spans="1:7">
+    <row r="631" spans="1:10">
       <c r="A631" s="2"/>
       <c r="B631" s="2" t="s">
         <v>46</v>
@@ -13535,7 +15761,7 @@
         <v>1.236051457989496</v>
       </c>
     </row>
-    <row r="632" spans="1:7">
+    <row r="632" spans="1:10">
       <c r="A632" s="2"/>
       <c r="B632" s="2" t="s">
         <v>50</v>
@@ -13553,10 +15779,10 @@
         <v>1.536229977246976</v>
       </c>
     </row>
-    <row r="633" spans="1:7">
+    <row r="633" spans="1:10">
       <c r="A633" s="2"/>
       <c r="B633" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C633" s="1">
         <v>0.3499381433206767</v>
@@ -13571,7 +15797,7 @@
         <v>1.493578800480897</v>
       </c>
     </row>
-    <row r="634" spans="1:7">
+    <row r="634" spans="1:10">
       <c r="A634" s="2"/>
       <c r="B634" s="2" t="s">
         <v>48</v>
@@ -13589,7 +15815,7 @@
         <v>1.507198111720417</v>
       </c>
     </row>
-    <row r="635" spans="1:7">
+    <row r="635" spans="1:10">
       <c r="A635" s="2"/>
       <c r="B635" s="2" t="s">
         <v>49</v>
@@ -13607,7 +15833,7 @@
         <v>1.915199402348792</v>
       </c>
     </row>
-    <row r="636" spans="1:7">
+    <row r="636" spans="1:10">
       <c r="A636" s="2"/>
       <c r="B636" s="2" t="s">
         <v>47</v>
@@ -13627,8 +15853,17 @@
       <c r="G636" s="1">
         <v>2.715284210130997</v>
       </c>
-    </row>
-    <row r="637" spans="1:7">
+      <c r="H636" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="I636" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="J636" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="637" spans="1:10">
       <c r="A637" s="2"/>
       <c r="B637" s="2" t="s">
         <v>44</v>
@@ -13646,7 +15881,7 @@
         <v>2.216644518216063</v>
       </c>
     </row>
-    <row r="638" spans="1:7">
+    <row r="638" spans="1:10">
       <c r="A638" s="2"/>
       <c r="B638" s="2" t="s">
         <v>43</v>
@@ -13664,9 +15899,9 @@
         <v>1.588972298792745</v>
       </c>
     </row>
-    <row r="639" spans="1:7">
+    <row r="639" spans="1:10">
       <c r="A639" s="2" t="s">
-        <v>156</v>
+        <v>320</v>
       </c>
       <c r="B639" s="2" t="s">
         <v>40</v>
@@ -13686,8 +15921,17 @@
       <c r="G639" s="1">
         <v>0.2682562884776737</v>
       </c>
-    </row>
-    <row r="640" spans="1:7">
+      <c r="H639" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="I639" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="J639" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="640" spans="1:10">
       <c r="A640" s="2"/>
       <c r="B640" s="2" t="s">
         <v>42</v>
@@ -13707,8 +15951,17 @@
       <c r="G640" s="1">
         <v>1.700447993399802</v>
       </c>
-    </row>
-    <row r="641" spans="1:7">
+      <c r="H640" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="I640" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="J640" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="641" spans="1:10">
       <c r="A641" s="2"/>
       <c r="B641" s="2" t="s">
         <v>41</v>
@@ -13728,11 +15981,20 @@
       <c r="G641" s="1">
         <v>0.9419700660410008</v>
       </c>
-    </row>
-    <row r="642" spans="1:7">
+      <c r="H641" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I641" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="J641" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="642" spans="1:10">
       <c r="A642" s="2"/>
       <c r="B642" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C642" s="1">
         <v>0.4531864316378061</v>
@@ -13747,7 +16009,7 @@
         <v>1.325162312906154</v>
       </c>
     </row>
-    <row r="643" spans="1:7">
+    <row r="643" spans="1:10">
       <c r="A643" s="2"/>
       <c r="B643" s="2" t="s">
         <v>45</v>
@@ -13767,8 +16029,17 @@
       <c r="G643" s="1">
         <v>2.244342309626032</v>
       </c>
-    </row>
-    <row r="644" spans="1:7">
+      <c r="H643" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="I643" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J643" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="644" spans="1:10">
       <c r="A644" s="2"/>
       <c r="B644" s="2" t="s">
         <v>46</v>
@@ -13788,8 +16059,17 @@
       <c r="G644" s="1">
         <v>1.416743265551941</v>
       </c>
-    </row>
-    <row r="645" spans="1:7">
+      <c r="H644" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="I644" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="J644" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="645" spans="1:10">
       <c r="A645" s="2"/>
       <c r="B645" s="2" t="s">
         <v>50</v>
@@ -13807,10 +16087,10 @@
         <v>1.266801159763143</v>
       </c>
     </row>
-    <row r="646" spans="1:7">
+    <row r="646" spans="1:10">
       <c r="A646" s="2"/>
       <c r="B646" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C646" s="1">
         <v>0.8896330971005005</v>
@@ -13825,7 +16105,7 @@
         <v>1.253986573767405</v>
       </c>
     </row>
-    <row r="647" spans="1:7">
+    <row r="647" spans="1:10">
       <c r="A647" s="2"/>
       <c r="B647" s="2" t="s">
         <v>48</v>
@@ -13845,8 +16125,17 @@
       <c r="G647" s="1">
         <v>2.536065691979798</v>
       </c>
-    </row>
-    <row r="648" spans="1:7">
+      <c r="H647" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="I647" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="J647" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="648" spans="1:10">
       <c r="A648" s="2"/>
       <c r="B648" s="2" t="s">
         <v>49</v>
@@ -13864,7 +16153,7 @@
         <v>2.237770034280498</v>
       </c>
     </row>
-    <row r="649" spans="1:7">
+    <row r="649" spans="1:10">
       <c r="A649" s="2"/>
       <c r="B649" s="2" t="s">
         <v>47</v>
@@ -13884,8 +16173,17 @@
       <c r="G649" s="1">
         <v>4.335457151494842</v>
       </c>
-    </row>
-    <row r="650" spans="1:7">
+      <c r="H649" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="I649" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="J649" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="650" spans="1:10">
       <c r="A650" s="2"/>
       <c r="B650" s="2" t="s">
         <v>44</v>
@@ -13903,7 +16201,7 @@
         <v>1.223879767204388</v>
       </c>
     </row>
-    <row r="651" spans="1:7">
+    <row r="651" spans="1:10">
       <c r="A651" s="2"/>
       <c r="B651" s="2" t="s">
         <v>43</v>
@@ -13923,10 +16221,19 @@
       <c r="G651" s="1">
         <v>0.8043305400352543</v>
       </c>
-    </row>
-    <row r="652" spans="1:7">
+      <c r="H651" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="I651" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="J651" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="652" spans="1:10">
       <c r="A652" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B652" s="2" t="s">
         <v>40</v>
@@ -13946,8 +16253,17 @@
       <c r="G652" s="1">
         <v>0.3574376464780358</v>
       </c>
-    </row>
-    <row r="653" spans="1:7">
+      <c r="H652" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="I652" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="J652" s="1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="653" spans="1:10">
       <c r="A653" s="2"/>
       <c r="B653" s="2" t="s">
         <v>42</v>
@@ -13965,7 +16281,7 @@
         <v>1.469864056467701</v>
       </c>
     </row>
-    <row r="654" spans="1:7">
+    <row r="654" spans="1:10">
       <c r="A654" s="2"/>
       <c r="B654" s="2" t="s">
         <v>41</v>
@@ -13983,10 +16299,10 @@
         <v>1.037246901569717</v>
       </c>
     </row>
-    <row r="655" spans="1:7">
+    <row r="655" spans="1:10">
       <c r="A655" s="2"/>
       <c r="B655" s="2" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C655" s="1">
         <v>0.2103323207642823</v>
@@ -14001,7 +16317,7 @@
         <v>1.084107591306336</v>
       </c>
     </row>
-    <row r="656" spans="1:7">
+    <row r="656" spans="1:10">
       <c r="A656" s="2"/>
       <c r="B656" s="2" t="s">
         <v>45</v>
@@ -14021,8 +16337,17 @@
       <c r="G656" s="1">
         <v>2.310510438744527</v>
       </c>
-    </row>
-    <row r="657" spans="1:7">
+      <c r="H656" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="I656" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J656" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="657" spans="1:10">
       <c r="A657" s="2"/>
       <c r="B657" s="2" t="s">
         <v>46</v>
@@ -14040,7 +16365,7 @@
         <v>1.048370243926604</v>
       </c>
     </row>
-    <row r="658" spans="1:7">
+    <row r="658" spans="1:10">
       <c r="A658" s="2"/>
       <c r="B658" s="2" t="s">
         <v>50</v>
@@ -14060,11 +16385,20 @@
       <c r="G658" s="1">
         <v>0.9929876912735229</v>
       </c>
-    </row>
-    <row r="659" spans="1:7">
+      <c r="H658" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="I658" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J658" s="1" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="659" spans="1:10">
       <c r="A659" s="2"/>
       <c r="B659" s="2" t="s">
-        <v>125</v>
+        <v>278</v>
       </c>
       <c r="C659" s="1">
         <v>0.03817110476886406</v>
@@ -14081,8 +16415,17 @@
       <c r="G659" s="1">
         <v>1.762351716356664</v>
       </c>
-    </row>
-    <row r="660" spans="1:7">
+      <c r="H659" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="I659" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="J659" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="660" spans="1:10">
       <c r="A660" s="2"/>
       <c r="B660" s="2" t="s">
         <v>48</v>
@@ -14102,8 +16445,17 @@
       <c r="G660" s="1">
         <v>3.495551132227617</v>
       </c>
-    </row>
-    <row r="661" spans="1:7">
+      <c r="H660" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="I660" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="J660" s="1" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="661" spans="1:10">
       <c r="A661" s="2"/>
       <c r="B661" s="2" t="s">
         <v>49</v>
@@ -14121,7 +16473,7 @@
         <v>1.579013990371032</v>
       </c>
     </row>
-    <row r="662" spans="1:7">
+    <row r="662" spans="1:10">
       <c r="A662" s="2"/>
       <c r="B662" s="2" t="s">
         <v>47</v>
@@ -14141,8 +16493,17 @@
       <c r="G662" s="1">
         <v>2.115859625722389</v>
       </c>
-    </row>
-    <row r="663" spans="1:7">
+      <c r="H662" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="I662" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="J662" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="663" spans="1:10">
       <c r="A663" s="2"/>
       <c r="B663" s="2" t="s">
         <v>44</v>
@@ -14160,7 +16521,7 @@
         <v>2.005271857521062</v>
       </c>
     </row>
-    <row r="664" spans="1:7">
+    <row r="664" spans="1:10">
       <c r="A664" s="2"/>
       <c r="B664" s="2" t="s">
         <v>43</v>
@@ -14179,6 +16540,15 @@
       </c>
       <c r="G664" s="1">
         <v>0.7726123138058778</v>
+      </c>
+      <c r="H664" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="I664" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="J664" s="1" t="s">
+        <v>554</v>
       </c>
     </row>
   </sheetData>
